--- a/model/Outputs/11. Interest rate/20/Output Files/0.2/Output_12_39.xlsx
+++ b/model/Outputs/11. Interest rate/20/Output Files/0.2/Output_12_39.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2741446.245701355</v>
+        <v>2742560.521034251</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14149578.12011754</v>
+        <v>14180036.52077127</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14149578.12011754</v>
+        <v>14180036.52077127</v>
       </c>
     </row>
     <row r="9">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>287242.3594286051</v>
+        <v>296115.8053715112</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>287242.3594286051</v>
+        <v>296115.8053715112</v>
       </c>
     </row>
     <row r="11">
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>27679189.53269589</v>
+        <v>27676286.32298139</v>
       </c>
     </row>
   </sheetData>
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>81.99931295557391</v>
+        <v>81.99931295557451</v>
       </c>
       <c r="C2" t="n">
         <v>49.47457824299391</v>
@@ -669,10 +669,10 @@
         <v>4.889628708011855</v>
       </c>
       <c r="G2" t="n">
-        <v>3.34732203575993</v>
+        <v>3.343301935257443</v>
       </c>
       <c r="H2" t="n">
-        <v>3.81023156784903</v>
+        <v>3.769060713577687</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -705,13 +705,13 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>87.3028355696476</v>
+        <v>83.48514612241085</v>
       </c>
       <c r="T2" t="n">
-        <v>184.8805867536895</v>
+        <v>184.8629887637397</v>
       </c>
       <c r="U2" t="n">
-        <v>249.1884925285102</v>
+        <v>249.1881709204699</v>
       </c>
       <c r="V2" t="n">
         <v>229.8510241668239</v>
@@ -733,7 +733,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>356.7600266655855</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -754,7 +754,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>209.5726123064429</v>
+        <v>108.2435886461458</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -781,28 +781,28 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>374</v>
+        <v>133.5184388018132</v>
       </c>
       <c r="S3" t="n">
-        <v>62.48881128536601</v>
+        <v>62.44885845517734</v>
       </c>
       <c r="T3" t="n">
-        <v>4.473444462796863</v>
+        <v>4.464774651476091</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1959257979225981</v>
+        <v>373</v>
       </c>
       <c r="V3" t="n">
-        <v>14.51066719152016</v>
+        <v>373</v>
       </c>
       <c r="W3" t="n">
-        <v>32.37314290982852</v>
+        <v>373</v>
       </c>
       <c r="X3" t="n">
         <v>19.86273944538755</v>
       </c>
       <c r="Y3" t="n">
-        <v>374</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -845,22 +845,22 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>91.79905402550071</v>
+        <v>91.51638189435317</v>
       </c>
       <c r="N4" t="n">
-        <v>143.0380916651276</v>
+        <v>142.7621408454554</v>
       </c>
       <c r="O4" t="n">
-        <v>214.4472689970478</v>
+        <v>214.1923837511461</v>
       </c>
       <c r="P4" t="n">
-        <v>265.2018645413922</v>
+        <v>264.9837661807364</v>
       </c>
       <c r="Q4" t="n">
-        <v>310.437266425598</v>
+        <v>310.286266425598</v>
       </c>
       <c r="R4" t="n">
-        <v>318.3317673254134</v>
+        <v>318.2506853582003</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -906,10 +906,10 @@
         <v>4.889628708011855</v>
       </c>
       <c r="G5" t="n">
-        <v>5.146009903586577</v>
+        <v>3.343301935257416</v>
       </c>
       <c r="H5" t="n">
-        <v>3.810231567849018</v>
+        <v>1.841667174369153</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -942,13 +942,13 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>85.50414770182039</v>
+        <v>85.41253966161939</v>
       </c>
       <c r="T5" t="n">
-        <v>184.8805867536895</v>
+        <v>184.8629887637398</v>
       </c>
       <c r="U5" t="n">
-        <v>249.1884925285102</v>
+        <v>249.18817092047</v>
       </c>
       <c r="V5" t="n">
         <v>229.8510241668239</v>
@@ -970,16 +970,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>374</v>
+        <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>361.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1015,31 +1015,31 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>113.3998766115246</v>
       </c>
       <c r="R6" t="n">
-        <v>133.6519859716246</v>
+        <v>133.5184388018133</v>
       </c>
       <c r="S6" t="n">
-        <v>165.3974546183378</v>
+        <v>62.44885845517734</v>
       </c>
       <c r="T6" t="n">
-        <v>4.473444462796834</v>
+        <v>4.46477465147608</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1959257979225968</v>
+        <v>0.1957842884886345</v>
       </c>
       <c r="V6" t="n">
         <v>14.51066719152016</v>
       </c>
       <c r="W6" t="n">
-        <v>32.37314290982852</v>
+        <v>373</v>
       </c>
       <c r="X6" t="n">
-        <v>19.86273944538755</v>
+        <v>373</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>373</v>
       </c>
     </row>
     <row r="7">
@@ -1082,22 +1082,22 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>91.79905402550071</v>
+        <v>91.51638189435316</v>
       </c>
       <c r="N7" t="n">
-        <v>143.0380916651275</v>
+        <v>142.7621408454554</v>
       </c>
       <c r="O7" t="n">
-        <v>214.4472689970477</v>
+        <v>214.1923837511461</v>
       </c>
       <c r="P7" t="n">
-        <v>265.2018645413922</v>
+        <v>264.9837661807365</v>
       </c>
       <c r="Q7" t="n">
-        <v>310.437266425598</v>
+        <v>310.286266425598</v>
       </c>
       <c r="R7" t="n">
-        <v>318.3317673254134</v>
+        <v>318.2506853582003</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1143,10 +1143,10 @@
         <v>4.889628708011855</v>
       </c>
       <c r="G8" t="n">
-        <v>3.347322035759929</v>
+        <v>3.343301935257416</v>
       </c>
       <c r="H8" t="n">
-        <v>5.608919435675665</v>
+        <v>3.769060713577661</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -1179,13 +1179,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>85.50414770182039</v>
+        <v>83.48514612241739</v>
       </c>
       <c r="T8" t="n">
-        <v>184.8805867536895</v>
+        <v>184.8629887637398</v>
       </c>
       <c r="U8" t="n">
-        <v>249.1884925285102</v>
+        <v>249.18817092047</v>
       </c>
       <c r="V8" t="n">
         <v>229.8510241668239</v>
@@ -1216,19 +1216,19 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>330.0284079411381</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>209.4985557026693</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1252,22 +1252,22 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>145.073529241423</v>
+        <v>144.7989632036872</v>
       </c>
       <c r="R9" t="n">
-        <v>133.6519859716246</v>
+        <v>133.5184388018133</v>
       </c>
       <c r="S9" t="n">
-        <v>62.48881128536602</v>
+        <v>62.44885845517734</v>
       </c>
       <c r="T9" t="n">
-        <v>357.7722286619882</v>
+        <v>4.46477465147608</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1959257979225968</v>
+        <v>373</v>
       </c>
       <c r="V9" t="n">
-        <v>14.51066719152016</v>
+        <v>137.5445188888223</v>
       </c>
       <c r="W9" t="n">
         <v>32.37314290982852</v>
@@ -1319,22 +1319,22 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>91.79905402550071</v>
+        <v>91.51638189435316</v>
       </c>
       <c r="N10" t="n">
-        <v>143.0380916651275</v>
+        <v>142.7621408454554</v>
       </c>
       <c r="O10" t="n">
-        <v>214.4472689970477</v>
+        <v>214.1923837511461</v>
       </c>
       <c r="P10" t="n">
-        <v>265.2018645413922</v>
+        <v>264.9837661807365</v>
       </c>
       <c r="Q10" t="n">
-        <v>310.437266425598</v>
+        <v>310.286266425598</v>
       </c>
       <c r="R10" t="n">
-        <v>318.3317673254134</v>
+        <v>318.2506853582003</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -1383,10 +1383,10 @@
         <v>82.32219640761923</v>
       </c>
       <c r="H11" t="n">
-        <v>73.31166372865304</v>
+        <v>73.31166372865306</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1143290738567598</v>
+        <v>0.1143290738567457</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1422,7 +1422,7 @@
         <v>260.3930993165036</v>
       </c>
       <c r="U11" t="n">
-        <v>329.1064824782589</v>
+        <v>329.106482478259</v>
       </c>
       <c r="V11" t="n">
         <v>309.8510241668239</v>
@@ -1447,10 +1447,10 @@
         <v>64.55655664632661</v>
       </c>
       <c r="C12" t="n">
-        <v>41.09991244551929</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D12" t="n">
-        <v>347.9376868977026</v>
+        <v>27.93768689770263</v>
       </c>
       <c r="E12" t="n">
         <v>22.67209722191262</v>
@@ -1459,10 +1459,10 @@
         <v>19.63624233787687</v>
       </c>
       <c r="G12" t="n">
-        <v>4.971649082574513</v>
+        <v>132.963229233503</v>
       </c>
       <c r="H12" t="n">
-        <v>4.751917375100376</v>
+        <v>4.75191737510039</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -1498,22 +1498,22 @@
         <v>132.3008395872528</v>
       </c>
       <c r="T12" t="n">
-        <v>82.26264257600438</v>
+        <v>82.2626425760044</v>
       </c>
       <c r="U12" t="n">
-        <v>80.15984089226222</v>
+        <v>80.1598408922622</v>
       </c>
       <c r="V12" t="n">
-        <v>414.5106671915202</v>
+        <v>94.51066719152016</v>
       </c>
       <c r="W12" t="n">
-        <v>112.3731429098285</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X12" t="n">
         <v>419.8627394453875</v>
       </c>
       <c r="Y12" t="n">
-        <v>207.3829729170628</v>
+        <v>79.39139276613435</v>
       </c>
     </row>
     <row r="13">
@@ -1553,19 +1553,19 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>7.836513403680812</v>
+        <v>7.836513403680783</v>
       </c>
       <c r="M13" t="n">
-        <v>99.71766058287777</v>
+        <v>99.71766058287778</v>
       </c>
       <c r="N13" t="n">
         <v>152.6706326487341</v>
       </c>
       <c r="O13" t="n">
-        <v>229.4515312921297</v>
+        <v>229.4515312921296</v>
       </c>
       <c r="P13" t="n">
-        <v>289.5867825741792</v>
+        <v>289.5867825741791</v>
       </c>
       <c r="Q13" t="n">
         <v>351.932266425598</v>
@@ -1574,7 +1574,7 @@
         <v>377.6558656860691</v>
       </c>
       <c r="S13" t="n">
-        <v>31.15431576842921</v>
+        <v>31.15431576842923</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
@@ -1620,10 +1620,10 @@
         <v>82.32219640761923</v>
       </c>
       <c r="H14" t="n">
-        <v>73.31166372865306</v>
+        <v>73.31166372865304</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1143290738567457</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1650,7 +1650,7 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>0.1143290738568794</v>
       </c>
       <c r="S14" t="n">
         <v>142.1440974505641</v>
@@ -1659,7 +1659,7 @@
         <v>260.3930993165036</v>
       </c>
       <c r="U14" t="n">
-        <v>329.106482478259</v>
+        <v>329.1064824782589</v>
       </c>
       <c r="V14" t="n">
         <v>309.8510241668239</v>
@@ -1684,22 +1684,22 @@
         <v>64.55655664632661</v>
       </c>
       <c r="C15" t="n">
-        <v>244.1506822152293</v>
+        <v>41.09991244551929</v>
       </c>
       <c r="D15" t="n">
-        <v>347.9376868977026</v>
+        <v>27.93768689770263</v>
       </c>
       <c r="E15" t="n">
-        <v>342.6720972219126</v>
+        <v>22.67209722191262</v>
       </c>
       <c r="F15" t="n">
-        <v>339.6362423378769</v>
+        <v>19.63624233787687</v>
       </c>
       <c r="G15" t="n">
-        <v>4.971649082574515</v>
+        <v>4.971649082574513</v>
       </c>
       <c r="H15" t="n">
-        <v>4.75191737510039</v>
+        <v>4.751917375100376</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -1735,19 +1735,19 @@
         <v>132.3008395872528</v>
       </c>
       <c r="T15" t="n">
-        <v>82.2626425760044</v>
+        <v>82.26264257600438</v>
       </c>
       <c r="U15" t="n">
-        <v>80.1598408922622</v>
+        <v>400.1598408922622</v>
       </c>
       <c r="V15" t="n">
-        <v>94.51066719152016</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W15" t="n">
-        <v>112.3731429098285</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X15" t="n">
-        <v>99.86273944538755</v>
+        <v>302.9135092150974</v>
       </c>
       <c r="Y15" t="n">
         <v>79.39139276613435</v>
@@ -1790,19 +1790,19 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>7.836513403680783</v>
+        <v>7.836513403680812</v>
       </c>
       <c r="M16" t="n">
-        <v>99.71766058287778</v>
+        <v>99.71766058287777</v>
       </c>
       <c r="N16" t="n">
         <v>152.6706326487341</v>
       </c>
       <c r="O16" t="n">
-        <v>229.4515312921296</v>
+        <v>229.4515312921297</v>
       </c>
       <c r="P16" t="n">
-        <v>289.5867825741791</v>
+        <v>289.5867825741792</v>
       </c>
       <c r="Q16" t="n">
         <v>351.932266425598</v>
@@ -1811,7 +1811,7 @@
         <v>377.6558656860691</v>
       </c>
       <c r="S16" t="n">
-        <v>31.15431576842923</v>
+        <v>31.15431576842921</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -1857,10 +1857,10 @@
         <v>82.32219640761923</v>
       </c>
       <c r="H17" t="n">
-        <v>73.42599280250981</v>
+        <v>73.31166372865306</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>0.1143290738567457</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1896,7 +1896,7 @@
         <v>260.3930993165036</v>
       </c>
       <c r="U17" t="n">
-        <v>329.1064824782589</v>
+        <v>329.106482478259</v>
       </c>
       <c r="V17" t="n">
         <v>309.8510241668239</v>
@@ -1918,25 +1918,25 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>64.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C18" t="n">
         <v>361.0999124455193</v>
       </c>
       <c r="D18" t="n">
-        <v>347.9376868977026</v>
+        <v>27.93768689770263</v>
       </c>
       <c r="E18" t="n">
-        <v>225.7228669916226</v>
+        <v>22.67209722191262</v>
       </c>
       <c r="F18" t="n">
         <v>19.63624233787687</v>
       </c>
       <c r="G18" t="n">
-        <v>4.971649082574513</v>
+        <v>4.971649082574515</v>
       </c>
       <c r="H18" t="n">
-        <v>4.751917375100376</v>
+        <v>4.75191737510039</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -1972,22 +1972,22 @@
         <v>132.3008395872528</v>
       </c>
       <c r="T18" t="n">
-        <v>82.26264257600438</v>
+        <v>82.2626425760044</v>
       </c>
       <c r="U18" t="n">
-        <v>80.15984089226222</v>
+        <v>80.1598408922622</v>
       </c>
       <c r="V18" t="n">
         <v>94.51066719152016</v>
       </c>
       <c r="W18" t="n">
-        <v>432.3731429098285</v>
+        <v>112.3731429098285</v>
       </c>
       <c r="X18" t="n">
-        <v>99.86273944538755</v>
+        <v>302.9135092150977</v>
       </c>
       <c r="Y18" t="n">
-        <v>79.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="19">
@@ -2027,19 +2027,19 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>7.836513403680812</v>
+        <v>7.836513403680783</v>
       </c>
       <c r="M19" t="n">
-        <v>99.71766058287777</v>
+        <v>99.71766058287778</v>
       </c>
       <c r="N19" t="n">
         <v>152.6706326487341</v>
       </c>
       <c r="O19" t="n">
-        <v>229.4515312921297</v>
+        <v>229.4515312921296</v>
       </c>
       <c r="P19" t="n">
-        <v>289.5867825741792</v>
+        <v>289.5867825741791</v>
       </c>
       <c r="Q19" t="n">
         <v>351.932266425598</v>
@@ -2048,7 +2048,7 @@
         <v>377.6558656860691</v>
       </c>
       <c r="S19" t="n">
-        <v>31.15431576842921</v>
+        <v>31.15431576842923</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -2158,7 +2158,7 @@
         <v>64.55655664632661</v>
       </c>
       <c r="C21" t="n">
-        <v>169.0914925964478</v>
+        <v>244.1506822152293</v>
       </c>
       <c r="D21" t="n">
         <v>347.9376868977026</v>
@@ -2200,7 +2200,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>75.05918961878146</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
         <v>179.5974576697378</v>
@@ -2334,7 +2334,7 @@
         <v>73.31166372865306</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1143290738567457</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2361,7 +2361,7 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>0.1143290738568794</v>
       </c>
       <c r="S23" t="n">
         <v>142.1440974505641</v>
@@ -2395,19 +2395,19 @@
         <v>64.55655664632661</v>
       </c>
       <c r="C24" t="n">
-        <v>41.09991244551929</v>
+        <v>244.1506822152293</v>
       </c>
       <c r="D24" t="n">
         <v>347.9376868977026</v>
       </c>
       <c r="E24" t="n">
-        <v>22.67209722191262</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F24" t="n">
-        <v>19.63624233787687</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G24" t="n">
-        <v>324.9716490825745</v>
+        <v>4.971649082574515</v>
       </c>
       <c r="H24" t="n">
         <v>4.75191737510039</v>
@@ -2437,13 +2437,13 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>75.05918961878146</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>307.5890378206665</v>
+        <v>179.5974576697378</v>
       </c>
       <c r="S24" t="n">
-        <v>452.3008395872528</v>
+        <v>132.3008395872528</v>
       </c>
       <c r="T24" t="n">
         <v>82.2626425760044</v>
@@ -2568,7 +2568,7 @@
         <v>82.32219640761923</v>
       </c>
       <c r="H26" t="n">
-        <v>73.42599280250981</v>
+        <v>73.31166372865306</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -2598,7 +2598,7 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>0.1143290738568794</v>
       </c>
       <c r="S26" t="n">
         <v>142.1440974505641</v>
@@ -2607,7 +2607,7 @@
         <v>260.3930993165036</v>
       </c>
       <c r="U26" t="n">
-        <v>329.1064824782589</v>
+        <v>329.106482478259</v>
       </c>
       <c r="V26" t="n">
         <v>309.8510241668239</v>
@@ -2635,19 +2635,19 @@
         <v>41.09991244551929</v>
       </c>
       <c r="D27" t="n">
-        <v>347.9376868977026</v>
+        <v>27.93768689770263</v>
       </c>
       <c r="E27" t="n">
         <v>22.67209722191262</v>
       </c>
       <c r="F27" t="n">
-        <v>339.6362423378769</v>
+        <v>222.6870121075869</v>
       </c>
       <c r="G27" t="n">
-        <v>208.0224188522846</v>
+        <v>4.971649082574515</v>
       </c>
       <c r="H27" t="n">
-        <v>324.7519173751004</v>
+        <v>4.75191737510039</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
@@ -2683,22 +2683,22 @@
         <v>132.3008395872528</v>
       </c>
       <c r="T27" t="n">
-        <v>82.26264257600438</v>
+        <v>82.2626425760044</v>
       </c>
       <c r="U27" t="n">
-        <v>80.15984089226222</v>
+        <v>80.1598408922622</v>
       </c>
       <c r="V27" t="n">
-        <v>94.51066719152016</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W27" t="n">
-        <v>112.3731429098285</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X27" t="n">
         <v>99.86273944538755</v>
       </c>
       <c r="Y27" t="n">
-        <v>79.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="28">
@@ -2738,19 +2738,19 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>7.836513403680812</v>
+        <v>7.836513403680783</v>
       </c>
       <c r="M28" t="n">
-        <v>99.71766058287777</v>
+        <v>99.71766058287778</v>
       </c>
       <c r="N28" t="n">
         <v>152.6706326487341</v>
       </c>
       <c r="O28" t="n">
-        <v>229.4515312921297</v>
+        <v>229.4515312921296</v>
       </c>
       <c r="P28" t="n">
-        <v>289.5867825741792</v>
+        <v>289.5867825741791</v>
       </c>
       <c r="Q28" t="n">
         <v>351.932266425598</v>
@@ -2759,7 +2759,7 @@
         <v>377.6558656860691</v>
       </c>
       <c r="S28" t="n">
-        <v>31.15431576842921</v>
+        <v>31.15431576842923</v>
       </c>
       <c r="T28" t="n">
         <v>0</v>
@@ -2805,7 +2805,7 @@
         <v>82.32219640761923</v>
       </c>
       <c r="H29" t="n">
-        <v>73.31166372865304</v>
+        <v>73.31166372865306</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -2844,7 +2844,7 @@
         <v>260.3930993165036</v>
       </c>
       <c r="U29" t="n">
-        <v>329.1064824782589</v>
+        <v>329.106482478259</v>
       </c>
       <c r="V29" t="n">
         <v>309.8510241668239</v>
@@ -2869,25 +2869,25 @@
         <v>64.55655664632661</v>
       </c>
       <c r="C30" t="n">
-        <v>361.0999124455193</v>
+        <v>41.09991244551929</v>
       </c>
       <c r="D30" t="n">
-        <v>27.93768689770263</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E30" t="n">
-        <v>22.67209722191262</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F30" t="n">
-        <v>19.63624233787687</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G30" t="n">
-        <v>4.971649082574513</v>
+        <v>4.971649082574515</v>
       </c>
       <c r="H30" t="n">
-        <v>4.751917375100376</v>
+        <v>4.75191737510039</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>127.9915801509286</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2914,22 +2914,22 @@
         <v>75.05918961878146</v>
       </c>
       <c r="R30" t="n">
-        <v>307.589037820666</v>
+        <v>179.5974576697378</v>
       </c>
       <c r="S30" t="n">
         <v>132.3008395872528</v>
       </c>
       <c r="T30" t="n">
-        <v>82.26264257600438</v>
+        <v>82.2626425760044</v>
       </c>
       <c r="U30" t="n">
-        <v>80.15984089226222</v>
+        <v>80.1598408922622</v>
       </c>
       <c r="V30" t="n">
-        <v>414.5106671915202</v>
+        <v>94.51066719152016</v>
       </c>
       <c r="W30" t="n">
-        <v>432.3731429098285</v>
+        <v>112.3731429098285</v>
       </c>
       <c r="X30" t="n">
         <v>99.86273944538755</v>
@@ -2975,19 +2975,19 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>7.836513403680812</v>
+        <v>7.836513403680783</v>
       </c>
       <c r="M31" t="n">
-        <v>99.71766058287777</v>
+        <v>99.71766058287778</v>
       </c>
       <c r="N31" t="n">
         <v>152.6706326487341</v>
       </c>
       <c r="O31" t="n">
-        <v>229.4515312921297</v>
+        <v>229.4515312921296</v>
       </c>
       <c r="P31" t="n">
-        <v>289.5867825741792</v>
+        <v>289.5867825741791</v>
       </c>
       <c r="Q31" t="n">
         <v>351.932266425598</v>
@@ -2996,7 +2996,7 @@
         <v>377.6558656860691</v>
       </c>
       <c r="S31" t="n">
-        <v>31.15431576842921</v>
+        <v>31.15431576842923</v>
       </c>
       <c r="T31" t="n">
         <v>0</v>
@@ -3103,16 +3103,16 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>64.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C33" t="n">
-        <v>361.0999124455193</v>
+        <v>244.1506822152292</v>
       </c>
       <c r="D33" t="n">
-        <v>347.9376868977026</v>
+        <v>27.93768689770263</v>
       </c>
       <c r="E33" t="n">
-        <v>150.6636773728411</v>
+        <v>22.67209722191262</v>
       </c>
       <c r="F33" t="n">
         <v>19.63624233787687</v>
@@ -3148,7 +3148,7 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>75.05918961878146</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
         <v>179.5974576697378</v>
@@ -3163,7 +3163,7 @@
         <v>80.15984089226222</v>
       </c>
       <c r="V33" t="n">
-        <v>94.51066719152016</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W33" t="n">
         <v>112.3731429098285</v>
@@ -3261,28 +3261,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>109.9993129555745</v>
+        <v>108.9993129555745</v>
       </c>
       <c r="C35" t="n">
-        <v>77.47457824299391</v>
+        <v>76.47457824299391</v>
       </c>
       <c r="D35" t="n">
-        <v>38.33915573984979</v>
+        <v>37.33915573984979</v>
       </c>
       <c r="E35" t="n">
-        <v>32.36328960686865</v>
+        <v>31.36328960686865</v>
       </c>
       <c r="F35" t="n">
-        <v>32.88962870801186</v>
+        <v>31.88962870801186</v>
       </c>
       <c r="G35" t="n">
-        <v>30.32219640761923</v>
+        <v>29.32219640761923</v>
       </c>
       <c r="H35" t="n">
-        <v>21.31166372865304</v>
+        <v>20.31166372865304</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>0.8815290738566833</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3312,25 +3312,25 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>90.1440974505641</v>
+        <v>89.1440974505641</v>
       </c>
       <c r="T35" t="n">
-        <v>208.3930993165036</v>
+        <v>207.3930993165036</v>
       </c>
       <c r="U35" t="n">
-        <v>283.3920115521155</v>
+        <v>276.1064824782589</v>
       </c>
       <c r="V35" t="n">
-        <v>257.8510241668239</v>
+        <v>256.8510241668239</v>
       </c>
       <c r="W35" t="n">
-        <v>266.3734759809475</v>
+        <v>265.3734759809475</v>
       </c>
       <c r="X35" t="n">
-        <v>220.2818334606677</v>
+        <v>219.2818334606677</v>
       </c>
       <c r="Y35" t="n">
-        <v>139.3174326828064</v>
+        <v>138.3174326828064</v>
       </c>
     </row>
     <row r="36">
@@ -3340,10 +3340,10 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>12.55655664632661</v>
+        <v>11.55655664632661</v>
       </c>
       <c r="C36" t="n">
-        <v>361.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
@@ -3352,7 +3352,7 @@
         <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -3388,28 +3388,28 @@
         <v>75.05918961878146</v>
       </c>
       <c r="R36" t="n">
-        <v>331.2396335831054</v>
+        <v>273.5717883665015</v>
       </c>
       <c r="S36" t="n">
-        <v>80.30083958725282</v>
+        <v>79.30083958725282</v>
       </c>
       <c r="T36" t="n">
-        <v>30.26264257600438</v>
+        <v>29.26264257600438</v>
       </c>
       <c r="U36" t="n">
-        <v>28.15984089226222</v>
+        <v>27.15984089226222</v>
       </c>
       <c r="V36" t="n">
-        <v>42.51066719152016</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W36" t="n">
-        <v>60.37314290982852</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X36" t="n">
-        <v>47.86273944538755</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y36" t="n">
-        <v>399.3913927661343</v>
+        <v>26.39139276613435</v>
       </c>
     </row>
     <row r="37">
@@ -3452,22 +3452,22 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>47.71766058287777</v>
+        <v>46.71766058287777</v>
       </c>
       <c r="N37" t="n">
-        <v>100.670632648734</v>
+        <v>99.67063264873404</v>
       </c>
       <c r="O37" t="n">
-        <v>177.4515312921297</v>
+        <v>176.4515312921297</v>
       </c>
       <c r="P37" t="n">
-        <v>237.5867825741792</v>
+        <v>236.5867825741792</v>
       </c>
       <c r="Q37" t="n">
-        <v>299.932266425598</v>
+        <v>298.932266425598</v>
       </c>
       <c r="R37" t="n">
-        <v>325.6558656860691</v>
+        <v>324.6558656860691</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -3498,25 +3498,25 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>109.9993129555745</v>
+        <v>108.9993129555745</v>
       </c>
       <c r="C38" t="n">
-        <v>77.47457824299391</v>
+        <v>76.47457824299391</v>
       </c>
       <c r="D38" t="n">
-        <v>38.33915573984979</v>
+        <v>37.33915573984979</v>
       </c>
       <c r="E38" t="n">
-        <v>32.36328960686865</v>
+        <v>31.36328960686865</v>
       </c>
       <c r="F38" t="n">
-        <v>32.88962870801186</v>
+        <v>31.88962870801186</v>
       </c>
       <c r="G38" t="n">
-        <v>30.32219640761923</v>
+        <v>29.32219640761923</v>
       </c>
       <c r="H38" t="n">
-        <v>27.59719280250956</v>
+        <v>20.31166372865304</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
@@ -3546,28 +3546,28 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>0.8815290738565568</v>
       </c>
       <c r="S38" t="n">
-        <v>90.1440974505641</v>
+        <v>89.1440974505641</v>
       </c>
       <c r="T38" t="n">
-        <v>208.3930993165036</v>
+        <v>207.3930993165036</v>
       </c>
       <c r="U38" t="n">
-        <v>277.1064824782589</v>
+        <v>276.1064824782589</v>
       </c>
       <c r="V38" t="n">
-        <v>257.8510241668239</v>
+        <v>256.8510241668239</v>
       </c>
       <c r="W38" t="n">
-        <v>266.3734759809475</v>
+        <v>265.3734759809475</v>
       </c>
       <c r="X38" t="n">
-        <v>220.2818334606677</v>
+        <v>219.2818334606677</v>
       </c>
       <c r="Y38" t="n">
-        <v>139.3174326828064</v>
+        <v>138.3174326828064</v>
       </c>
     </row>
     <row r="39">
@@ -3577,10 +3577,10 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>12.55655664632661</v>
+        <v>11.55655664632661</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D39" t="n">
         <v>347.9376868977026</v>
@@ -3592,7 +3592,7 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G39" t="n">
-        <v>324.9716490825745</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -3622,31 +3622,31 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>75.05918961878146</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>127.5974576697378</v>
+        <v>126.5974576697378</v>
       </c>
       <c r="S39" t="n">
-        <v>80.30083958725282</v>
+        <v>371.6605182216995</v>
       </c>
       <c r="T39" t="n">
-        <v>30.26264257600438</v>
+        <v>29.26264257600438</v>
       </c>
       <c r="U39" t="n">
-        <v>28.15984089226222</v>
+        <v>27.15984089226222</v>
       </c>
       <c r="V39" t="n">
-        <v>42.51066719152016</v>
+        <v>41.51066719152016</v>
       </c>
       <c r="W39" t="n">
-        <v>60.37314290982852</v>
+        <v>59.37314290982852</v>
       </c>
       <c r="X39" t="n">
-        <v>47.86273944538755</v>
+        <v>46.86273944538755</v>
       </c>
       <c r="Y39" t="n">
-        <v>291.2241451447441</v>
+        <v>26.39139276613435</v>
       </c>
     </row>
     <row r="40">
@@ -3689,22 +3689,22 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>47.71766058287777</v>
+        <v>46.71766058287777</v>
       </c>
       <c r="N40" t="n">
-        <v>100.670632648734</v>
+        <v>99.67063264873404</v>
       </c>
       <c r="O40" t="n">
-        <v>177.4515312921297</v>
+        <v>176.4515312921297</v>
       </c>
       <c r="P40" t="n">
-        <v>237.5867825741792</v>
+        <v>236.5867825741792</v>
       </c>
       <c r="Q40" t="n">
-        <v>299.932266425598</v>
+        <v>298.932266425598</v>
       </c>
       <c r="R40" t="n">
-        <v>325.6558656860691</v>
+        <v>324.6558656860691</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -3741,19 +3741,19 @@
         <v>129.4745782429939</v>
       </c>
       <c r="D41" t="n">
-        <v>90.33915573984979</v>
+        <v>0</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>84.88962870801186</v>
+        <v>0</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>73.31166372865304</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -3786,16 +3786,16 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>142.1440974505641</v>
       </c>
       <c r="T41" t="n">
-        <v>176.6146943336713</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>329.1064824782589</v>
       </c>
       <c r="V41" t="n">
-        <v>309.8510241668239</v>
+        <v>244.3515867481868</v>
       </c>
       <c r="W41" t="n">
         <v>318.3734759809475</v>
@@ -3817,22 +3817,22 @@
         <v>64.55655664632661</v>
       </c>
       <c r="C42" t="n">
-        <v>41.09991244551929</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D42" t="n">
         <v>27.93768689770263</v>
       </c>
       <c r="E42" t="n">
-        <v>342.6720972219126</v>
+        <v>22.67209722191262</v>
       </c>
       <c r="F42" t="n">
-        <v>339.6362423378769</v>
+        <v>19.63624233787687</v>
       </c>
       <c r="G42" t="n">
         <v>4.971649082574513</v>
       </c>
       <c r="H42" t="n">
-        <v>52.06074271117839</v>
+        <v>107.7159323299596</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
@@ -3859,7 +3859,7 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>75.05918961878146</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
         <v>179.5974576697378</v>
@@ -3871,7 +3871,7 @@
         <v>82.26264257600438</v>
       </c>
       <c r="U42" t="n">
-        <v>80.15984089226222</v>
+        <v>400.1598408922622</v>
       </c>
       <c r="V42" t="n">
         <v>94.51066719152016</v>
@@ -3972,16 +3972,16 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0</v>
+        <v>161.9993129555745</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>129.4745782429939</v>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
+        <v>90.33915573984979</v>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>84.36328960686865</v>
       </c>
       <c r="F44" t="n">
         <v>0</v>
@@ -3990,7 +3990,7 @@
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>73.31166372865306</v>
+        <v>0</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -4023,13 +4023,13 @@
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>142.1440974505641</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>172.0667900512784</v>
+        <v>231.0486971634675</v>
       </c>
       <c r="U44" t="n">
-        <v>329.106482478259</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
         <v>309.8510241668239</v>
@@ -4051,7 +4051,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>384.5565566463266</v>
+        <v>64.55655664632661</v>
       </c>
       <c r="C45" t="n">
         <v>41.09991244551929</v>
@@ -4060,19 +4060,19 @@
         <v>27.93768689770263</v>
       </c>
       <c r="E45" t="n">
-        <v>22.67209722191262</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F45" t="n">
-        <v>339.6362423378769</v>
+        <v>19.63624233787687</v>
       </c>
       <c r="G45" t="n">
         <v>4.971649082574515</v>
       </c>
       <c r="H45" t="n">
-        <v>4.75191737510039</v>
+        <v>146.3133899996972</v>
       </c>
       <c r="I45" t="n">
-        <v>122.3680149548594</v>
+        <v>0</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4099,7 +4099,7 @@
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>179.5974576697378</v>
+        <v>461</v>
       </c>
       <c r="S45" t="n">
         <v>132.3008395872528</v>
@@ -4297,76 +4297,76 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>106.914147375084</v>
+        <v>106.7884999460195</v>
       </c>
       <c r="C2" t="n">
-        <v>56.9398259175144</v>
+        <v>56.81417848844992</v>
       </c>
       <c r="D2" t="n">
-        <v>46.49623426110047</v>
+        <v>46.37058683203599</v>
       </c>
       <c r="E2" t="n">
-        <v>42.08887102183921</v>
+        <v>41.96322359277473</v>
       </c>
       <c r="F2" t="n">
-        <v>37.14985212485754</v>
+        <v>37.02420469579306</v>
       </c>
       <c r="G2" t="n">
-        <v>33.76871875540306</v>
+        <v>33.64713203391685</v>
       </c>
       <c r="H2" t="n">
-        <v>29.92</v>
+        <v>29.84</v>
       </c>
       <c r="I2" t="n">
-        <v>29.92</v>
+        <v>29.84</v>
       </c>
       <c r="J2" t="n">
-        <v>29.92</v>
+        <v>399.11</v>
       </c>
       <c r="K2" t="n">
-        <v>81.5583303517588</v>
+        <v>451.2545884924623</v>
       </c>
       <c r="L2" t="n">
-        <v>451.8183303517587</v>
+        <v>515.9445614572863</v>
       </c>
       <c r="M2" t="n">
-        <v>822.0783303517587</v>
+        <v>885.2145614572864</v>
       </c>
       <c r="N2" t="n">
-        <v>1192.338330351759</v>
+        <v>1064.065793611129</v>
       </c>
       <c r="O2" t="n">
-        <v>1192.338330351759</v>
+        <v>1064.065793611129</v>
       </c>
       <c r="P2" t="n">
-        <v>1250.430222218017</v>
+        <v>1122.73</v>
       </c>
       <c r="Q2" t="n">
-        <v>1496</v>
+        <v>1492</v>
       </c>
       <c r="R2" t="n">
-        <v>1496</v>
+        <v>1492</v>
       </c>
       <c r="S2" t="n">
-        <v>1407.815317606417</v>
+        <v>1407.671569573322</v>
       </c>
       <c r="T2" t="n">
-        <v>1221.067250178447</v>
+        <v>1220.941277892777</v>
       </c>
       <c r="U2" t="n">
-        <v>969.3617021698512</v>
+        <v>969.2360547407874</v>
       </c>
       <c r="V2" t="n">
-        <v>737.1889504861907</v>
+        <v>737.0633030571269</v>
       </c>
       <c r="W2" t="n">
-        <v>496.4076616165467</v>
+        <v>496.2820141874828</v>
       </c>
       <c r="X2" t="n">
-        <v>302.183587413852</v>
+        <v>302.0579399847881</v>
       </c>
       <c r="Y2" t="n">
-        <v>189.7417362190981</v>
+        <v>189.6160887900342</v>
       </c>
     </row>
     <row r="3">
@@ -4376,76 +4376,76 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>244.8234770117097</v>
+        <v>139.1769582284301</v>
       </c>
       <c r="C3" t="n">
-        <v>244.8234770117097</v>
+        <v>139.1769582284301</v>
       </c>
       <c r="D3" t="n">
-        <v>244.8234770117097</v>
+        <v>139.1769582284301</v>
       </c>
       <c r="E3" t="n">
-        <v>244.8234770117097</v>
+        <v>139.1769582284301</v>
       </c>
       <c r="F3" t="n">
-        <v>244.8234770117097</v>
+        <v>139.1769582284301</v>
       </c>
       <c r="G3" t="n">
-        <v>244.8234770117097</v>
+        <v>139.1769582284301</v>
       </c>
       <c r="H3" t="n">
-        <v>244.8234770117097</v>
+        <v>139.1769582284301</v>
       </c>
       <c r="I3" t="n">
-        <v>33.13396963146437</v>
+        <v>29.84</v>
       </c>
       <c r="J3" t="n">
-        <v>177.6113405614803</v>
+        <v>174.5185557413367</v>
       </c>
       <c r="K3" t="n">
-        <v>401.8775591086939</v>
+        <v>399.1286311753428</v>
       </c>
       <c r="L3" t="n">
-        <v>720.3885386284223</v>
+        <v>714.3818833454036</v>
       </c>
       <c r="M3" t="n">
-        <v>861.5031803712816</v>
+        <v>856.0360750882628</v>
       </c>
       <c r="N3" t="n">
-        <v>1051.274153846774</v>
+        <v>1046.360878846775</v>
       </c>
       <c r="O3" t="n">
-        <v>1341.994549492757</v>
+        <v>1337.587921002191</v>
       </c>
       <c r="P3" t="n">
-        <v>1496</v>
+        <v>1492</v>
       </c>
       <c r="Q3" t="n">
-        <v>1496</v>
+        <v>1492</v>
       </c>
       <c r="R3" t="n">
-        <v>1118.222222222222</v>
+        <v>1357.132890099179</v>
       </c>
       <c r="S3" t="n">
-        <v>1055.102210822863</v>
+        <v>1294.053235093949</v>
       </c>
       <c r="T3" t="n">
-        <v>1050.583580052361</v>
+        <v>1289.54336170862</v>
       </c>
       <c r="U3" t="n">
-        <v>1050.385675205974</v>
+        <v>912.7756849409428</v>
       </c>
       <c r="V3" t="n">
-        <v>1035.72843561858</v>
+        <v>536.008008173266</v>
       </c>
       <c r="W3" t="n">
-        <v>1003.028291265218</v>
+        <v>159.2403314055892</v>
       </c>
       <c r="X3" t="n">
-        <v>982.9649180880588</v>
+        <v>139.1769582284301</v>
       </c>
       <c r="Y3" t="n">
-        <v>605.1871403102809</v>
+        <v>139.1769582284301</v>
       </c>
     </row>
     <row r="4">
@@ -4455,76 +4455,76 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>445.227292545419</v>
+        <v>664.0839650109062</v>
       </c>
       <c r="C4" t="n">
-        <v>571.2292983638548</v>
+        <v>664.0839650109062</v>
       </c>
       <c r="D4" t="n">
-        <v>684.5484424888549</v>
+        <v>664.0839650109062</v>
       </c>
       <c r="E4" t="n">
-        <v>802.3773467002679</v>
+        <v>781.9128692223193</v>
       </c>
       <c r="F4" t="n">
-        <v>926.7383192922034</v>
+        <v>906.2738418142548</v>
       </c>
       <c r="G4" t="n">
-        <v>1080.326980261056</v>
+        <v>1059.864288029009</v>
       </c>
       <c r="H4" t="n">
-        <v>1251.462556240126</v>
+        <v>1059.864288029009</v>
       </c>
       <c r="I4" t="n">
-        <v>1251.462556240126</v>
+        <v>1286.526949915912</v>
       </c>
       <c r="J4" t="n">
-        <v>1251.462556240126</v>
+        <v>1385.387095409585</v>
       </c>
       <c r="K4" t="n">
-        <v>1382.983127881912</v>
+        <v>1385.387095409585</v>
       </c>
       <c r="L4" t="n">
-        <v>1386.743548464727</v>
+        <v>1385.387095409585</v>
       </c>
       <c r="M4" t="n">
-        <v>1294.017231267251</v>
+        <v>1292.946305617309</v>
       </c>
       <c r="N4" t="n">
-        <v>1149.534310393385</v>
+        <v>1148.742122945132</v>
       </c>
       <c r="O4" t="n">
-        <v>932.9209073660642</v>
+        <v>932.3861797621563</v>
       </c>
       <c r="P4" t="n">
-        <v>665.0402361121327</v>
+        <v>664.7258098826245</v>
       </c>
       <c r="Q4" t="n">
-        <v>351.4672397226398</v>
+        <v>351.3053387456568</v>
       </c>
       <c r="R4" t="n">
-        <v>29.92</v>
+        <v>29.84</v>
       </c>
       <c r="S4" t="n">
-        <v>29.92</v>
+        <v>29.84</v>
       </c>
       <c r="T4" t="n">
-        <v>29.92</v>
+        <v>218.7013496506081</v>
       </c>
       <c r="U4" t="n">
-        <v>29.92</v>
+        <v>465.2625721249603</v>
       </c>
       <c r="V4" t="n">
-        <v>29.92</v>
+        <v>664.0839650109062</v>
       </c>
       <c r="W4" t="n">
-        <v>71.02986317590111</v>
+        <v>664.0839650109062</v>
       </c>
       <c r="X4" t="n">
-        <v>222.0606542000946</v>
+        <v>664.0839650109062</v>
       </c>
       <c r="Y4" t="n">
-        <v>333.4699548791269</v>
+        <v>664.0839650109062</v>
       </c>
     </row>
     <row r="5">
@@ -4534,76 +4534,76 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>108.7310038072321</v>
+        <v>104.8416377852028</v>
       </c>
       <c r="C5" t="n">
-        <v>58.75668234966251</v>
+        <v>54.86731632763319</v>
       </c>
       <c r="D5" t="n">
-        <v>48.31309069324858</v>
+        <v>44.42372467121926</v>
       </c>
       <c r="E5" t="n">
-        <v>43.90572745398732</v>
+        <v>40.016361431958</v>
       </c>
       <c r="F5" t="n">
-        <v>38.96670855700565</v>
+        <v>35.07734253497633</v>
       </c>
       <c r="G5" t="n">
-        <v>33.76871875540305</v>
+        <v>31.70026987310015</v>
       </c>
       <c r="H5" t="n">
-        <v>29.92</v>
+        <v>29.84</v>
       </c>
       <c r="I5" t="n">
-        <v>29.92</v>
+        <v>29.84</v>
       </c>
       <c r="J5" t="n">
-        <v>29.92</v>
+        <v>29.93969029977264</v>
       </c>
       <c r="K5" t="n">
-        <v>400.18</v>
+        <v>260.8358206463047</v>
       </c>
       <c r="L5" t="n">
-        <v>464.2419149748744</v>
+        <v>325.5257936111288</v>
       </c>
       <c r="M5" t="n">
-        <v>834.5019149748744</v>
+        <v>694.7957936111288</v>
       </c>
       <c r="N5" t="n">
-        <v>1067.648108133742</v>
+        <v>1064.065793611129</v>
       </c>
       <c r="O5" t="n">
-        <v>1067.648108133742</v>
+        <v>1064.065793611129</v>
       </c>
       <c r="P5" t="n">
-        <v>1125.74</v>
+        <v>1122.73</v>
       </c>
       <c r="Q5" t="n">
-        <v>1496</v>
+        <v>1492</v>
       </c>
       <c r="R5" t="n">
-        <v>1496</v>
+        <v>1492</v>
       </c>
       <c r="S5" t="n">
-        <v>1409.632174038565</v>
+        <v>1405.724707412506</v>
       </c>
       <c r="T5" t="n">
-        <v>1222.884106610596</v>
+        <v>1218.994415731961</v>
       </c>
       <c r="U5" t="n">
-        <v>971.178558602</v>
+        <v>967.2891925799706</v>
       </c>
       <c r="V5" t="n">
-        <v>739.0058069183394</v>
+        <v>735.1164408963101</v>
       </c>
       <c r="W5" t="n">
-        <v>498.2245180486954</v>
+        <v>494.3351520266661</v>
       </c>
       <c r="X5" t="n">
-        <v>304.0004438460007</v>
+        <v>300.1110778239714</v>
       </c>
       <c r="Y5" t="n">
-        <v>191.5585926512468</v>
+        <v>187.6692266292175</v>
       </c>
     </row>
     <row r="6">
@@ -4613,76 +4613,76 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>740.8008178458908</v>
+        <v>29.84</v>
       </c>
       <c r="C6" t="n">
-        <v>376.0534315372855</v>
+        <v>29.84</v>
       </c>
       <c r="D6" t="n">
-        <v>376.0534315372855</v>
+        <v>29.84</v>
       </c>
       <c r="E6" t="n">
-        <v>29.92</v>
+        <v>29.84</v>
       </c>
       <c r="F6" t="n">
-        <v>29.92</v>
+        <v>29.84</v>
       </c>
       <c r="G6" t="n">
-        <v>29.92</v>
+        <v>29.84</v>
       </c>
       <c r="H6" t="n">
-        <v>29.92</v>
+        <v>29.84</v>
       </c>
       <c r="I6" t="n">
-        <v>29.92</v>
+        <v>29.84</v>
       </c>
       <c r="J6" t="n">
-        <v>174.3973709300159</v>
+        <v>174.5185557413367</v>
       </c>
       <c r="K6" t="n">
-        <v>398.6635894772295</v>
+        <v>399.1286311753428</v>
       </c>
       <c r="L6" t="n">
-        <v>717.174568996958</v>
+        <v>714.3818833454036</v>
       </c>
       <c r="M6" t="n">
-        <v>858.2892107398172</v>
+        <v>856.0360750882628</v>
       </c>
       <c r="N6" t="n">
-        <v>1048.06018421531</v>
+        <v>1046.360878846775</v>
       </c>
       <c r="O6" t="n">
-        <v>1338.780579861293</v>
+        <v>1337.587921002191</v>
       </c>
       <c r="P6" t="n">
-        <v>1492.786030368536</v>
+        <v>1492</v>
       </c>
       <c r="Q6" t="n">
-        <v>1492.786030368536</v>
+        <v>1377.454670089369</v>
       </c>
       <c r="R6" t="n">
-        <v>1357.784024336592</v>
+        <v>1242.587560188548</v>
       </c>
       <c r="S6" t="n">
-        <v>1190.715888358473</v>
+        <v>1179.507905183318</v>
       </c>
       <c r="T6" t="n">
-        <v>1186.197257587971</v>
+        <v>1174.998031797988</v>
       </c>
       <c r="U6" t="n">
-        <v>1185.999352741584</v>
+        <v>1174.800269890424</v>
       </c>
       <c r="V6" t="n">
-        <v>1171.34211315419</v>
+        <v>1160.14303030303</v>
       </c>
       <c r="W6" t="n">
-        <v>1138.641968800828</v>
+        <v>783.3753535353535</v>
       </c>
       <c r="X6" t="n">
-        <v>1118.578595623669</v>
+        <v>406.6076767676768</v>
       </c>
       <c r="Y6" t="n">
-        <v>1118.578595623669</v>
+        <v>29.84</v>
       </c>
     </row>
     <row r="7">
@@ -4692,76 +4692,76 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1210.2445873942</v>
+        <v>506.0619583378124</v>
       </c>
       <c r="C7" t="n">
-        <v>1336.246593212636</v>
+        <v>632.0639641562482</v>
       </c>
       <c r="D7" t="n">
-        <v>1386.743548464727</v>
+        <v>745.3831082812483</v>
       </c>
       <c r="E7" t="n">
-        <v>1386.743548464727</v>
+        <v>863.2120124926613</v>
       </c>
       <c r="F7" t="n">
-        <v>1386.743548464727</v>
+        <v>987.5729850845968</v>
       </c>
       <c r="G7" t="n">
-        <v>1386.743548464727</v>
+        <v>987.5729850845968</v>
       </c>
       <c r="H7" t="n">
-        <v>1386.743548464727</v>
+        <v>1158.724433522683</v>
       </c>
       <c r="I7" t="n">
-        <v>1386.743548464727</v>
+        <v>1385.387095409585</v>
       </c>
       <c r="J7" t="n">
-        <v>1386.743548464727</v>
+        <v>1385.387095409585</v>
       </c>
       <c r="K7" t="n">
-        <v>1386.743548464727</v>
+        <v>1385.387095409585</v>
       </c>
       <c r="L7" t="n">
-        <v>1386.743548464727</v>
+        <v>1385.387095409585</v>
       </c>
       <c r="M7" t="n">
-        <v>1294.017231267251</v>
+        <v>1292.946305617309</v>
       </c>
       <c r="N7" t="n">
-        <v>1149.534310393385</v>
+        <v>1148.742122945132</v>
       </c>
       <c r="O7" t="n">
-        <v>932.9209073660643</v>
+        <v>932.3861797621564</v>
       </c>
       <c r="P7" t="n">
-        <v>665.0402361121328</v>
+        <v>664.7258098826245</v>
       </c>
       <c r="Q7" t="n">
-        <v>351.4672397226398</v>
+        <v>351.3053387456568</v>
       </c>
       <c r="R7" t="n">
-        <v>29.92</v>
+        <v>29.84</v>
       </c>
       <c r="S7" t="n">
-        <v>29.92</v>
+        <v>29.84</v>
       </c>
       <c r="T7" t="n">
-        <v>218.7737217817557</v>
+        <v>29.84</v>
       </c>
       <c r="U7" t="n">
-        <v>465.3348468790587</v>
+        <v>29.84</v>
       </c>
       <c r="V7" t="n">
-        <v>664.1562397650047</v>
+        <v>29.84</v>
       </c>
       <c r="W7" t="n">
-        <v>836.0471580246821</v>
+        <v>131.8645289682945</v>
       </c>
       <c r="X7" t="n">
-        <v>987.0779490488756</v>
+        <v>282.895319992488</v>
       </c>
       <c r="Y7" t="n">
-        <v>1098.487249727908</v>
+        <v>394.3046206715202</v>
       </c>
     </row>
     <row r="8">
@@ -4771,76 +4771,76 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>108.7310038072321</v>
+        <v>106.7884999460195</v>
       </c>
       <c r="C8" t="n">
-        <v>58.75668234966251</v>
+        <v>56.81417848844986</v>
       </c>
       <c r="D8" t="n">
-        <v>48.31309069324858</v>
+        <v>46.37058683203593</v>
       </c>
       <c r="E8" t="n">
-        <v>43.90572745398732</v>
+        <v>41.96322359277467</v>
       </c>
       <c r="F8" t="n">
-        <v>38.96670855700565</v>
+        <v>37.024204695793</v>
       </c>
       <c r="G8" t="n">
-        <v>35.58557518755118</v>
+        <v>33.64713203391683</v>
       </c>
       <c r="H8" t="n">
-        <v>29.92</v>
+        <v>29.84</v>
       </c>
       <c r="I8" t="n">
-        <v>29.92</v>
+        <v>29.84</v>
       </c>
       <c r="J8" t="n">
-        <v>263.0661931588676</v>
+        <v>29.93969029977264</v>
       </c>
       <c r="K8" t="n">
-        <v>633.3261931588676</v>
+        <v>82.08427879223495</v>
       </c>
       <c r="L8" t="n">
-        <v>697.388108133742</v>
+        <v>451.3542787922349</v>
       </c>
       <c r="M8" t="n">
-        <v>1067.648108133742</v>
+        <v>820.6242787922349</v>
       </c>
       <c r="N8" t="n">
-        <v>1437.908108133742</v>
+        <v>1064.065793611129</v>
       </c>
       <c r="O8" t="n">
-        <v>1437.908108133742</v>
+        <v>1064.065793611129</v>
       </c>
       <c r="P8" t="n">
-        <v>1496</v>
+        <v>1122.73</v>
       </c>
       <c r="Q8" t="n">
-        <v>1496</v>
+        <v>1492</v>
       </c>
       <c r="R8" t="n">
-        <v>1496</v>
+        <v>1492.000000000007</v>
       </c>
       <c r="S8" t="n">
-        <v>1409.632174038565</v>
+        <v>1407.671569573322</v>
       </c>
       <c r="T8" t="n">
-        <v>1222.884106610596</v>
+        <v>1220.941277892777</v>
       </c>
       <c r="U8" t="n">
-        <v>971.178558602</v>
+        <v>969.2360547407873</v>
       </c>
       <c r="V8" t="n">
-        <v>739.0058069183394</v>
+        <v>737.0633030571267</v>
       </c>
       <c r="W8" t="n">
-        <v>498.2245180486954</v>
+        <v>496.2820141874827</v>
       </c>
       <c r="X8" t="n">
-        <v>304.0004438460007</v>
+        <v>302.057939984788</v>
       </c>
       <c r="Y8" t="n">
-        <v>191.5585926512468</v>
+        <v>189.6160887900341</v>
       </c>
     </row>
     <row r="9">
@@ -4850,76 +4850,76 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>719.1203429896864</v>
+        <v>574.8167309533409</v>
       </c>
       <c r="C9" t="n">
-        <v>719.1203429896864</v>
+        <v>574.8167309533409</v>
       </c>
       <c r="D9" t="n">
-        <v>719.1203429896864</v>
+        <v>574.8167309533409</v>
       </c>
       <c r="E9" t="n">
-        <v>372.9869114524009</v>
+        <v>574.8167309533409</v>
       </c>
       <c r="F9" t="n">
-        <v>29.92</v>
+        <v>574.8167309533409</v>
       </c>
       <c r="G9" t="n">
-        <v>29.92</v>
+        <v>574.8167309533409</v>
       </c>
       <c r="H9" t="n">
-        <v>29.92</v>
+        <v>241.454702729969</v>
       </c>
       <c r="I9" t="n">
-        <v>29.92</v>
+        <v>29.84</v>
       </c>
       <c r="J9" t="n">
-        <v>174.3973709300159</v>
+        <v>174.5185557413367</v>
       </c>
       <c r="K9" t="n">
-        <v>398.6635894772295</v>
+        <v>399.1286311753428</v>
       </c>
       <c r="L9" t="n">
-        <v>717.174568996958</v>
+        <v>718.1019687139392</v>
       </c>
       <c r="M9" t="n">
-        <v>858.2892107398172</v>
+        <v>859.7561604567984</v>
       </c>
       <c r="N9" t="n">
-        <v>1048.06018421531</v>
+        <v>1046.360878846775</v>
       </c>
       <c r="O9" t="n">
-        <v>1338.780579861293</v>
+        <v>1337.587921002191</v>
       </c>
       <c r="P9" t="n">
-        <v>1492.786030368536</v>
+        <v>1492</v>
       </c>
       <c r="Q9" t="n">
-        <v>1346.247111942856</v>
+        <v>1345.738421006376</v>
       </c>
       <c r="R9" t="n">
-        <v>1211.245105910912</v>
+        <v>1210.871311105555</v>
       </c>
       <c r="S9" t="n">
-        <v>1148.125094511552</v>
+        <v>1147.791656100325</v>
       </c>
       <c r="T9" t="n">
-        <v>786.7390049539882</v>
+        <v>1143.281782714996</v>
       </c>
       <c r="U9" t="n">
-        <v>786.5411001076018</v>
+        <v>766.5141059473191</v>
       </c>
       <c r="V9" t="n">
-        <v>771.8838605202077</v>
+        <v>627.5802484838622</v>
       </c>
       <c r="W9" t="n">
-        <v>739.1837161668456</v>
+        <v>594.8801041305001</v>
       </c>
       <c r="X9" t="n">
-        <v>719.1203429896864</v>
+        <v>574.8167309533409</v>
       </c>
       <c r="Y9" t="n">
-        <v>719.1203429896864</v>
+        <v>574.8167309533409</v>
       </c>
     </row>
     <row r="10">
@@ -4929,76 +4929,76 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>785.5324316229015</v>
+        <v>1210.172312640102</v>
       </c>
       <c r="C10" t="n">
-        <v>911.5344374413373</v>
+        <v>1336.174318458537</v>
       </c>
       <c r="D10" t="n">
-        <v>1024.853581566337</v>
+        <v>1336.174318458537</v>
       </c>
       <c r="E10" t="n">
-        <v>1024.853581566337</v>
+        <v>1336.174318458537</v>
       </c>
       <c r="F10" t="n">
-        <v>1024.853581566337</v>
+        <v>1336.174318458537</v>
       </c>
       <c r="G10" t="n">
-        <v>1024.853581566337</v>
+        <v>1385.387095409585</v>
       </c>
       <c r="H10" t="n">
-        <v>1024.853581566337</v>
+        <v>1385.387095409585</v>
       </c>
       <c r="I10" t="n">
-        <v>1251.462556240125</v>
+        <v>1385.387095409585</v>
       </c>
       <c r="J10" t="n">
-        <v>1251.462556240125</v>
+        <v>1385.387095409585</v>
       </c>
       <c r="K10" t="n">
-        <v>1382.983127881912</v>
+        <v>1385.387095409585</v>
       </c>
       <c r="L10" t="n">
-        <v>1386.743548464727</v>
+        <v>1385.387095409585</v>
       </c>
       <c r="M10" t="n">
-        <v>1294.017231267251</v>
+        <v>1292.946305617309</v>
       </c>
       <c r="N10" t="n">
-        <v>1149.534310393385</v>
+        <v>1148.742122945132</v>
       </c>
       <c r="O10" t="n">
-        <v>932.9209073660643</v>
+        <v>932.3861797621564</v>
       </c>
       <c r="P10" t="n">
-        <v>665.0402361121328</v>
+        <v>664.7258098826245</v>
       </c>
       <c r="Q10" t="n">
-        <v>351.4672397226398</v>
+        <v>351.3053387456568</v>
       </c>
       <c r="R10" t="n">
-        <v>29.92</v>
+        <v>29.84</v>
       </c>
       <c r="S10" t="n">
-        <v>70.34367574991083</v>
+        <v>29.84</v>
       </c>
       <c r="T10" t="n">
-        <v>152.0319917867926</v>
+        <v>218.7013496506081</v>
       </c>
       <c r="U10" t="n">
-        <v>152.0319917867926</v>
+        <v>465.2625721249603</v>
       </c>
       <c r="V10" t="n">
-        <v>350.8533846727386</v>
+        <v>664.0839650109062</v>
       </c>
       <c r="W10" t="n">
-        <v>522.744302932416</v>
+        <v>835.9748832705836</v>
       </c>
       <c r="X10" t="n">
-        <v>673.7750939566095</v>
+        <v>987.0056742947771</v>
       </c>
       <c r="Y10" t="n">
-        <v>673.7750939566095</v>
+        <v>1098.414974973809</v>
       </c>
     </row>
     <row r="11">
@@ -5026,7 +5026,7 @@
         <v>126.3276694974847</v>
       </c>
       <c r="H11" t="n">
-        <v>52.27548391298663</v>
+        <v>52.27548391298662</v>
       </c>
       <c r="I11" t="n">
         <v>52.16</v>
@@ -5041,16 +5041,16 @@
         <v>1433.756486655746</v>
       </c>
       <c r="M11" t="n">
-        <v>1433.756486655746</v>
+        <v>1588.64041569551</v>
       </c>
       <c r="N11" t="n">
-        <v>1642.088299889074</v>
+        <v>2234.12041569551</v>
       </c>
       <c r="O11" t="n">
-        <v>1811.935789060974</v>
+        <v>2403.96790486741</v>
       </c>
       <c r="P11" t="n">
-        <v>2015.967884193564</v>
+        <v>2608</v>
       </c>
       <c r="Q11" t="n">
         <v>2608</v>
@@ -5087,22 +5087,22 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>497.6847528895822</v>
+        <v>626.9691772844594</v>
       </c>
       <c r="C12" t="n">
-        <v>456.1696898133001</v>
+        <v>262.221790975854</v>
       </c>
       <c r="D12" t="n">
-        <v>104.7174808257216</v>
+        <v>234.0019052205989</v>
       </c>
       <c r="E12" t="n">
-        <v>81.81637252075936</v>
+        <v>211.1007969156366</v>
       </c>
       <c r="F12" t="n">
-        <v>61.98178430068171</v>
+        <v>191.266208695559</v>
       </c>
       <c r="G12" t="n">
-        <v>56.95991654050543</v>
+        <v>56.95991654050545</v>
       </c>
       <c r="H12" t="n">
         <v>52.16</v>
@@ -5147,7 +5147,7 @@
         <v>1728.68079239476</v>
       </c>
       <c r="V12" t="n">
-        <v>1309.983148766961</v>
+        <v>1633.215471999285</v>
       </c>
       <c r="W12" t="n">
         <v>1196.474923605519</v>
@@ -5156,7 +5156,7 @@
         <v>772.3711463879554</v>
       </c>
       <c r="Y12" t="n">
-        <v>562.8933959666798</v>
+        <v>692.177820361557</v>
       </c>
     </row>
     <row r="13">
@@ -5178,7 +5178,7 @@
         <v>799.6045792539669</v>
       </c>
       <c r="F13" t="n">
-        <v>843.6409298741427</v>
+        <v>844.7655518459023</v>
       </c>
       <c r="G13" t="n">
         <v>918.4848285479131</v>
@@ -5190,7 +5190,7 @@
         <v>1175.567095594213</v>
       </c>
       <c r="J13" t="n">
-        <v>1502.510264279452</v>
+        <v>1502.510264279451</v>
       </c>
       <c r="K13" t="n">
         <v>1607.721180183533</v>
@@ -5208,13 +5208,13 @@
         <v>1113.09861662048</v>
       </c>
       <c r="P13" t="n">
-        <v>820.5867150304003</v>
+        <v>820.5867150304002</v>
       </c>
       <c r="Q13" t="n">
         <v>465.099577226766</v>
       </c>
       <c r="R13" t="n">
-        <v>83.62900582669619</v>
+        <v>83.6290058266962</v>
       </c>
       <c r="S13" t="n">
         <v>52.16</v>
@@ -5223,10 +5223,10 @@
         <v>163.7588283391327</v>
       </c>
       <c r="U13" t="n">
-        <v>331.1447845839768</v>
+        <v>331.1447845839767</v>
       </c>
       <c r="V13" t="n">
-        <v>450.7661774699228</v>
+        <v>450.7661774699227</v>
       </c>
       <c r="W13" t="n">
         <v>543.4570957296002</v>
@@ -5245,76 +5245,76 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>602.4780217251043</v>
+        <v>602.3625378121177</v>
       </c>
       <c r="C14" t="n">
-        <v>471.6956194594539</v>
+        <v>471.5801355464673</v>
       </c>
       <c r="D14" t="n">
-        <v>380.4439469949592</v>
+        <v>380.3284630819725</v>
       </c>
       <c r="E14" t="n">
-        <v>295.2285029476171</v>
+        <v>295.1130190346304</v>
       </c>
       <c r="F14" t="n">
-        <v>209.4814032425546</v>
+        <v>209.365919329568</v>
       </c>
       <c r="G14" t="n">
-        <v>126.3276694974847</v>
+        <v>126.212185584498</v>
       </c>
       <c r="H14" t="n">
-        <v>52.27548391298662</v>
+        <v>52.16</v>
       </c>
       <c r="I14" t="n">
         <v>52.16</v>
       </c>
       <c r="J14" t="n">
-        <v>138.0580950233907</v>
+        <v>564.059784243686</v>
       </c>
       <c r="K14" t="n">
-        <v>318.7922512545465</v>
+        <v>744.7939404748417</v>
       </c>
       <c r="L14" t="n">
-        <v>543.0089536666068</v>
+        <v>969.010642886902</v>
       </c>
       <c r="M14" t="n">
-        <v>555.160395021664</v>
+        <v>1588.64041569551</v>
       </c>
       <c r="N14" t="n">
-        <v>1200.640395021664</v>
+        <v>2234.12041569551</v>
       </c>
       <c r="O14" t="n">
-        <v>1370.487884193564</v>
+        <v>2403.96790486741</v>
       </c>
       <c r="P14" t="n">
-        <v>2015.967884193564</v>
+        <v>2608</v>
       </c>
       <c r="Q14" t="n">
         <v>2608</v>
       </c>
       <c r="R14" t="n">
-        <v>2608</v>
+        <v>2607.884516087013</v>
       </c>
       <c r="S14" t="n">
-        <v>2464.420103585289</v>
+        <v>2464.304619672302</v>
       </c>
       <c r="T14" t="n">
-        <v>2201.396770942356</v>
+        <v>2201.281287029369</v>
       </c>
       <c r="U14" t="n">
-        <v>1868.965980560276</v>
+        <v>1868.850496647289</v>
       </c>
       <c r="V14" t="n">
-        <v>1555.985148068535</v>
+        <v>1555.869664155548</v>
       </c>
       <c r="W14" t="n">
-        <v>1234.39577839081</v>
+        <v>1234.280294477823</v>
       </c>
       <c r="X14" t="n">
-        <v>959.3636233800346</v>
+        <v>959.248139467048</v>
       </c>
       <c r="Y14" t="n">
-        <v>766.1136913771999</v>
+        <v>765.9982074642132</v>
       </c>
     </row>
     <row r="15">
@@ -5324,22 +5324,22 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1349.2511870004</v>
+        <v>174.4524296572589</v>
       </c>
       <c r="C15" t="n">
-        <v>1102.634336277947</v>
+        <v>132.9373665809768</v>
       </c>
       <c r="D15" t="n">
-        <v>751.1821272903682</v>
+        <v>104.7174808257216</v>
       </c>
       <c r="E15" t="n">
-        <v>405.0486957530827</v>
+        <v>81.81637252075936</v>
       </c>
       <c r="F15" t="n">
-        <v>61.98178430068172</v>
+        <v>61.98178430068171</v>
       </c>
       <c r="G15" t="n">
-        <v>56.95991654050545</v>
+        <v>56.95991654050543</v>
       </c>
       <c r="H15" t="n">
         <v>52.16</v>
@@ -5381,19 +5381,19 @@
         <v>1885.467691900864</v>
       </c>
       <c r="U15" t="n">
-        <v>1804.498155646054</v>
+        <v>1481.265832413731</v>
       </c>
       <c r="V15" t="n">
-        <v>1709.032835250579</v>
+        <v>1062.568188785933</v>
       </c>
       <c r="W15" t="n">
-        <v>1595.524610089136</v>
+        <v>625.8276403921664</v>
       </c>
       <c r="X15" t="n">
-        <v>1494.653156103896</v>
+        <v>319.8543987607548</v>
       </c>
       <c r="Y15" t="n">
-        <v>1414.459830077498</v>
+        <v>239.6610727343565</v>
       </c>
     </row>
     <row r="16">
@@ -5403,13 +5403,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>680.0545250991181</v>
+        <v>678.9299031273583</v>
       </c>
       <c r="C16" t="n">
-        <v>726.8565309175539</v>
+        <v>725.7319089457941</v>
       </c>
       <c r="D16" t="n">
-        <v>760.9756750425539</v>
+        <v>759.8510530707941</v>
       </c>
       <c r="E16" t="n">
         <v>798.4799572822071</v>
@@ -5427,7 +5427,7 @@
         <v>1175.567095594213</v>
       </c>
       <c r="J16" t="n">
-        <v>1502.510264279451</v>
+        <v>1502.510264279452</v>
       </c>
       <c r="K16" t="n">
         <v>1607.721180183533</v>
@@ -5445,13 +5445,13 @@
         <v>1113.09861662048</v>
       </c>
       <c r="P16" t="n">
-        <v>820.5867150304002</v>
+        <v>820.5867150304003</v>
       </c>
       <c r="Q16" t="n">
         <v>465.099577226766</v>
       </c>
       <c r="R16" t="n">
-        <v>83.6290058266962</v>
+        <v>83.62900582669619</v>
       </c>
       <c r="S16" t="n">
         <v>52.16</v>
@@ -5460,10 +5460,10 @@
         <v>163.7588283391327</v>
       </c>
       <c r="U16" t="n">
-        <v>331.1447845839767</v>
+        <v>331.1447845839768</v>
       </c>
       <c r="V16" t="n">
-        <v>450.7661774699227</v>
+        <v>450.7661774699228</v>
       </c>
       <c r="W16" t="n">
         <v>543.4570957296002</v>
@@ -5472,7 +5472,7 @@
         <v>615.2878867537937</v>
       </c>
       <c r="Y16" t="n">
-        <v>647.497187432826</v>
+        <v>646.3725654610662</v>
       </c>
     </row>
     <row r="17">
@@ -5500,7 +5500,7 @@
         <v>126.3276694974847</v>
       </c>
       <c r="H17" t="n">
-        <v>52.16</v>
+        <v>52.27548391298662</v>
       </c>
       <c r="I17" t="n">
         <v>52.16</v>
@@ -5509,22 +5509,22 @@
         <v>138.0580950233907</v>
       </c>
       <c r="K17" t="n">
-        <v>783.5380950233907</v>
+        <v>318.7922512545465</v>
       </c>
       <c r="L17" t="n">
-        <v>1007.754797435451</v>
+        <v>543.0089536666068</v>
       </c>
       <c r="M17" t="n">
-        <v>1147.1925108281</v>
+        <v>1188.488953666607</v>
       </c>
       <c r="N17" t="n">
-        <v>1792.6725108281</v>
+        <v>1833.968953666607</v>
       </c>
       <c r="O17" t="n">
-        <v>1962.52</v>
+        <v>2003.816442838507</v>
       </c>
       <c r="P17" t="n">
-        <v>2608</v>
+        <v>2207.848537971096</v>
       </c>
       <c r="Q17" t="n">
         <v>2608</v>
@@ -5561,22 +5561,22 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1026.018863768077</v>
+        <v>497.6847528895822</v>
       </c>
       <c r="C18" t="n">
-        <v>661.2714774594717</v>
+        <v>132.9373665809768</v>
       </c>
       <c r="D18" t="n">
-        <v>309.8192684718933</v>
+        <v>104.7174808257216</v>
       </c>
       <c r="E18" t="n">
         <v>81.81637252075936</v>
       </c>
       <c r="F18" t="n">
-        <v>61.98178430068171</v>
+        <v>61.98178430068172</v>
       </c>
       <c r="G18" t="n">
-        <v>56.95991654050543</v>
+        <v>56.95991654050545</v>
       </c>
       <c r="H18" t="n">
         <v>52.16</v>
@@ -5624,13 +5624,13 @@
         <v>1709.032835250579</v>
       </c>
       <c r="W18" t="n">
-        <v>1272.292286856813</v>
+        <v>1595.524610089136</v>
       </c>
       <c r="X18" t="n">
-        <v>1171.420832871573</v>
+        <v>1289.551368457724</v>
       </c>
       <c r="Y18" t="n">
-        <v>1091.227506845175</v>
+        <v>886.125719199003</v>
       </c>
     </row>
     <row r="19">
@@ -5664,7 +5664,7 @@
         <v>1175.567095594213</v>
       </c>
       <c r="J19" t="n">
-        <v>1502.510264279452</v>
+        <v>1502.510264279451</v>
       </c>
       <c r="K19" t="n">
         <v>1607.721180183533</v>
@@ -5682,28 +5682,28 @@
         <v>1113.09861662048</v>
       </c>
       <c r="P19" t="n">
-        <v>820.5867150304003</v>
+        <v>820.5867150304002</v>
       </c>
       <c r="Q19" t="n">
         <v>465.099577226766</v>
       </c>
       <c r="R19" t="n">
-        <v>83.62900582669619</v>
+        <v>83.6290058266962</v>
       </c>
       <c r="S19" t="n">
         <v>52.16</v>
       </c>
       <c r="T19" t="n">
-        <v>162.634206367373</v>
+        <v>163.7588283391327</v>
       </c>
       <c r="U19" t="n">
-        <v>330.020162612217</v>
+        <v>331.1447845839767</v>
       </c>
       <c r="V19" t="n">
-        <v>449.641555498163</v>
+        <v>450.7661774699227</v>
       </c>
       <c r="W19" t="n">
-        <v>542.3324737578404</v>
+        <v>543.4570957296002</v>
       </c>
       <c r="X19" t="n">
         <v>614.1632647820339</v>
@@ -5743,25 +5743,25 @@
         <v>52.16</v>
       </c>
       <c r="J20" t="n">
-        <v>564.059784243686</v>
+        <v>138.0580950233907</v>
       </c>
       <c r="K20" t="n">
-        <v>1209.539784243686</v>
+        <v>318.7922512545465</v>
       </c>
       <c r="L20" t="n">
-        <v>1433.756486655746</v>
+        <v>964.2722512545465</v>
       </c>
       <c r="M20" t="n">
-        <v>1433.756486655746</v>
+        <v>1609.752251254547</v>
       </c>
       <c r="N20" t="n">
-        <v>1758.48790486741</v>
+        <v>1642.088299889074</v>
       </c>
       <c r="O20" t="n">
-        <v>2403.96790486741</v>
+        <v>1811.935789060974</v>
       </c>
       <c r="P20" t="n">
-        <v>2608</v>
+        <v>2015.967884193564</v>
       </c>
       <c r="Q20" t="n">
         <v>2608</v>
@@ -5798,7 +5798,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1273.433823749106</v>
+        <v>1349.2511870004</v>
       </c>
       <c r="C21" t="n">
         <v>1102.634336277947</v>
@@ -5843,31 +5843,31 @@
         <v>2283.610055368536</v>
       </c>
       <c r="Q21" t="n">
-        <v>2207.792692117242</v>
+        <v>2283.610055368536</v>
       </c>
       <c r="R21" t="n">
-        <v>2026.381118713466</v>
+        <v>2102.198481964761</v>
       </c>
       <c r="S21" t="n">
-        <v>1892.74390700917</v>
+        <v>1968.561270260465</v>
       </c>
       <c r="T21" t="n">
-        <v>1809.65032864957</v>
+        <v>1885.467691900864</v>
       </c>
       <c r="U21" t="n">
-        <v>1728.68079239476</v>
+        <v>1804.498155646054</v>
       </c>
       <c r="V21" t="n">
-        <v>1633.215471999285</v>
+        <v>1709.032835250579</v>
       </c>
       <c r="W21" t="n">
-        <v>1519.707246837842</v>
+        <v>1595.524610089136</v>
       </c>
       <c r="X21" t="n">
-        <v>1418.835792852602</v>
+        <v>1494.653156103896</v>
       </c>
       <c r="Y21" t="n">
-        <v>1338.642466826204</v>
+        <v>1414.459830077498</v>
       </c>
     </row>
     <row r="22">
@@ -5877,25 +5877,25 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>680.0545250991181</v>
+        <v>678.9299031273583</v>
       </c>
       <c r="C22" t="n">
-        <v>726.8565309175539</v>
+        <v>725.7319089457941</v>
       </c>
       <c r="D22" t="n">
-        <v>760.9756750425539</v>
+        <v>759.8510530707941</v>
       </c>
       <c r="E22" t="n">
-        <v>799.6045792539669</v>
+        <v>798.4799572822071</v>
       </c>
       <c r="F22" t="n">
-        <v>844.7655518459023</v>
+        <v>843.6409298741427</v>
       </c>
       <c r="G22" t="n">
-        <v>919.6094505196728</v>
+        <v>918.4848285479131</v>
       </c>
       <c r="H22" t="n">
-        <v>1015.592503547923</v>
+        <v>1014.467881576163</v>
       </c>
       <c r="I22" t="n">
         <v>1175.567095594213</v>
@@ -5931,22 +5931,22 @@
         <v>52.16</v>
       </c>
       <c r="T22" t="n">
-        <v>163.7588283391327</v>
+        <v>162.634206367373</v>
       </c>
       <c r="U22" t="n">
-        <v>331.1447845839767</v>
+        <v>330.020162612217</v>
       </c>
       <c r="V22" t="n">
-        <v>450.7661774699227</v>
+        <v>449.641555498163</v>
       </c>
       <c r="W22" t="n">
-        <v>543.4570957296002</v>
+        <v>542.3324737578404</v>
       </c>
       <c r="X22" t="n">
-        <v>615.2878867537937</v>
+        <v>614.1632647820339</v>
       </c>
       <c r="Y22" t="n">
-        <v>647.497187432826</v>
+        <v>646.3725654610662</v>
       </c>
     </row>
     <row r="23">
@@ -5956,76 +5956,76 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>602.4780217251043</v>
+        <v>602.3625378121178</v>
       </c>
       <c r="C23" t="n">
-        <v>471.6956194594539</v>
+        <v>471.5801355464673</v>
       </c>
       <c r="D23" t="n">
-        <v>380.4439469949592</v>
+        <v>380.3284630819726</v>
       </c>
       <c r="E23" t="n">
-        <v>295.2285029476171</v>
+        <v>295.1130190346305</v>
       </c>
       <c r="F23" t="n">
-        <v>209.4814032425546</v>
+        <v>209.365919329568</v>
       </c>
       <c r="G23" t="n">
-        <v>126.3276694974847</v>
+        <v>126.2121855844981</v>
       </c>
       <c r="H23" t="n">
-        <v>52.27548391298662</v>
+        <v>52.16</v>
       </c>
       <c r="I23" t="n">
         <v>52.16</v>
       </c>
       <c r="J23" t="n">
-        <v>138.0580950233907</v>
+        <v>564.059784243686</v>
       </c>
       <c r="K23" t="n">
-        <v>783.5380950233907</v>
+        <v>744.7939404748417</v>
       </c>
       <c r="L23" t="n">
-        <v>1429.018095023391</v>
+        <v>1390.273940474842</v>
       </c>
       <c r="M23" t="n">
-        <v>1588.64041569551</v>
+        <v>2035.753940474842</v>
       </c>
       <c r="N23" t="n">
-        <v>2234.12041569551</v>
+        <v>2035.753940474842</v>
       </c>
       <c r="O23" t="n">
-        <v>2403.96790486741</v>
+        <v>2205.601429646742</v>
       </c>
       <c r="P23" t="n">
-        <v>2608</v>
+        <v>2409.633524779332</v>
       </c>
       <c r="Q23" t="n">
         <v>2608</v>
       </c>
       <c r="R23" t="n">
-        <v>2608</v>
+        <v>2607.884516087013</v>
       </c>
       <c r="S23" t="n">
-        <v>2464.420103585289</v>
+        <v>2464.304619672302</v>
       </c>
       <c r="T23" t="n">
-        <v>2201.396770942356</v>
+        <v>2201.281287029369</v>
       </c>
       <c r="U23" t="n">
-        <v>1868.965980560276</v>
+        <v>1868.850496647289</v>
       </c>
       <c r="V23" t="n">
-        <v>1555.985148068535</v>
+        <v>1555.869664155548</v>
       </c>
       <c r="W23" t="n">
-        <v>1234.39577839081</v>
+        <v>1234.280294477823</v>
       </c>
       <c r="X23" t="n">
-        <v>959.3636233800346</v>
+        <v>959.248139467048</v>
       </c>
       <c r="Y23" t="n">
-        <v>766.1136913771999</v>
+        <v>765.9982074642132</v>
       </c>
     </row>
     <row r="24">
@@ -6035,19 +6035,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>820.9170761219054</v>
+        <v>1349.2511870004</v>
       </c>
       <c r="C24" t="n">
-        <v>779.4020130456233</v>
+        <v>1102.634336277947</v>
       </c>
       <c r="D24" t="n">
-        <v>427.9498040580449</v>
+        <v>751.1821272903682</v>
       </c>
       <c r="E24" t="n">
         <v>405.0486957530827</v>
       </c>
       <c r="F24" t="n">
-        <v>385.214107533005</v>
+        <v>61.98178430068172</v>
       </c>
       <c r="G24" t="n">
         <v>56.95991654050545</v>
@@ -6080,31 +6080,31 @@
         <v>2283.610055368536</v>
       </c>
       <c r="Q24" t="n">
-        <v>2207.792692117242</v>
+        <v>2283.610055368536</v>
       </c>
       <c r="R24" t="n">
-        <v>1897.096694318589</v>
+        <v>2102.198481964761</v>
       </c>
       <c r="S24" t="n">
-        <v>1440.22715938197</v>
+        <v>1968.561270260465</v>
       </c>
       <c r="T24" t="n">
-        <v>1357.133581022369</v>
+        <v>1885.467691900864</v>
       </c>
       <c r="U24" t="n">
-        <v>1276.164044767559</v>
+        <v>1804.498155646054</v>
       </c>
       <c r="V24" t="n">
-        <v>1180.698724372084</v>
+        <v>1709.032835250579</v>
       </c>
       <c r="W24" t="n">
-        <v>1067.190499210641</v>
+        <v>1595.524610089136</v>
       </c>
       <c r="X24" t="n">
-        <v>966.3190452254014</v>
+        <v>1494.653156103896</v>
       </c>
       <c r="Y24" t="n">
-        <v>886.125719199003</v>
+        <v>1414.459830077498</v>
       </c>
     </row>
     <row r="25">
@@ -6114,28 +6114,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>678.9299031273583</v>
+        <v>680.0545250991181</v>
       </c>
       <c r="C25" t="n">
-        <v>725.7319089457941</v>
+        <v>726.8565309175539</v>
       </c>
       <c r="D25" t="n">
-        <v>759.8510530707941</v>
+        <v>760.9756750425539</v>
       </c>
       <c r="E25" t="n">
-        <v>798.4799572822071</v>
+        <v>799.6045792539669</v>
       </c>
       <c r="F25" t="n">
-        <v>843.6409298741427</v>
+        <v>844.7655518459023</v>
       </c>
       <c r="G25" t="n">
-        <v>918.4848285479131</v>
+        <v>919.6094505196728</v>
       </c>
       <c r="H25" t="n">
-        <v>1014.467881576163</v>
+        <v>1015.592503547923</v>
       </c>
       <c r="I25" t="n">
-        <v>1175.567095594213</v>
+        <v>1176.691717565973</v>
       </c>
       <c r="J25" t="n">
         <v>1502.510264279451</v>
@@ -6168,22 +6168,22 @@
         <v>52.16</v>
       </c>
       <c r="T25" t="n">
-        <v>162.634206367373</v>
+        <v>163.7588283391327</v>
       </c>
       <c r="U25" t="n">
-        <v>330.020162612217</v>
+        <v>331.1447845839767</v>
       </c>
       <c r="V25" t="n">
-        <v>449.641555498163</v>
+        <v>450.7661774699227</v>
       </c>
       <c r="W25" t="n">
-        <v>542.3324737578404</v>
+        <v>543.4570957296002</v>
       </c>
       <c r="X25" t="n">
-        <v>614.1632647820339</v>
+        <v>615.2878867537937</v>
       </c>
       <c r="Y25" t="n">
-        <v>646.3725654610662</v>
+        <v>647.497187432826</v>
       </c>
     </row>
     <row r="26">
@@ -6193,22 +6193,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>602.4780217251043</v>
+        <v>602.3625378121178</v>
       </c>
       <c r="C26" t="n">
-        <v>471.6956194594539</v>
+        <v>471.5801355464673</v>
       </c>
       <c r="D26" t="n">
-        <v>380.4439469949592</v>
+        <v>380.3284630819726</v>
       </c>
       <c r="E26" t="n">
-        <v>295.2285029476171</v>
+        <v>295.1130190346305</v>
       </c>
       <c r="F26" t="n">
-        <v>209.4814032425546</v>
+        <v>209.365919329568</v>
       </c>
       <c r="G26" t="n">
-        <v>126.3276694974847</v>
+        <v>126.2121855844981</v>
       </c>
       <c r="H26" t="n">
         <v>52.16</v>
@@ -6217,52 +6217,52 @@
         <v>52.16</v>
       </c>
       <c r="J26" t="n">
-        <v>138.0580950233907</v>
+        <v>564.059784243686</v>
       </c>
       <c r="K26" t="n">
-        <v>318.7922512545465</v>
+        <v>1209.539784243686</v>
       </c>
       <c r="L26" t="n">
-        <v>964.2722512545465</v>
+        <v>1588.64041569551</v>
       </c>
       <c r="M26" t="n">
-        <v>1200.640395021664</v>
+        <v>2234.12041569551</v>
       </c>
       <c r="N26" t="n">
-        <v>1200.640395021664</v>
+        <v>2234.12041569551</v>
       </c>
       <c r="O26" t="n">
-        <v>1370.487884193564</v>
+        <v>2403.96790486741</v>
       </c>
       <c r="P26" t="n">
-        <v>2015.967884193564</v>
+        <v>2608</v>
       </c>
       <c r="Q26" t="n">
         <v>2608</v>
       </c>
       <c r="R26" t="n">
-        <v>2608</v>
+        <v>2607.884516087013</v>
       </c>
       <c r="S26" t="n">
-        <v>2464.420103585289</v>
+        <v>2464.304619672302</v>
       </c>
       <c r="T26" t="n">
-        <v>2201.396770942356</v>
+        <v>2201.281287029369</v>
       </c>
       <c r="U26" t="n">
-        <v>1868.965980560276</v>
+        <v>1868.850496647289</v>
       </c>
       <c r="V26" t="n">
-        <v>1555.985148068535</v>
+        <v>1555.869664155548</v>
       </c>
       <c r="W26" t="n">
-        <v>1234.39577839081</v>
+        <v>1234.280294477823</v>
       </c>
       <c r="X26" t="n">
-        <v>959.3636233800346</v>
+        <v>959.248139467048</v>
       </c>
       <c r="Y26" t="n">
-        <v>766.1136913771999</v>
+        <v>765.9982074642132</v>
       </c>
     </row>
     <row r="27">
@@ -6272,22 +6272,22 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1349.2511870004</v>
+        <v>379.5542173034306</v>
       </c>
       <c r="C27" t="n">
-        <v>1307.736123924118</v>
+        <v>338.0391542271485</v>
       </c>
       <c r="D27" t="n">
-        <v>956.28391493654</v>
+        <v>309.8192684718933</v>
       </c>
       <c r="E27" t="n">
-        <v>933.3828066315778</v>
+        <v>286.9181601669311</v>
       </c>
       <c r="F27" t="n">
-        <v>590.3158951791768</v>
+        <v>61.98178430068172</v>
       </c>
       <c r="G27" t="n">
-        <v>380.1922397728287</v>
+        <v>56.95991654050545</v>
       </c>
       <c r="H27" t="n">
         <v>52.16</v>
@@ -6332,16 +6332,16 @@
         <v>1804.498155646054</v>
       </c>
       <c r="V27" t="n">
-        <v>1709.032835250579</v>
+        <v>1385.800512018256</v>
       </c>
       <c r="W27" t="n">
-        <v>1595.524610089136</v>
+        <v>949.0599636244897</v>
       </c>
       <c r="X27" t="n">
-        <v>1494.653156103896</v>
+        <v>848.1885096392498</v>
       </c>
       <c r="Y27" t="n">
-        <v>1414.459830077498</v>
+        <v>444.7628603805282</v>
       </c>
     </row>
     <row r="28">
@@ -6366,16 +6366,16 @@
         <v>844.7655518459023</v>
       </c>
       <c r="G28" t="n">
-        <v>918.4848285479131</v>
+        <v>919.6094505196728</v>
       </c>
       <c r="H28" t="n">
-        <v>1014.467881576163</v>
+        <v>1015.592503547923</v>
       </c>
       <c r="I28" t="n">
-        <v>1175.567095594213</v>
+        <v>1176.691717565973</v>
       </c>
       <c r="J28" t="n">
-        <v>1502.510264279452</v>
+        <v>1502.510264279451</v>
       </c>
       <c r="K28" t="n">
         <v>1607.721180183533</v>
@@ -6393,13 +6393,13 @@
         <v>1113.09861662048</v>
       </c>
       <c r="P28" t="n">
-        <v>820.5867150304003</v>
+        <v>820.5867150304002</v>
       </c>
       <c r="Q28" t="n">
         <v>465.099577226766</v>
       </c>
       <c r="R28" t="n">
-        <v>83.62900582669619</v>
+        <v>83.6290058266962</v>
       </c>
       <c r="S28" t="n">
         <v>52.16</v>
@@ -6408,10 +6408,10 @@
         <v>163.7588283391327</v>
       </c>
       <c r="U28" t="n">
-        <v>331.1447845839768</v>
+        <v>331.1447845839767</v>
       </c>
       <c r="V28" t="n">
-        <v>450.7661774699228</v>
+        <v>450.7661774699227</v>
       </c>
       <c r="W28" t="n">
         <v>543.4570957296002</v>
@@ -6430,22 +6430,22 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>602.3625378121177</v>
+        <v>602.3625378121178</v>
       </c>
       <c r="C29" t="n">
         <v>471.5801355464673</v>
       </c>
       <c r="D29" t="n">
-        <v>380.3284630819725</v>
+        <v>380.3284630819726</v>
       </c>
       <c r="E29" t="n">
-        <v>295.1130190346304</v>
+        <v>295.1130190346305</v>
       </c>
       <c r="F29" t="n">
         <v>209.365919329568</v>
       </c>
       <c r="G29" t="n">
-        <v>126.212185584498</v>
+        <v>126.2121855844981</v>
       </c>
       <c r="H29" t="n">
         <v>52.16</v>
@@ -6457,22 +6457,22 @@
         <v>138.0580950233907</v>
       </c>
       <c r="K29" t="n">
-        <v>783.5380950233907</v>
+        <v>318.7922512545465</v>
       </c>
       <c r="L29" t="n">
-        <v>1429.018095023391</v>
+        <v>543.0089536666068</v>
       </c>
       <c r="M29" t="n">
-        <v>2074.498095023391</v>
+        <v>1188.488953666607</v>
       </c>
       <c r="N29" t="n">
-        <v>2234.12041569551</v>
+        <v>1200.640395021664</v>
       </c>
       <c r="O29" t="n">
-        <v>2403.96790486741</v>
+        <v>1370.487884193564</v>
       </c>
       <c r="P29" t="n">
-        <v>2608</v>
+        <v>2015.967884193564</v>
       </c>
       <c r="Q29" t="n">
         <v>2608</v>
@@ -6509,25 +6509,25 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>497.6847528895822</v>
+        <v>1273.433823749106</v>
       </c>
       <c r="C30" t="n">
-        <v>132.9373665809768</v>
+        <v>1231.918760672824</v>
       </c>
       <c r="D30" t="n">
-        <v>104.7174808257216</v>
+        <v>880.4665516852456</v>
       </c>
       <c r="E30" t="n">
-        <v>81.81637252075936</v>
+        <v>534.33312014796</v>
       </c>
       <c r="F30" t="n">
-        <v>61.98178430068171</v>
+        <v>191.2662086955591</v>
       </c>
       <c r="G30" t="n">
-        <v>56.95991654050543</v>
+        <v>186.2443409353828</v>
       </c>
       <c r="H30" t="n">
-        <v>52.16</v>
+        <v>181.4444243948774</v>
       </c>
       <c r="I30" t="n">
         <v>52.16</v>
@@ -6557,28 +6557,28 @@
         <v>2207.792692117242</v>
       </c>
       <c r="R30" t="n">
-        <v>1897.096694318589</v>
+        <v>2026.381118713466</v>
       </c>
       <c r="S30" t="n">
-        <v>1763.459482614293</v>
+        <v>1892.74390700917</v>
       </c>
       <c r="T30" t="n">
-        <v>1680.365904254693</v>
+        <v>1809.65032864957</v>
       </c>
       <c r="U30" t="n">
-        <v>1599.396367999883</v>
+        <v>1728.68079239476</v>
       </c>
       <c r="V30" t="n">
-        <v>1180.698724372084</v>
+        <v>1633.215471999285</v>
       </c>
       <c r="W30" t="n">
-        <v>743.9581759783182</v>
+        <v>1519.707246837842</v>
       </c>
       <c r="X30" t="n">
-        <v>643.0867219930782</v>
+        <v>1418.835792852602</v>
       </c>
       <c r="Y30" t="n">
-        <v>562.8933959666798</v>
+        <v>1338.642466826204</v>
       </c>
     </row>
     <row r="31">
@@ -6588,16 +6588,16 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>680.0545250991181</v>
+        <v>678.9299031273583</v>
       </c>
       <c r="C31" t="n">
-        <v>726.8565309175539</v>
+        <v>725.7319089457941</v>
       </c>
       <c r="D31" t="n">
-        <v>760.9756750425539</v>
+        <v>759.8510530707941</v>
       </c>
       <c r="E31" t="n">
-        <v>799.6045792539669</v>
+        <v>798.4799572822071</v>
       </c>
       <c r="F31" t="n">
         <v>843.6409298741427</v>
@@ -6612,7 +6612,7 @@
         <v>1175.567095594213</v>
       </c>
       <c r="J31" t="n">
-        <v>1502.510264279452</v>
+        <v>1502.510264279451</v>
       </c>
       <c r="K31" t="n">
         <v>1607.721180183533</v>
@@ -6630,34 +6630,34 @@
         <v>1113.09861662048</v>
       </c>
       <c r="P31" t="n">
-        <v>820.5867150304003</v>
+        <v>820.5867150304002</v>
       </c>
       <c r="Q31" t="n">
         <v>465.099577226766</v>
       </c>
       <c r="R31" t="n">
-        <v>83.62900582669619</v>
+        <v>83.6290058266962</v>
       </c>
       <c r="S31" t="n">
         <v>52.16</v>
       </c>
       <c r="T31" t="n">
-        <v>163.7588283391327</v>
+        <v>162.634206367373</v>
       </c>
       <c r="U31" t="n">
-        <v>331.1447845839768</v>
+        <v>330.020162612217</v>
       </c>
       <c r="V31" t="n">
-        <v>450.7661774699228</v>
+        <v>449.641555498163</v>
       </c>
       <c r="W31" t="n">
-        <v>543.4570957296002</v>
+        <v>542.3324737578404</v>
       </c>
       <c r="X31" t="n">
-        <v>615.2878867537937</v>
+        <v>614.1632647820339</v>
       </c>
       <c r="Y31" t="n">
-        <v>647.497187432826</v>
+        <v>646.3725654610662</v>
       </c>
     </row>
     <row r="32">
@@ -6700,16 +6700,16 @@
         <v>964.2722512545465</v>
       </c>
       <c r="M32" t="n">
-        <v>996.6082998890743</v>
+        <v>1609.752251254547</v>
       </c>
       <c r="N32" t="n">
-        <v>1642.088299889074</v>
+        <v>2234.12041569551</v>
       </c>
       <c r="O32" t="n">
-        <v>1811.935789060974</v>
+        <v>2403.96790486741</v>
       </c>
       <c r="P32" t="n">
-        <v>2015.967884193564</v>
+        <v>2608</v>
       </c>
       <c r="Q32" t="n">
         <v>2608</v>
@@ -6746,13 +6746,13 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>950.2015005167827</v>
+        <v>379.5542173034306</v>
       </c>
       <c r="C33" t="n">
-        <v>585.4541142081773</v>
+        <v>132.9373665809768</v>
       </c>
       <c r="D33" t="n">
-        <v>234.0019052205989</v>
+        <v>104.7174808257216</v>
       </c>
       <c r="E33" t="n">
         <v>81.81637252075936</v>
@@ -6791,31 +6791,31 @@
         <v>2283.610055368536</v>
       </c>
       <c r="Q33" t="n">
-        <v>2207.792692117242</v>
+        <v>2283.610055368536</v>
       </c>
       <c r="R33" t="n">
-        <v>2026.381118713466</v>
+        <v>2102.198481964761</v>
       </c>
       <c r="S33" t="n">
-        <v>1892.74390700917</v>
+        <v>1968.561270260465</v>
       </c>
       <c r="T33" t="n">
-        <v>1809.65032864957</v>
+        <v>1885.467691900864</v>
       </c>
       <c r="U33" t="n">
-        <v>1728.68079239476</v>
+        <v>1804.498155646054</v>
       </c>
       <c r="V33" t="n">
-        <v>1633.215471999285</v>
+        <v>1385.800512018256</v>
       </c>
       <c r="W33" t="n">
-        <v>1519.707246837842</v>
+        <v>1272.292286856813</v>
       </c>
       <c r="X33" t="n">
-        <v>1095.603469620279</v>
+        <v>848.1885096392498</v>
       </c>
       <c r="Y33" t="n">
-        <v>1015.41014359388</v>
+        <v>767.9951836128514</v>
       </c>
     </row>
     <row r="34">
@@ -6825,13 +6825,13 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>678.9299031273583</v>
+        <v>680.0545250991181</v>
       </c>
       <c r="C34" t="n">
-        <v>725.7319089457941</v>
+        <v>726.8565309175539</v>
       </c>
       <c r="D34" t="n">
-        <v>759.8510530707941</v>
+        <v>760.9756750425539</v>
       </c>
       <c r="E34" t="n">
         <v>798.4799572822071</v>
@@ -6879,22 +6879,22 @@
         <v>52.16</v>
       </c>
       <c r="T34" t="n">
-        <v>162.634206367373</v>
+        <v>163.7588283391327</v>
       </c>
       <c r="U34" t="n">
-        <v>330.020162612217</v>
+        <v>331.1447845839768</v>
       </c>
       <c r="V34" t="n">
-        <v>449.641555498163</v>
+        <v>450.7661774699228</v>
       </c>
       <c r="W34" t="n">
-        <v>542.3324737578404</v>
+        <v>543.4570957296002</v>
       </c>
       <c r="X34" t="n">
-        <v>614.1632647820339</v>
+        <v>615.2878867537937</v>
       </c>
       <c r="Y34" t="n">
-        <v>646.3725654610662</v>
+        <v>647.497187432826</v>
       </c>
     </row>
     <row r="35">
@@ -6904,76 +6904,76 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>272.3310226606025</v>
+        <v>266.7608500079325</v>
       </c>
       <c r="C35" t="n">
-        <v>194.0738729202046</v>
+        <v>189.5138012776356</v>
       </c>
       <c r="D35" t="n">
-        <v>155.3474529809624</v>
+        <v>151.7974823484944</v>
       </c>
       <c r="E35" t="n">
-        <v>122.6572614588729</v>
+        <v>120.1173918365059</v>
       </c>
       <c r="F35" t="n">
-        <v>89.43541427906291</v>
+        <v>87.90564566679693</v>
       </c>
       <c r="G35" t="n">
-        <v>58.8069330592455</v>
+        <v>58.28726545708054</v>
       </c>
       <c r="H35" t="n">
-        <v>37.28</v>
+        <v>37.77043340793605</v>
       </c>
       <c r="I35" t="n">
-        <v>37.28</v>
+        <v>36.88</v>
       </c>
       <c r="J35" t="n">
-        <v>123.1780950233907</v>
+        <v>493.27</v>
       </c>
       <c r="K35" t="n">
-        <v>303.9122512545465</v>
+        <v>674.0041562311558</v>
       </c>
       <c r="L35" t="n">
-        <v>528.1289536666068</v>
+        <v>898.220858643216</v>
       </c>
       <c r="M35" t="n">
-        <v>989.4689536666067</v>
+        <v>1354.610858643216</v>
       </c>
       <c r="N35" t="n">
-        <v>1450.808953666607</v>
+        <v>1470.12041569551</v>
       </c>
       <c r="O35" t="n">
-        <v>1620.656442838506</v>
+        <v>1639.96790486741</v>
       </c>
       <c r="P35" t="n">
-        <v>1824.688537971096</v>
+        <v>1844</v>
       </c>
       <c r="Q35" t="n">
-        <v>1864</v>
+        <v>1844</v>
       </c>
       <c r="R35" t="n">
-        <v>1864</v>
+        <v>1844</v>
       </c>
       <c r="S35" t="n">
-        <v>1772.945356110541</v>
+        <v>1753.955457120642</v>
       </c>
       <c r="T35" t="n">
-        <v>1562.447275992861</v>
+        <v>1544.467478013063</v>
       </c>
       <c r="U35" t="n">
-        <v>1276.192718869512</v>
+        <v>1265.572041166337</v>
       </c>
       <c r="V35" t="n">
-        <v>1015.737138903023</v>
+        <v>1006.126562209949</v>
       </c>
       <c r="W35" t="n">
-        <v>746.6730217505506</v>
+        <v>738.0725460675776</v>
       </c>
       <c r="X35" t="n">
-        <v>524.1661192650276</v>
+        <v>516.5757445921556</v>
       </c>
       <c r="Y35" t="n">
-        <v>383.4414397874455</v>
+        <v>376.8611661246744</v>
       </c>
     </row>
     <row r="36">
@@ -6983,76 +6983,76 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>745.0942977610064</v>
+        <v>36.88</v>
       </c>
       <c r="C36" t="n">
-        <v>380.3469114524009</v>
+        <v>36.88</v>
       </c>
       <c r="D36" t="n">
-        <v>380.3469114524009</v>
+        <v>36.88</v>
       </c>
       <c r="E36" t="n">
-        <v>380.3469114524009</v>
+        <v>36.88</v>
       </c>
       <c r="F36" t="n">
-        <v>37.28</v>
+        <v>36.88</v>
       </c>
       <c r="G36" t="n">
-        <v>37.28</v>
+        <v>36.88</v>
       </c>
       <c r="H36" t="n">
-        <v>37.28</v>
+        <v>36.88</v>
       </c>
       <c r="I36" t="n">
-        <v>37.28</v>
+        <v>36.88</v>
       </c>
       <c r="J36" t="n">
-        <v>233.0594978168084</v>
+        <v>232.6594978168084</v>
       </c>
       <c r="K36" t="n">
-        <v>545.0092224960974</v>
+        <v>544.6092224960975</v>
       </c>
       <c r="L36" t="n">
-        <v>981.4214968271467</v>
+        <v>935.5464222715058</v>
       </c>
       <c r="M36" t="n">
-        <v>1260.121388570006</v>
+        <v>1214.246314014365</v>
       </c>
       <c r="N36" t="n">
-        <v>1565.244009659669</v>
+        <v>1545.244009659669</v>
       </c>
       <c r="O36" t="n">
-        <v>1606.304284398418</v>
+        <v>1586.304284398418</v>
       </c>
       <c r="P36" t="n">
-        <v>1864</v>
+        <v>1844</v>
       </c>
       <c r="Q36" t="n">
-        <v>1788.182636748706</v>
+        <v>1768.182636748706</v>
       </c>
       <c r="R36" t="n">
-        <v>1453.597148280922</v>
+        <v>1491.847496984563</v>
       </c>
       <c r="S36" t="n">
-        <v>1372.485189101879</v>
+        <v>1411.74563881562</v>
       </c>
       <c r="T36" t="n">
-        <v>1341.916863267531</v>
+        <v>1382.187413991373</v>
       </c>
       <c r="U36" t="n">
-        <v>1313.472579537973</v>
+        <v>1354.753231271917</v>
       </c>
       <c r="V36" t="n">
-        <v>1270.532511667751</v>
+        <v>936.0555876441183</v>
       </c>
       <c r="W36" t="n">
-        <v>1209.54953903156</v>
+        <v>499.3150392503521</v>
       </c>
       <c r="X36" t="n">
-        <v>1161.203337571573</v>
+        <v>75.21126203278885</v>
       </c>
       <c r="Y36" t="n">
-        <v>757.7776883128514</v>
+        <v>48.55328954174406</v>
       </c>
     </row>
     <row r="37">
@@ -7062,76 +7062,76 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>643.5897405151413</v>
+        <v>330.8874293695179</v>
       </c>
       <c r="C37" t="n">
-        <v>741.8717463335771</v>
+        <v>430.1594351879537</v>
       </c>
       <c r="D37" t="n">
-        <v>827.4708904585772</v>
+        <v>516.7485793129538</v>
       </c>
       <c r="E37" t="n">
-        <v>917.5797946699902</v>
+        <v>607.8474835243668</v>
       </c>
       <c r="F37" t="n">
-        <v>971.8607546669496</v>
+        <v>705.4784561163023</v>
       </c>
       <c r="G37" t="n">
-        <v>971.8607546669496</v>
+        <v>832.7923547900727</v>
       </c>
       <c r="H37" t="n">
-        <v>971.8607546669496</v>
+        <v>832.7923547900727</v>
       </c>
       <c r="I37" t="n">
-        <v>1184.439968685</v>
+        <v>1046.361568808123</v>
       </c>
       <c r="J37" t="n">
-        <v>1194.583137370238</v>
+        <v>1056.504737493361</v>
       </c>
       <c r="K37" t="n">
-        <v>1194.583137370238</v>
+        <v>1214.185653397443</v>
       </c>
       <c r="L37" t="n">
-        <v>1238.304989100594</v>
+        <v>1231.844383039988</v>
       </c>
       <c r="M37" t="n">
-        <v>1190.105331946172</v>
+        <v>1184.654826895667</v>
       </c>
       <c r="N37" t="n">
-        <v>1088.417824220178</v>
+        <v>1083.977420179774</v>
       </c>
       <c r="O37" t="n">
-        <v>909.1738532180266</v>
+        <v>905.7435501877235</v>
       </c>
       <c r="P37" t="n">
-        <v>669.1872041531991</v>
+        <v>666.767002132997</v>
       </c>
       <c r="Q37" t="n">
-        <v>366.2253188748173</v>
+        <v>364.8152178647163</v>
       </c>
       <c r="R37" t="n">
-        <v>37.28</v>
+        <v>36.88</v>
       </c>
       <c r="S37" t="n">
-        <v>37.28</v>
+        <v>36.88</v>
       </c>
       <c r="T37" t="n">
-        <v>37.28</v>
+        <v>36.88</v>
       </c>
       <c r="U37" t="n">
-        <v>37.28</v>
+        <v>36.88</v>
       </c>
       <c r="V37" t="n">
-        <v>208.381392885946</v>
+        <v>36.88</v>
       </c>
       <c r="W37" t="n">
-        <v>352.5523111456234</v>
+        <v>36.88</v>
       </c>
       <c r="X37" t="n">
-        <v>475.8631021698169</v>
+        <v>161.1807910241935</v>
       </c>
       <c r="Y37" t="n">
-        <v>559.5524028488492</v>
+        <v>245.8600917032258</v>
       </c>
     </row>
     <row r="38">
@@ -7141,76 +7141,76 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>278.6800419271243</v>
+        <v>265.8704165999965</v>
       </c>
       <c r="C38" t="n">
-        <v>200.4228921867264</v>
+        <v>188.6233678696996</v>
       </c>
       <c r="D38" t="n">
-        <v>161.6964722474841</v>
+        <v>150.9070489405584</v>
       </c>
       <c r="E38" t="n">
-        <v>129.0062807253946</v>
+        <v>119.2269584285698</v>
       </c>
       <c r="F38" t="n">
-        <v>95.78443354558463</v>
+        <v>87.01521225886088</v>
       </c>
       <c r="G38" t="n">
-        <v>65.15595232576723</v>
+        <v>57.39683204914449</v>
       </c>
       <c r="H38" t="n">
-        <v>37.28</v>
+        <v>36.88</v>
       </c>
       <c r="I38" t="n">
-        <v>37.28</v>
+        <v>36.88</v>
       </c>
       <c r="J38" t="n">
-        <v>123.1780950233907</v>
+        <v>122.7780950233907</v>
       </c>
       <c r="K38" t="n">
-        <v>584.5180950233907</v>
+        <v>303.5122512545465</v>
       </c>
       <c r="L38" t="n">
-        <v>808.734797435451</v>
+        <v>527.7289536666068</v>
       </c>
       <c r="M38" t="n">
-        <v>1270.074797435451</v>
+        <v>984.1189536666068</v>
       </c>
       <c r="N38" t="n">
-        <v>1490.12041569551</v>
+        <v>1440.508953666607</v>
       </c>
       <c r="O38" t="n">
-        <v>1659.96790486741</v>
+        <v>1610.356442838507</v>
       </c>
       <c r="P38" t="n">
-        <v>1864</v>
+        <v>1814.388537971096</v>
       </c>
       <c r="Q38" t="n">
-        <v>1864</v>
+        <v>1844</v>
       </c>
       <c r="R38" t="n">
-        <v>1864</v>
+        <v>1843.109566592064</v>
       </c>
       <c r="S38" t="n">
-        <v>1772.945356110541</v>
+        <v>1753.065023712706</v>
       </c>
       <c r="T38" t="n">
-        <v>1562.447275992861</v>
+        <v>1543.577044605127</v>
       </c>
       <c r="U38" t="n">
-        <v>1282.541738136033</v>
+        <v>1264.681607758401</v>
       </c>
       <c r="V38" t="n">
-        <v>1022.086158169545</v>
+        <v>1005.236128802013</v>
       </c>
       <c r="W38" t="n">
-        <v>753.0220410170723</v>
+        <v>737.1821126596417</v>
       </c>
       <c r="X38" t="n">
-        <v>530.5151385315494</v>
+        <v>515.6853111842197</v>
       </c>
       <c r="Y38" t="n">
-        <v>389.7904590539672</v>
+        <v>375.9707327167384</v>
       </c>
     </row>
     <row r="39">
@@ -7220,76 +7220,76 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1060.053311432479</v>
+        <v>1096.146506748585</v>
       </c>
       <c r="C39" t="n">
-        <v>1060.053311432479</v>
+        <v>731.3991204399794</v>
       </c>
       <c r="D39" t="n">
-        <v>708.6011024449006</v>
+        <v>379.9469114524009</v>
       </c>
       <c r="E39" t="n">
-        <v>708.6011024449006</v>
+        <v>379.9469114524009</v>
       </c>
       <c r="F39" t="n">
-        <v>365.5341909924996</v>
+        <v>36.88</v>
       </c>
       <c r="G39" t="n">
-        <v>37.28</v>
+        <v>36.88</v>
       </c>
       <c r="H39" t="n">
-        <v>37.28</v>
+        <v>36.88</v>
       </c>
       <c r="I39" t="n">
-        <v>37.28</v>
+        <v>36.88</v>
       </c>
       <c r="J39" t="n">
-        <v>233.0594978168084</v>
+        <v>232.6594978168084</v>
       </c>
       <c r="K39" t="n">
-        <v>545.0092224960974</v>
+        <v>544.6092224960975</v>
       </c>
       <c r="L39" t="n">
-        <v>981.4214968271467</v>
+        <v>596.8130537319465</v>
       </c>
       <c r="M39" t="n">
-        <v>1260.121388570006</v>
+        <v>875.5129454748057</v>
       </c>
       <c r="N39" t="n">
-        <v>1591.11908421531</v>
+        <v>1206.51064112011</v>
       </c>
       <c r="O39" t="n">
-        <v>1823.263489120562</v>
+        <v>1586.304284398418</v>
       </c>
       <c r="P39" t="n">
-        <v>1864</v>
+        <v>1844</v>
       </c>
       <c r="Q39" t="n">
-        <v>1788.182636748706</v>
+        <v>1844</v>
       </c>
       <c r="R39" t="n">
-        <v>1659.296315870183</v>
+        <v>1716.123780131578</v>
       </c>
       <c r="S39" t="n">
-        <v>1578.184356691139</v>
+        <v>1340.709115261174</v>
       </c>
       <c r="T39" t="n">
-        <v>1547.616030856791</v>
+        <v>1311.150890436928</v>
       </c>
       <c r="U39" t="n">
-        <v>1519.171747127234</v>
+        <v>1283.716707717471</v>
       </c>
       <c r="V39" t="n">
-        <v>1476.231679257011</v>
+        <v>1241.786740857349</v>
       </c>
       <c r="W39" t="n">
-        <v>1415.248706620821</v>
+        <v>1181.81386923126</v>
       </c>
       <c r="X39" t="n">
-        <v>1366.902505160833</v>
+        <v>1134.477768781373</v>
       </c>
       <c r="Y39" t="n">
-        <v>1072.736701984324</v>
+        <v>1107.819796290329</v>
       </c>
     </row>
     <row r="40">
@@ -7299,76 +7299,76 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>220.9960557283878</v>
+        <v>668.9742084978801</v>
       </c>
       <c r="C40" t="n">
-        <v>220.9960557283878</v>
+        <v>768.2462143163159</v>
       </c>
       <c r="D40" t="n">
-        <v>220.9960557283878</v>
+        <v>854.835358441316</v>
       </c>
       <c r="E40" t="n">
-        <v>220.9960557283878</v>
+        <v>945.934262652729</v>
       </c>
       <c r="F40" t="n">
-        <v>220.9960557283878</v>
+        <v>945.934262652729</v>
       </c>
       <c r="G40" t="n">
-        <v>347.3199544021583</v>
+        <v>1073.248161326499</v>
       </c>
       <c r="H40" t="n">
-        <v>446.8898387628681</v>
+        <v>1221.701214354749</v>
       </c>
       <c r="I40" t="n">
-        <v>659.4690527809182</v>
+        <v>1221.701214354749</v>
       </c>
       <c r="J40" t="n">
-        <v>1037.892221466156</v>
+        <v>1231.844383039988</v>
       </c>
       <c r="K40" t="n">
-        <v>1194.583137370238</v>
+        <v>1231.844383039988</v>
       </c>
       <c r="L40" t="n">
-        <v>1238.304989100594</v>
+        <v>1231.844383039988</v>
       </c>
       <c r="M40" t="n">
-        <v>1190.105331946172</v>
+        <v>1184.654826895667</v>
       </c>
       <c r="N40" t="n">
-        <v>1088.417824220178</v>
+        <v>1083.977420179774</v>
       </c>
       <c r="O40" t="n">
-        <v>909.1738532180266</v>
+        <v>905.7435501877235</v>
       </c>
       <c r="P40" t="n">
-        <v>669.1872041531991</v>
+        <v>666.767002132997</v>
       </c>
       <c r="Q40" t="n">
-        <v>366.2253188748173</v>
+        <v>364.8152178647163</v>
       </c>
       <c r="R40" t="n">
-        <v>37.28</v>
+        <v>36.88</v>
       </c>
       <c r="S40" t="n">
-        <v>57.91722738925508</v>
+        <v>36.88</v>
       </c>
       <c r="T40" t="n">
-        <v>220.9960557283878</v>
+        <v>36.88</v>
       </c>
       <c r="U40" t="n">
-        <v>220.9960557283878</v>
+        <v>256.735956244844</v>
       </c>
       <c r="V40" t="n">
-        <v>220.9960557283878</v>
+        <v>314.8331985349769</v>
       </c>
       <c r="W40" t="n">
-        <v>220.9960557283878</v>
+        <v>459.9941167946543</v>
       </c>
       <c r="X40" t="n">
-        <v>220.9960557283878</v>
+        <v>584.2949078188478</v>
       </c>
       <c r="Y40" t="n">
-        <v>220.9960557283878</v>
+        <v>668.9742084978801</v>
       </c>
     </row>
     <row r="41">
@@ -7378,76 +7378,76 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>419.1133600197057</v>
+        <v>167.6624022656504</v>
       </c>
       <c r="C41" t="n">
-        <v>288.3309577540552</v>
+        <v>36.88</v>
       </c>
       <c r="D41" t="n">
-        <v>197.0792852895605</v>
+        <v>36.88</v>
       </c>
       <c r="E41" t="n">
-        <v>197.0792852895605</v>
+        <v>36.88</v>
       </c>
       <c r="F41" t="n">
-        <v>111.332185584498</v>
+        <v>36.88</v>
       </c>
       <c r="G41" t="n">
-        <v>111.332185584498</v>
+        <v>36.88</v>
       </c>
       <c r="H41" t="n">
-        <v>37.28</v>
+        <v>36.88</v>
       </c>
       <c r="I41" t="n">
-        <v>37.28</v>
+        <v>36.88</v>
       </c>
       <c r="J41" t="n">
-        <v>123.1780950233907</v>
+        <v>122.7780950233907</v>
       </c>
       <c r="K41" t="n">
-        <v>303.9122512545465</v>
+        <v>303.5122512545465</v>
       </c>
       <c r="L41" t="n">
-        <v>528.1289536666068</v>
+        <v>527.7289536666068</v>
       </c>
       <c r="M41" t="n">
-        <v>989.4689536666067</v>
+        <v>557.3404156955106</v>
       </c>
       <c r="N41" t="n">
-        <v>1450.808953666607</v>
+        <v>1013.730415695511</v>
       </c>
       <c r="O41" t="n">
-        <v>1620.656442838506</v>
+        <v>1183.57790486741</v>
       </c>
       <c r="P41" t="n">
-        <v>1824.688537971096</v>
+        <v>1387.61</v>
       </c>
       <c r="Q41" t="n">
-        <v>1864</v>
+        <v>1844</v>
       </c>
       <c r="R41" t="n">
-        <v>1864</v>
+        <v>1844</v>
       </c>
       <c r="S41" t="n">
-        <v>1864</v>
+        <v>1700.420103585289</v>
       </c>
       <c r="T41" t="n">
-        <v>1685.601318854877</v>
+        <v>1700.420103585289</v>
       </c>
       <c r="U41" t="n">
-        <v>1685.601318854877</v>
+        <v>1367.989313203209</v>
       </c>
       <c r="V41" t="n">
-        <v>1372.620486363136</v>
+        <v>1121.169528609081</v>
       </c>
       <c r="W41" t="n">
-        <v>1051.031116685411</v>
+        <v>799.5801589313562</v>
       </c>
       <c r="X41" t="n">
-        <v>775.9989616746359</v>
+        <v>524.5480039205806</v>
       </c>
       <c r="Y41" t="n">
-        <v>582.7490296718012</v>
+        <v>331.2980719177459</v>
       </c>
     </row>
     <row r="42">
@@ -7457,76 +7457,76 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>853.8237683805701</v>
+        <v>586.4088083995409</v>
       </c>
       <c r="C42" t="n">
-        <v>812.308705304288</v>
+        <v>221.6614220909356</v>
       </c>
       <c r="D42" t="n">
-        <v>784.0888195490328</v>
+        <v>193.4415363356804</v>
       </c>
       <c r="E42" t="n">
-        <v>437.9553880117473</v>
+        <v>170.5404280307181</v>
       </c>
       <c r="F42" t="n">
-        <v>94.88847655934637</v>
+        <v>150.7058398106405</v>
       </c>
       <c r="G42" t="n">
-        <v>89.86660879917009</v>
+        <v>145.6839720504642</v>
       </c>
       <c r="H42" t="n">
-        <v>37.28</v>
+        <v>36.88</v>
       </c>
       <c r="I42" t="n">
-        <v>37.28</v>
+        <v>36.88</v>
       </c>
       <c r="J42" t="n">
-        <v>233.0594978168084</v>
+        <v>192.5378855434729</v>
       </c>
       <c r="K42" t="n">
-        <v>545.0092224960974</v>
+        <v>504.487610222762</v>
       </c>
       <c r="L42" t="n">
-        <v>597.2130537319465</v>
+        <v>556.6914414586111</v>
       </c>
       <c r="M42" t="n">
-        <v>855.3913332014703</v>
+        <v>835.3913332014703</v>
       </c>
       <c r="N42" t="n">
-        <v>1186.389028846774</v>
+        <v>1166.389028846774</v>
       </c>
       <c r="O42" t="n">
-        <v>1606.304284398418</v>
+        <v>1586.304284398418</v>
       </c>
       <c r="P42" t="n">
-        <v>1864</v>
+        <v>1844</v>
       </c>
       <c r="Q42" t="n">
-        <v>1788.182636748706</v>
+        <v>1844</v>
       </c>
       <c r="R42" t="n">
-        <v>1606.77106334493</v>
+        <v>1662.588426596225</v>
       </c>
       <c r="S42" t="n">
-        <v>1473.133851640634</v>
+        <v>1528.951214891929</v>
       </c>
       <c r="T42" t="n">
-        <v>1390.040273281034</v>
+        <v>1445.857636532328</v>
       </c>
       <c r="U42" t="n">
-        <v>1309.070737026224</v>
+        <v>1041.655777045195</v>
       </c>
       <c r="V42" t="n">
-        <v>1213.605416630749</v>
+        <v>946.1904566497199</v>
       </c>
       <c r="W42" t="n">
-        <v>1100.097191469306</v>
+        <v>832.6822314882769</v>
       </c>
       <c r="X42" t="n">
-        <v>999.225737484066</v>
+        <v>731.8107775030369</v>
       </c>
       <c r="Y42" t="n">
-        <v>919.0324114576676</v>
+        <v>651.6174514766385</v>
       </c>
     </row>
     <row r="43">
@@ -7536,76 +7536,76 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>664.0499031273587</v>
+        <v>663.6499031273586</v>
       </c>
       <c r="C43" t="n">
-        <v>710.8519089457944</v>
+        <v>710.4519089457943</v>
       </c>
       <c r="D43" t="n">
-        <v>744.9710530707945</v>
+        <v>744.5710530707944</v>
       </c>
       <c r="E43" t="n">
-        <v>783.5999572822075</v>
+        <v>783.1999572822074</v>
       </c>
       <c r="F43" t="n">
-        <v>828.760929874143</v>
+        <v>828.3609298741429</v>
       </c>
       <c r="G43" t="n">
-        <v>903.6048285479135</v>
+        <v>903.2048285479134</v>
       </c>
       <c r="H43" t="n">
-        <v>999.5878815761635</v>
+        <v>999.1878815761634</v>
       </c>
       <c r="I43" t="n">
-        <v>1160.687095594214</v>
+        <v>1160.287095594213</v>
       </c>
       <c r="J43" t="n">
-        <v>1487.630264279452</v>
+        <v>1487.230264279452</v>
       </c>
       <c r="K43" t="n">
-        <v>1592.841180183533</v>
+        <v>1592.441180183533</v>
       </c>
       <c r="L43" t="n">
-        <v>1584.925510078805</v>
+        <v>1584.525510078805</v>
       </c>
       <c r="M43" t="n">
-        <v>1484.200600399131</v>
+        <v>1483.80060039913</v>
       </c>
       <c r="N43" t="n">
-        <v>1329.987840147884</v>
+        <v>1329.587840147884</v>
       </c>
       <c r="O43" t="n">
-        <v>1098.21861662048</v>
+        <v>1097.81861662048</v>
       </c>
       <c r="P43" t="n">
-        <v>805.7067150304003</v>
+        <v>805.3067150304004</v>
       </c>
       <c r="Q43" t="n">
-        <v>450.219577226766</v>
+        <v>449.819577226766</v>
       </c>
       <c r="R43" t="n">
-        <v>68.74900582669618</v>
+        <v>68.34900582669619</v>
       </c>
       <c r="S43" t="n">
-        <v>37.28</v>
+        <v>36.88</v>
       </c>
       <c r="T43" t="n">
-        <v>148.8788283391327</v>
+        <v>147.3542063673732</v>
       </c>
       <c r="U43" t="n">
-        <v>315.1401626122174</v>
+        <v>314.7401626122173</v>
       </c>
       <c r="V43" t="n">
-        <v>434.7615554981633</v>
+        <v>434.3615554981632</v>
       </c>
       <c r="W43" t="n">
-        <v>527.4524737578407</v>
+        <v>527.0524737578406</v>
       </c>
       <c r="X43" t="n">
-        <v>599.2832647820343</v>
+        <v>598.8832647820342</v>
       </c>
       <c r="Y43" t="n">
-        <v>631.4925654610665</v>
+        <v>631.0925654610664</v>
       </c>
     </row>
     <row r="44">
@@ -7615,76 +7615,76 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>111.332185584498</v>
+        <v>344.1295187774872</v>
       </c>
       <c r="C44" t="n">
-        <v>111.332185584498</v>
+        <v>213.3471165118368</v>
       </c>
       <c r="D44" t="n">
-        <v>111.332185584498</v>
+        <v>122.0954440473421</v>
       </c>
       <c r="E44" t="n">
-        <v>111.332185584498</v>
+        <v>36.88</v>
       </c>
       <c r="F44" t="n">
-        <v>111.332185584498</v>
+        <v>36.88</v>
       </c>
       <c r="G44" t="n">
-        <v>111.332185584498</v>
+        <v>36.88</v>
       </c>
       <c r="H44" t="n">
-        <v>37.28</v>
+        <v>36.88</v>
       </c>
       <c r="I44" t="n">
-        <v>37.28</v>
+        <v>36.88</v>
       </c>
       <c r="J44" t="n">
-        <v>123.1780950233907</v>
+        <v>122.7780950233907</v>
       </c>
       <c r="K44" t="n">
-        <v>584.5180950233907</v>
+        <v>303.5122512545465</v>
       </c>
       <c r="L44" t="n">
-        <v>808.734797435451</v>
+        <v>527.7289536666068</v>
       </c>
       <c r="M44" t="n">
-        <v>1028.780415695511</v>
+        <v>984.1189536666068</v>
       </c>
       <c r="N44" t="n">
-        <v>1490.12041569551</v>
+        <v>1440.508953666607</v>
       </c>
       <c r="O44" t="n">
-        <v>1659.96790486741</v>
+        <v>1610.356442838507</v>
       </c>
       <c r="P44" t="n">
-        <v>1864</v>
+        <v>1814.388537971096</v>
       </c>
       <c r="Q44" t="n">
-        <v>1864</v>
+        <v>1844</v>
       </c>
       <c r="R44" t="n">
-        <v>1864</v>
+        <v>1844</v>
       </c>
       <c r="S44" t="n">
-        <v>1720.420103585289</v>
+        <v>1844</v>
       </c>
       <c r="T44" t="n">
-        <v>1546.615265149654</v>
+        <v>1610.617477612659</v>
       </c>
       <c r="U44" t="n">
-        <v>1214.184474767574</v>
+        <v>1610.617477612659</v>
       </c>
       <c r="V44" t="n">
-        <v>901.2036422758331</v>
+        <v>1297.636645120918</v>
       </c>
       <c r="W44" t="n">
-        <v>579.6142725981083</v>
+        <v>976.047275443193</v>
       </c>
       <c r="X44" t="n">
-        <v>304.5821175873328</v>
+        <v>701.0151204324175</v>
       </c>
       <c r="Y44" t="n">
-        <v>111.332185584498</v>
+        <v>507.7651884295827</v>
       </c>
     </row>
     <row r="45">
@@ -7694,76 +7694,76 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>606.4088083995412</v>
+        <v>625.3961393790739</v>
       </c>
       <c r="C45" t="n">
-        <v>564.8937453232591</v>
+        <v>583.8810763027918</v>
       </c>
       <c r="D45" t="n">
-        <v>536.6738595680039</v>
+        <v>555.6611905475366</v>
       </c>
       <c r="E45" t="n">
-        <v>513.7727512630416</v>
+        <v>209.5277590102511</v>
       </c>
       <c r="F45" t="n">
-        <v>170.7058398106407</v>
+        <v>189.6931707901735</v>
       </c>
       <c r="G45" t="n">
-        <v>165.6839720504644</v>
+        <v>184.6713030299972</v>
       </c>
       <c r="H45" t="n">
-        <v>160.884055509959</v>
+        <v>36.88</v>
       </c>
       <c r="I45" t="n">
-        <v>37.28</v>
+        <v>36.88</v>
       </c>
       <c r="J45" t="n">
-        <v>233.0594978168084</v>
+        <v>232.6594978168084</v>
       </c>
       <c r="K45" t="n">
-        <v>545.0092224960974</v>
+        <v>544.6092224960975</v>
       </c>
       <c r="L45" t="n">
-        <v>981.4214968271467</v>
+        <v>596.8130537319465</v>
       </c>
       <c r="M45" t="n">
-        <v>1260.121388570006</v>
+        <v>835.3913332014703</v>
       </c>
       <c r="N45" t="n">
-        <v>1565.244009659669</v>
+        <v>1166.389028846774</v>
       </c>
       <c r="O45" t="n">
-        <v>1606.304284398418</v>
+        <v>1586.304284398418</v>
       </c>
       <c r="P45" t="n">
-        <v>1864</v>
+        <v>1844</v>
       </c>
       <c r="Q45" t="n">
-        <v>1864</v>
+        <v>1844</v>
       </c>
       <c r="R45" t="n">
-        <v>1682.588426596225</v>
+        <v>1378.343434343434</v>
       </c>
       <c r="S45" t="n">
-        <v>1548.951214891929</v>
+        <v>1244.706222639138</v>
       </c>
       <c r="T45" t="n">
-        <v>1465.857636532328</v>
+        <v>1161.612644279538</v>
       </c>
       <c r="U45" t="n">
-        <v>1384.888100277518</v>
+        <v>1080.643108024728</v>
       </c>
       <c r="V45" t="n">
-        <v>1289.422779882043</v>
+        <v>985.1777876292529</v>
       </c>
       <c r="W45" t="n">
-        <v>1175.9145547206</v>
+        <v>871.6695624678099</v>
       </c>
       <c r="X45" t="n">
-        <v>1075.04310073536</v>
+        <v>770.7981084825699</v>
       </c>
       <c r="Y45" t="n">
-        <v>994.8497747089621</v>
+        <v>690.6047824561715</v>
       </c>
     </row>
     <row r="46">
@@ -7773,76 +7773,76 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>665.1745250991181</v>
+        <v>663.6499031273581</v>
       </c>
       <c r="C46" t="n">
-        <v>711.9765309175539</v>
+        <v>710.4519089457939</v>
       </c>
       <c r="D46" t="n">
-        <v>746.0956750425539</v>
+        <v>744.5710530707939</v>
       </c>
       <c r="E46" t="n">
-        <v>784.7245792539669</v>
+        <v>783.1999572822069</v>
       </c>
       <c r="F46" t="n">
-        <v>829.8855518459025</v>
+        <v>828.3609298741425</v>
       </c>
       <c r="G46" t="n">
-        <v>904.7294505196729</v>
+        <v>903.2048285479129</v>
       </c>
       <c r="H46" t="n">
-        <v>1000.712503547923</v>
+        <v>999.1878815761629</v>
       </c>
       <c r="I46" t="n">
-        <v>1161.811717565973</v>
+        <v>1160.287095594213</v>
       </c>
       <c r="J46" t="n">
-        <v>1488.754886251211</v>
+        <v>1487.230264279451</v>
       </c>
       <c r="K46" t="n">
-        <v>1592.841180183533</v>
+        <v>1592.441180183533</v>
       </c>
       <c r="L46" t="n">
-        <v>1584.925510078805</v>
+        <v>1584.525510078805</v>
       </c>
       <c r="M46" t="n">
-        <v>1484.20060039913</v>
+        <v>1483.80060039913</v>
       </c>
       <c r="N46" t="n">
-        <v>1329.987840147884</v>
+        <v>1329.587840147884</v>
       </c>
       <c r="O46" t="n">
-        <v>1098.21861662048</v>
+        <v>1097.81861662048</v>
       </c>
       <c r="P46" t="n">
-        <v>805.7067150304003</v>
+        <v>805.3067150304003</v>
       </c>
       <c r="Q46" t="n">
-        <v>450.219577226766</v>
+        <v>449.819577226766</v>
       </c>
       <c r="R46" t="n">
-        <v>68.74900582669619</v>
+        <v>68.3490058266962</v>
       </c>
       <c r="S46" t="n">
-        <v>37.28</v>
+        <v>36.88</v>
       </c>
       <c r="T46" t="n">
-        <v>148.8788283391327</v>
+        <v>147.3542063673728</v>
       </c>
       <c r="U46" t="n">
-        <v>316.2647845839767</v>
+        <v>314.7401626122168</v>
       </c>
       <c r="V46" t="n">
-        <v>435.8861774699227</v>
+        <v>434.3615554981628</v>
       </c>
       <c r="W46" t="n">
-        <v>528.5770957296002</v>
+        <v>527.0524737578402</v>
       </c>
       <c r="X46" t="n">
-        <v>600.4078867537937</v>
+        <v>598.8832647820337</v>
       </c>
       <c r="Y46" t="n">
-        <v>632.617187432826</v>
+        <v>631.092565461066</v>
       </c>
     </row>
   </sheetData>
@@ -7964,28 +7964,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2405037325275146</v>
+        <v>372.8993027275024</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>309.2909949748744</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>846.2608914614127</v>
+        <v>844.554996989051</v>
       </c>
       <c r="N2" t="n">
-        <v>778.0826666125488</v>
+        <v>584.0231602860407</v>
       </c>
       <c r="O2" t="n">
-        <v>1.159015302735668</v>
+        <v>0.4816735941929551</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>376.5921508449956</v>
+        <v>501.1077446289929</v>
       </c>
       <c r="R2" t="n">
         <v>294.54111633436</v>
@@ -8049,7 +8049,7 @@
         <v>295.8802408630135</v>
       </c>
       <c r="L3" t="n">
-        <v>388.0893364597981</v>
+        <v>384.3316744713784</v>
       </c>
       <c r="M3" t="n">
         <v>471.6948204301074</v>
@@ -8201,28 +8201,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2405037325275146</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>321.8400703517588</v>
+        <v>180.5571129839088</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>846.2608914614127</v>
+        <v>844.554996989051</v>
       </c>
       <c r="N5" t="n">
-        <v>639.5838718235262</v>
+        <v>776.3653500296342</v>
       </c>
       <c r="O5" t="n">
-        <v>1.159015302735668</v>
+        <v>0.4816735941929551</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>502.5418702571336</v>
+        <v>501.1077446289929</v>
       </c>
       <c r="R5" t="n">
         <v>294.54111633436</v>
@@ -8286,7 +8286,7 @@
         <v>295.8802408630135</v>
       </c>
       <c r="L6" t="n">
-        <v>388.0893364597981</v>
+        <v>384.3316744713784</v>
       </c>
       <c r="M6" t="n">
         <v>471.6948204301074</v>
@@ -8438,28 +8438,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J8" t="n">
-        <v>235.7417089435049</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>321.8400703517588</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>307.6565929648241</v>
       </c>
       <c r="M8" t="n">
-        <v>846.2608914614127</v>
+        <v>844.554996989051</v>
       </c>
       <c r="N8" t="n">
-        <v>778.0826666125488</v>
+        <v>649.265870048719</v>
       </c>
       <c r="O8" t="n">
-        <v>1.159015302735668</v>
+        <v>0.4816735941929551</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>128.5418702571336</v>
+        <v>501.1077446289929</v>
       </c>
       <c r="R8" t="n">
         <v>294.54111633436</v>
@@ -8529,7 +8529,7 @@
         <v>471.6948204301074</v>
       </c>
       <c r="N9" t="n">
-        <v>485.4085271713503</v>
+        <v>481.6508651829305</v>
       </c>
       <c r="O9" t="n">
         <v>382.6817988009037</v>
@@ -8684,10 +8684,10 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>292.2578010091515</v>
+        <v>448.7062141806306</v>
       </c>
       <c r="N11" t="n">
-        <v>431.6031129524924</v>
+        <v>873.1669379693327</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -8696,7 +8696,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>615.8520732695737</v>
+        <v>17.83983508125425</v>
       </c>
       <c r="R11" t="n">
         <v>294.54111633436</v>
@@ -8912,7 +8912,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -8921,7 +8921,7 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>304.531984196078</v>
+        <v>918.1464604117862</v>
       </c>
       <c r="N14" t="n">
         <v>873.1669379693327</v>
@@ -8930,10 +8930,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>445.9069746135458</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>615.8520732695737</v>
+        <v>17.83983508125425</v>
       </c>
       <c r="R14" t="n">
         <v>294.54111633436</v>
@@ -9152,13 +9152,13 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>469.4402462311558</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>433.1039761532417</v>
+        <v>944.2578010091515</v>
       </c>
       <c r="N17" t="n">
         <v>873.1669379693327</v>
@@ -9167,10 +9167,10 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>445.9069746135458</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>17.83983508125425</v>
+        <v>422.0332310700458</v>
       </c>
       <c r="R17" t="n">
         <v>294.54111633436</v>
@@ -9386,28 +9386,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J20" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>469.4402462311558</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>425.5184824120604</v>
       </c>
       <c r="M20" t="n">
-        <v>292.2578010091515</v>
+        <v>944.2578010091515</v>
       </c>
       <c r="N20" t="n">
-        <v>549.1784715164681</v>
+        <v>253.8296133577446</v>
       </c>
       <c r="O20" t="n">
-        <v>480.4368796243436</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>17.83983508125425</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R20" t="n">
         <v>294.54111633436</v>
@@ -9623,19 +9623,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K23" t="n">
-        <v>469.4402462311558</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>425.5184824120603</v>
+        <v>425.5184824120604</v>
       </c>
       <c r="M23" t="n">
-        <v>453.492468354727</v>
+        <v>944.2578010091515</v>
       </c>
       <c r="N23" t="n">
-        <v>873.1669379693327</v>
+        <v>221.1669379693327</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -9644,7 +9644,7 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>17.83983508125425</v>
+        <v>218.2100120718282</v>
       </c>
       <c r="R23" t="n">
         <v>294.54111633436</v>
@@ -9860,16 +9860,16 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>469.4402462311558</v>
       </c>
       <c r="L26" t="n">
-        <v>425.5184824120604</v>
+        <v>156.4484131714792</v>
       </c>
       <c r="M26" t="n">
-        <v>531.0135017840175</v>
+        <v>944.2578010091515</v>
       </c>
       <c r="N26" t="n">
         <v>221.1669379693327</v>
@@ -9878,10 +9878,10 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>445.9069746135458</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>615.8520732695737</v>
+        <v>17.83983508125425</v>
       </c>
       <c r="R26" t="n">
         <v>294.54111633436</v>
@@ -10100,25 +10100,25 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>469.4402462311558</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>425.5184824120603</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
         <v>944.2578010091515</v>
       </c>
       <c r="N29" t="n">
-        <v>382.4016053149082</v>
+        <v>233.4411211562591</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>445.9069746135458</v>
       </c>
       <c r="Q29" t="n">
-        <v>17.83983508125425</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R29" t="n">
         <v>294.54111633436</v>
@@ -10343,10 +10343,10 @@
         <v>425.5184824120604</v>
       </c>
       <c r="M32" t="n">
-        <v>324.9204763975632</v>
+        <v>944.2578010091515</v>
       </c>
       <c r="N32" t="n">
-        <v>873.1669379693327</v>
+        <v>851.841851546064</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -10355,7 +10355,7 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>615.8520732695737</v>
+        <v>17.83983508125425</v>
       </c>
       <c r="R32" t="n">
         <v>294.54111633436</v>
@@ -10571,7 +10571,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>374.2342474511205</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -10580,10 +10580,10 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>758.2578010091515</v>
+        <v>753.2578010091515</v>
       </c>
       <c r="N35" t="n">
-        <v>687.1669379693327</v>
+        <v>337.8432582241756</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -10592,7 +10592,7 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>57.54838258519754</v>
+        <v>17.83983508125425</v>
       </c>
       <c r="R35" t="n">
         <v>294.54111633436</v>
@@ -10656,13 +10656,13 @@
         <v>295.8802408630135</v>
       </c>
       <c r="L36" t="n">
-        <v>388.0893364597981</v>
+        <v>342.1549177167265</v>
       </c>
       <c r="M36" t="n">
         <v>471.6948204301074</v>
       </c>
       <c r="N36" t="n">
-        <v>459.2720882262584</v>
+        <v>485.4085271713503</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -10811,16 +10811,16 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>283.4402462311558</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>758.2578010091515</v>
+        <v>753.2578010091515</v>
       </c>
       <c r="N38" t="n">
-        <v>443.43523924212</v>
+        <v>682.1669379693327</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -10829,7 +10829,7 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>17.83983508125425</v>
+        <v>47.75040278721747</v>
       </c>
       <c r="R38" t="n">
         <v>294.54111633436</v>
@@ -10893,7 +10893,7 @@
         <v>295.8802408630135</v>
       </c>
       <c r="L39" t="n">
-        <v>388.0893364597981</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
         <v>471.6948204301074</v>
@@ -10902,10 +10902,10 @@
         <v>485.4085271713503</v>
       </c>
       <c r="O39" t="n">
-        <v>193.0142728954576</v>
+        <v>342.1549177167263</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>219.1507118405495</v>
       </c>
       <c r="Q39" t="n">
         <v>17.27519534353338</v>
@@ -11054,10 +11054,10 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>758.2578010091515</v>
+        <v>322.1683687151149</v>
       </c>
       <c r="N41" t="n">
-        <v>687.1669379693327</v>
+        <v>682.1669379693327</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -11066,7 +11066,7 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>57.54838258519754</v>
+        <v>478.8398350812543</v>
       </c>
       <c r="R41" t="n">
         <v>294.54111633436</v>
@@ -11124,7 +11124,7 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J42" t="n">
-        <v>227.4647419277884</v>
+        <v>186.9378608436112</v>
       </c>
       <c r="K42" t="n">
         <v>295.8802408630135</v>
@@ -11133,7 +11133,7 @@
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>450.96591914391</v>
+        <v>471.6948204301074</v>
       </c>
       <c r="N42" t="n">
         <v>485.4085271713503</v>
@@ -11285,16 +11285,16 @@
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>283.4402462311558</v>
+        <v>0</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>514.5261022819388</v>
+        <v>753.2578010091515</v>
       </c>
       <c r="N44" t="n">
-        <v>687.1669379693327</v>
+        <v>682.1669379693327</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -11303,7 +11303,7 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>17.83983508125425</v>
+        <v>47.75040278721747</v>
       </c>
       <c r="R44" t="n">
         <v>294.54111633436</v>
@@ -11367,16 +11367,16 @@
         <v>295.8802408630135</v>
       </c>
       <c r="L45" t="n">
-        <v>388.0893364597981</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>471.6948204301074</v>
+        <v>431.1679393459302</v>
       </c>
       <c r="N45" t="n">
-        <v>459.2720882262584</v>
+        <v>485.4085271713503</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>382.6817988009037</v>
       </c>
       <c r="P45" t="n">
         <v>219.1507118405495</v>
@@ -22512,7 +22512,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.968558980384842e-13</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -22563,7 +22563,7 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1.927393539208538</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
@@ -22767,7 +22767,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1.927393539208508</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -23037,7 +23037,7 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1.927393539202001</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -25599,19 +25599,19 @@
         <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>90.33915573984979</v>
       </c>
       <c r="E41" t="n">
         <v>84.36328960686865</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>84.88962870801186</v>
       </c>
       <c r="G41" t="n">
         <v>82.32219640761923</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>73.31166372865304</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -25644,16 +25644,16 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>142.1440974505641</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>83.77840498283231</v>
+        <v>260.3930993165036</v>
       </c>
       <c r="U41" t="n">
-        <v>329.1064824782589</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>65.49943741863706</v>
       </c>
       <c r="W41" t="n">
         <v>0</v>
@@ -25830,16 +25830,16 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>161.9993129555745</v>
+        <v>0</v>
       </c>
       <c r="C44" t="n">
-        <v>129.4745782429939</v>
+        <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>90.33915573984979</v>
+        <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>84.36328960686865</v>
+        <v>0</v>
       </c>
       <c r="F44" t="n">
         <v>84.88962870801186</v>
@@ -25848,7 +25848,7 @@
         <v>82.32219640761923</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>73.31166372865306</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -25881,13 +25881,13 @@
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>142.1440974505641</v>
       </c>
       <c r="T44" t="n">
-        <v>88.32630926522515</v>
+        <v>29.34440215303607</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>329.106482478259</v>
       </c>
       <c r="V44" t="n">
         <v>0</v>
@@ -26086,7 +26086,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1074129.012709067</v>
+        <v>1073757.917189626</v>
       </c>
     </row>
     <row r="3">
@@ -26094,7 +26094,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2050146.218966827</v>
+        <v>2049656.222539952</v>
       </c>
     </row>
     <row r="4">
@@ -26102,7 +26102,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3026163.425224589</v>
+        <v>3025554.52789028</v>
       </c>
     </row>
     <row r="5">
@@ -26110,7 +26110,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4000457.253603563</v>
+        <v>4000100.550881262</v>
       </c>
     </row>
     <row r="6">
@@ -26118,7 +26118,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>4976474.459861325</v>
+        <v>4976117.757139024</v>
       </c>
     </row>
     <row r="7">
@@ -26126,7 +26126,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5952491.666119086</v>
+        <v>5952134.963396785</v>
       </c>
     </row>
     <row r="8">
@@ -26134,7 +26134,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6928508.872376842</v>
+        <v>6928152.169654542</v>
       </c>
     </row>
     <row r="9">
@@ -26142,7 +26142,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7904526.0786346</v>
+        <v>7904169.375912299</v>
       </c>
     </row>
     <row r="10">
@@ -26150,7 +26150,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8880543.284892356</v>
+        <v>8880186.582170056</v>
       </c>
     </row>
     <row r="11">
@@ -26158,7 +26158,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9856560.491150115</v>
+        <v>9856203.788427813</v>
       </c>
     </row>
     <row r="12">
@@ -26166,7 +26166,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>10832577.69740788</v>
+        <v>10832220.99468558</v>
       </c>
     </row>
     <row r="13">
@@ -26174,7 +26174,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11785807.4774997</v>
+        <v>11784726.16871679</v>
       </c>
     </row>
     <row r="14">
@@ -26182,7 +26182,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>12761824.68375747</v>
+        <v>12760743.37497456</v>
       </c>
     </row>
     <row r="15">
@@ -26190,7 +26190,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13693319.3243038</v>
+        <v>13691040.9827609</v>
       </c>
     </row>
     <row r="16">
@@ -26198,7 +26198,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14624813.96485014</v>
+        <v>14621338.59054723</v>
       </c>
     </row>
   </sheetData>
@@ -26269,13 +26269,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1227892.614324279</v>
+        <v>1227743.029311702</v>
       </c>
       <c r="C2" t="n">
-        <v>1227892.61432428</v>
+        <v>1227743.029311702</v>
       </c>
       <c r="D2" t="n">
-        <v>1227892.61432428</v>
+        <v>1227743.029311702</v>
       </c>
       <c r="E2" t="n">
         <v>1227892.61432428</v>
@@ -26296,10 +26296,10 @@
         <v>1227892.61432428</v>
       </c>
       <c r="K2" t="n">
+        <v>1227892.61432428</v>
+      </c>
+      <c r="L2" t="n">
         <v>1227892.614324281</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1227892.61432428</v>
       </c>
       <c r="M2" t="n">
         <v>1227892.61432428</v>
@@ -26308,10 +26308,10 @@
         <v>1227892.61432428</v>
       </c>
       <c r="O2" t="n">
-        <v>1171880.354235702</v>
+        <v>1170374.409795702</v>
       </c>
       <c r="P2" t="n">
-        <v>1171880.354235702</v>
+        <v>1170374.409795702</v>
       </c>
     </row>
     <row r="3">
@@ -26321,7 +26321,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>231098</v>
+        <v>231721</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -26330,7 +26330,7 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>602481</v>
+        <v>601858</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -26345,7 +26345,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>387648</v>
+        <v>387296</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -26354,13 +26354,13 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>73984</v>
+        <v>73376</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>214400</v>
+        <v>213600</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>602419.1762101186</v>
+        <v>601999.0545970547</v>
       </c>
       <c r="C4" t="n">
-        <v>600410.2540226299</v>
+        <v>599989.9744270389</v>
       </c>
       <c r="D4" t="n">
-        <v>598398.6066068059</v>
+        <v>597978.1688143748</v>
       </c>
       <c r="E4" t="n">
-        <v>511269.9826128766</v>
+        <v>511074.1690089637</v>
       </c>
       <c r="F4" t="n">
-        <v>509593.2914637274</v>
+        <v>509397.4778598144</v>
       </c>
       <c r="G4" t="n">
-        <v>507914.2865436998</v>
+        <v>507718.4729397869</v>
       </c>
       <c r="H4" t="n">
-        <v>506232.9512606538</v>
+        <v>506037.1376567409</v>
       </c>
       <c r="I4" t="n">
-        <v>504549.2688062633</v>
+        <v>504353.4552023503</v>
       </c>
       <c r="J4" t="n">
-        <v>502863.2221519142</v>
+        <v>502667.4085480013</v>
       </c>
       <c r="K4" t="n">
-        <v>501174.7940445097</v>
+        <v>500978.9804405967</v>
       </c>
       <c r="L4" t="n">
-        <v>499483.967002161</v>
+        <v>499288.1533982481</v>
       </c>
       <c r="M4" t="n">
-        <v>514822.4743070322</v>
+        <v>515217.5761675969</v>
       </c>
       <c r="N4" t="n">
-        <v>512953.4824301332</v>
+        <v>513343.0673097741</v>
       </c>
       <c r="O4" t="n">
-        <v>480003.8779493122</v>
+        <v>479551.3425759952</v>
       </c>
       <c r="P4" t="n">
-        <v>478263.4973813285</v>
+        <v>477809.0366852888</v>
       </c>
     </row>
     <row r="5">
@@ -26425,13 +26425,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>58590.39999999999</v>
+        <v>58551.39999999999</v>
       </c>
       <c r="C5" t="n">
-        <v>58590.39999999999</v>
+        <v>58551.39999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>58590.39999999999</v>
+        <v>58551.39999999999</v>
       </c>
       <c r="E5" t="n">
         <v>74326.28</v>
@@ -26458,16 +26458,16 @@
         <v>74326.28</v>
       </c>
       <c r="M5" t="n">
-        <v>67389.068</v>
+        <v>67169.137</v>
       </c>
       <c r="N5" t="n">
-        <v>67389.068</v>
+        <v>67169.137</v>
       </c>
       <c r="O5" t="n">
-        <v>63017.48</v>
+        <v>62713.48</v>
       </c>
       <c r="P5" t="n">
-        <v>63017.48</v>
+        <v>62713.48</v>
       </c>
     </row>
     <row r="6">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>335785.0381141608</v>
+        <v>335471.5747146474</v>
       </c>
       <c r="C6" t="n">
-        <v>568891.9603016501</v>
+        <v>569201.6548846629</v>
       </c>
       <c r="D6" t="n">
-        <v>570903.6077174739</v>
+        <v>571213.460497327</v>
       </c>
       <c r="E6" t="n">
-        <v>39815.35171140372</v>
+        <v>40634.16531531609</v>
       </c>
       <c r="F6" t="n">
-        <v>643973.0428605524</v>
+        <v>644168.8564644658</v>
       </c>
       <c r="G6" t="n">
-        <v>645652.0477805805</v>
+        <v>645847.8613844932</v>
       </c>
       <c r="H6" t="n">
-        <v>647333.3830636262</v>
+        <v>647529.196667539</v>
       </c>
       <c r="I6" t="n">
-        <v>649017.0655180165</v>
+        <v>649212.8791219294</v>
       </c>
       <c r="J6" t="n">
-        <v>263055.1121723661</v>
+        <v>263602.9257762787</v>
       </c>
       <c r="K6" t="n">
-        <v>652391.5402797707</v>
+        <v>652587.3538836829</v>
       </c>
       <c r="L6" t="n">
-        <v>654082.3673221192</v>
+        <v>654278.1809260324</v>
       </c>
       <c r="M6" t="n">
-        <v>571697.0720172481</v>
+        <v>572129.9011566828</v>
       </c>
       <c r="N6" t="n">
-        <v>647550.0638941465</v>
+        <v>647380.4100145061</v>
       </c>
       <c r="O6" t="n">
-        <v>414458.9962863896</v>
+        <v>414509.5872197066</v>
       </c>
       <c r="P6" t="n">
-        <v>630599.376854374</v>
+        <v>629851.8931104132</v>
       </c>
     </row>
   </sheetData>
@@ -26788,10 +26788,10 @@
         <v>320</v>
       </c>
       <c r="M2" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="N2" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="O2" t="n">
         <v>320</v>
@@ -26807,13 +26807,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C3" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D3" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E3" t="n">
         <v>357</v>
@@ -26859,13 +26859,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C4" t="n">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="D4" t="n">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="E4" t="n">
         <v>652</v>
@@ -26892,16 +26892,16 @@
         <v>652</v>
       </c>
       <c r="M4" t="n">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="N4" t="n">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="O4" t="n">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="P4" t="n">
-        <v>466</v>
+        <v>461</v>
       </c>
     </row>
   </sheetData>
@@ -26972,10 +26972,10 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" t="n">
         <v>-0</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -26987,7 +26987,7 @@
         <v>-0</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H2" t="n">
         <v>-0</v>
@@ -27002,16 +27002,16 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M2" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="P2" t="n">
         <v>-0</v>
@@ -27024,7 +27024,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C3" t="n">
         <v>-0</v>
@@ -27033,7 +27033,7 @@
         <v>-0</v>
       </c>
       <c r="E3" t="n">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F3" t="n">
         <v>-0</v>
@@ -27076,7 +27076,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C4" t="n">
         <v>-0</v>
@@ -27085,7 +27085,7 @@
         <v>-0</v>
       </c>
       <c r="E4" t="n">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F4" t="n">
         <v>-0</v>
@@ -27100,7 +27100,7 @@
         <v>-0</v>
       </c>
       <c r="J4" t="n">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="K4" t="n">
         <v>-0</v>
@@ -27109,7 +27109,7 @@
         <v>-0</v>
       </c>
       <c r="M4" t="n">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="N4" t="n">
         <v>-0</v>
@@ -27317,7 +27317,7 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -27326,7 +27326,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -27454,7 +27454,7 @@
         <v>400</v>
       </c>
       <c r="I2" t="n">
-        <v>134.2726973711268</v>
+        <v>134.1177124465037</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -27481,10 +27481,10 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>225.120779732817</v>
+        <v>224.8682520946261</v>
       </c>
       <c r="S2" t="n">
-        <v>398.2013121321728</v>
+        <v>400</v>
       </c>
       <c r="T2" t="n">
         <v>400</v>
@@ -27512,7 +27512,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>27.79652998074107</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C3" t="n">
         <v>361.0999124455193</v>
@@ -27527,13 +27527,13 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G3" t="n">
-        <v>325.5201396486123</v>
+        <v>325.517988705216</v>
       </c>
       <c r="H3" t="n">
-        <v>330.0491815260438</v>
+        <v>330.0284079411381</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>101.2549670565235</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -27557,10 +27557,10 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>145.073529241423</v>
+        <v>144.7989632036872</v>
       </c>
       <c r="R3" t="n">
-        <v>159.6519859716246</v>
+        <v>400</v>
       </c>
       <c r="S3" t="n">
         <v>400</v>
@@ -27569,19 +27569,19 @@
         <v>400</v>
       </c>
       <c r="U3" t="n">
-        <v>400</v>
+        <v>27.19578428848864</v>
       </c>
       <c r="V3" t="n">
-        <v>400</v>
+        <v>41.51066719152016</v>
       </c>
       <c r="W3" t="n">
-        <v>400</v>
+        <v>59.37314290982852</v>
       </c>
       <c r="X3" t="n">
         <v>400</v>
       </c>
       <c r="Y3" t="n">
-        <v>25.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="4">
@@ -27591,13 +27591,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>400</v>
+        <v>287.1138003370787</v>
       </c>
       <c r="C4" t="n">
-        <v>400</v>
+        <v>272.7252466480447</v>
       </c>
       <c r="D4" t="n">
-        <v>400</v>
+        <v>285.5362180555555</v>
       </c>
       <c r="E4" t="n">
         <v>400</v>
@@ -27609,19 +27609,19 @@
         <v>400</v>
       </c>
       <c r="H4" t="n">
+        <v>227.1197490524383</v>
+      </c>
+      <c r="I4" t="n">
         <v>400</v>
       </c>
-      <c r="I4" t="n">
-        <v>171.1020457840527</v>
-      </c>
       <c r="J4" t="n">
-        <v>22.26478490148153</v>
+        <v>121.9960259200954</v>
       </c>
       <c r="K4" t="n">
-        <v>400</v>
+        <v>266.941429538848</v>
       </c>
       <c r="L4" t="n">
-        <v>400</v>
+        <v>395.9334970102382</v>
       </c>
       <c r="M4" t="n">
         <v>400</v>
@@ -27642,25 +27642,25 @@
         <v>400</v>
       </c>
       <c r="S4" t="n">
-        <v>359.1680042930194</v>
+        <v>359.1365780635112</v>
       </c>
       <c r="T4" t="n">
-        <v>209.2386648669134</v>
+        <v>400</v>
       </c>
       <c r="U4" t="n">
-        <v>150.9483584875727</v>
+        <v>400</v>
       </c>
       <c r="V4" t="n">
-        <v>199.1703102162162</v>
+        <v>400</v>
       </c>
       <c r="W4" t="n">
-        <v>267.8979241578017</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X4" t="n">
-        <v>400</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y4" t="n">
-        <v>400</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="5">
@@ -27685,13 +27685,13 @@
         <v>400</v>
       </c>
       <c r="G5" t="n">
-        <v>398.2013121321734</v>
+        <v>400</v>
       </c>
       <c r="H5" t="n">
         <v>400</v>
       </c>
       <c r="I5" t="n">
-        <v>134.2726973711268</v>
+        <v>134.1177124465037</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -27718,7 +27718,7 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>225.120779732817</v>
+        <v>224.8682520946261</v>
       </c>
       <c r="S5" t="n">
         <v>400</v>
@@ -27749,28 +27749,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D6" t="n">
         <v>347.9376868977026</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F6" t="n">
         <v>339.6362423378769</v>
       </c>
       <c r="G6" t="n">
-        <v>325.5201396486123</v>
+        <v>325.517988705216</v>
       </c>
       <c r="H6" t="n">
-        <v>330.0491815260438</v>
+        <v>330.0284079411381</v>
       </c>
       <c r="I6" t="n">
-        <v>209.5726123064429</v>
+        <v>209.4985557026693</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -27794,13 +27794,13 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>145.073529241423</v>
+        <v>31.39908659216251</v>
       </c>
       <c r="R6" t="n">
         <v>400</v>
       </c>
       <c r="S6" t="n">
-        <v>297.0913566670282</v>
+        <v>400</v>
       </c>
       <c r="T6" t="n">
         <v>400</v>
@@ -27812,13 +27812,13 @@
         <v>400</v>
       </c>
       <c r="W6" t="n">
-        <v>400</v>
+        <v>59.37314290982852</v>
       </c>
       <c r="X6" t="n">
-        <v>400</v>
+        <v>46.86273944538755</v>
       </c>
       <c r="Y6" t="n">
-        <v>399.3913927661343</v>
+        <v>26.39139276613435</v>
       </c>
     </row>
     <row r="7">
@@ -27834,31 +27834,31 @@
         <v>400</v>
       </c>
       <c r="D7" t="n">
-        <v>336.5432435627182</v>
+        <v>400</v>
       </c>
       <c r="E7" t="n">
-        <v>280.9809048369565</v>
+        <v>400</v>
       </c>
       <c r="F7" t="n">
-        <v>274.3828559677419</v>
+        <v>400</v>
       </c>
       <c r="G7" t="n">
-        <v>244.8599384153005</v>
+        <v>244.858135136612</v>
       </c>
       <c r="H7" t="n">
-        <v>227.1357818393235</v>
+        <v>400</v>
       </c>
       <c r="I7" t="n">
-        <v>171.1020457840527</v>
+        <v>400</v>
       </c>
       <c r="J7" t="n">
-        <v>22.26478490148153</v>
+        <v>22.13729309820286</v>
       </c>
       <c r="K7" t="n">
-        <v>267.1509377355693</v>
+        <v>266.941429538848</v>
       </c>
       <c r="L7" t="n">
-        <v>396.2015953708939</v>
+        <v>395.9334970102382</v>
       </c>
       <c r="M7" t="n">
         <v>400</v>
@@ -27879,19 +27879,19 @@
         <v>400</v>
       </c>
       <c r="S7" t="n">
-        <v>359.1680042930194</v>
+        <v>359.1365780635112</v>
       </c>
       <c r="T7" t="n">
-        <v>400</v>
+        <v>209.2309599488807</v>
       </c>
       <c r="U7" t="n">
-        <v>400</v>
+        <v>150.9482601269169</v>
       </c>
       <c r="V7" t="n">
-        <v>400</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W7" t="n">
-        <v>400</v>
+        <v>329.4278896046637</v>
       </c>
       <c r="X7" t="n">
         <v>400</v>
@@ -27925,10 +27925,10 @@
         <v>400</v>
       </c>
       <c r="H8" t="n">
-        <v>398.2013121321734</v>
+        <v>400</v>
       </c>
       <c r="I8" t="n">
-        <v>134.2726973711268</v>
+        <v>134.1177124465037</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -27955,7 +27955,7 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>225.120779732817</v>
+        <v>224.8682520946328</v>
       </c>
       <c r="S8" t="n">
         <v>400</v>
@@ -27995,19 +27995,19 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G9" t="n">
-        <v>325.5201396486123</v>
+        <v>325.517988705216</v>
       </c>
       <c r="H9" t="n">
-        <v>330.0491815260438</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>209.5726123064429</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -28040,13 +28040,13 @@
         <v>400</v>
       </c>
       <c r="T9" t="n">
-        <v>46.70121580080865</v>
+        <v>400</v>
       </c>
       <c r="U9" t="n">
-        <v>400</v>
+        <v>27.19578428848864</v>
       </c>
       <c r="V9" t="n">
-        <v>400</v>
+        <v>276.9661483026978</v>
       </c>
       <c r="W9" t="n">
         <v>400</v>
@@ -28071,7 +28071,7 @@
         <v>400</v>
       </c>
       <c r="D10" t="n">
-        <v>400</v>
+        <v>285.5362180555555</v>
       </c>
       <c r="E10" t="n">
         <v>280.9809048369565</v>
@@ -28080,22 +28080,22 @@
         <v>274.3828559677419</v>
       </c>
       <c r="G10" t="n">
-        <v>244.8599384153005</v>
+        <v>294.5680108447413</v>
       </c>
       <c r="H10" t="n">
-        <v>227.1357818393235</v>
+        <v>227.1197490524383</v>
       </c>
       <c r="I10" t="n">
-        <v>400</v>
+        <v>171.047816275856</v>
       </c>
       <c r="J10" t="n">
-        <v>22.26478490148153</v>
+        <v>22.13729309820286</v>
       </c>
       <c r="K10" t="n">
-        <v>400</v>
+        <v>266.941429538848</v>
       </c>
       <c r="L10" t="n">
-        <v>400</v>
+        <v>395.9334970102382</v>
       </c>
       <c r="M10" t="n">
         <v>400</v>
@@ -28116,13 +28116,13 @@
         <v>400</v>
       </c>
       <c r="S10" t="n">
+        <v>359.1365780635112</v>
+      </c>
+      <c r="T10" t="n">
         <v>400</v>
       </c>
-      <c r="T10" t="n">
-        <v>291.7521154092183</v>
-      </c>
       <c r="U10" t="n">
-        <v>150.9483584875727</v>
+        <v>400</v>
       </c>
       <c r="V10" t="n">
         <v>400</v>
@@ -28134,7 +28134,7 @@
         <v>400</v>
       </c>
       <c r="Y10" t="n">
-        <v>287.4653528494624</v>
+        <v>400</v>
       </c>
     </row>
     <row r="11">
@@ -28165,7 +28165,7 @@
         <v>320</v>
       </c>
       <c r="I11" t="n">
-        <v>94.63721251837558</v>
+        <v>94.63721251837561</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -28226,10 +28226,10 @@
         <v>320</v>
       </c>
       <c r="C12" t="n">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>320</v>
       </c>
       <c r="E12" t="n">
         <v>320</v>
@@ -28238,7 +28238,7 @@
         <v>320</v>
       </c>
       <c r="G12" t="n">
-        <v>320</v>
+        <v>192.0084198490715</v>
       </c>
       <c r="H12" t="n">
         <v>320</v>
@@ -28283,16 +28283,16 @@
         <v>320</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>320</v>
       </c>
       <c r="W12" t="n">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>192.0084198490715</v>
+        <v>320</v>
       </c>
     </row>
     <row r="13">
@@ -28314,10 +28314,10 @@
         <v>320</v>
       </c>
       <c r="F13" t="n">
+        <v>320</v>
+      </c>
+      <c r="G13" t="n">
         <v>318.8640182103437</v>
-      </c>
-      <c r="G13" t="n">
-        <v>320</v>
       </c>
       <c r="H13" t="n">
         <v>320</v>
@@ -28402,7 +28402,7 @@
         <v>320</v>
       </c>
       <c r="I14" t="n">
-        <v>94.63721251837561</v>
+        <v>94.75154159223234</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -28429,7 +28429,7 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>160.7262319941236</v>
+        <v>160.6119029202667</v>
       </c>
       <c r="S14" t="n">
         <v>320</v>
@@ -28463,16 +28463,16 @@
         <v>320</v>
       </c>
       <c r="C15" t="n">
-        <v>116.94923023029</v>
+        <v>320</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>320</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>320</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>320</v>
       </c>
       <c r="G15" t="n">
         <v>320</v>
@@ -28517,16 +28517,16 @@
         <v>320</v>
       </c>
       <c r="U15" t="n">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>320</v>
+        <v>116.9492302302901</v>
       </c>
       <c r="Y15" t="n">
         <v>320</v>
@@ -28548,7 +28548,7 @@
         <v>320</v>
       </c>
       <c r="E16" t="n">
-        <v>318.8640182103436</v>
+        <v>320</v>
       </c>
       <c r="F16" t="n">
         <v>320</v>
@@ -28608,7 +28608,7 @@
         <v>320</v>
       </c>
       <c r="Y16" t="n">
-        <v>320</v>
+        <v>318.8640182103437</v>
       </c>
     </row>
     <row r="17">
@@ -28636,10 +28636,10 @@
         <v>320</v>
       </c>
       <c r="H17" t="n">
-        <v>319.8856709261432</v>
+        <v>320</v>
       </c>
       <c r="I17" t="n">
-        <v>94.75154159223234</v>
+        <v>94.63721251837561</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -28697,16 +28697,16 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>320</v>
       </c>
       <c r="E18" t="n">
-        <v>116.9492302302901</v>
+        <v>320</v>
       </c>
       <c r="F18" t="n">
         <v>320</v>
@@ -28760,13 +28760,13 @@
         <v>320</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>320</v>
       </c>
       <c r="X18" t="n">
-        <v>320</v>
+        <v>116.9492302302899</v>
       </c>
       <c r="Y18" t="n">
-        <v>320</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -28830,19 +28830,19 @@
         <v>320</v>
       </c>
       <c r="T19" t="n">
+        <v>320</v>
+      </c>
+      <c r="U19" t="n">
+        <v>320</v>
+      </c>
+      <c r="V19" t="n">
+        <v>320</v>
+      </c>
+      <c r="W19" t="n">
+        <v>320</v>
+      </c>
+      <c r="X19" t="n">
         <v>318.8640182103437</v>
-      </c>
-      <c r="U19" t="n">
-        <v>320</v>
-      </c>
-      <c r="V19" t="n">
-        <v>320</v>
-      </c>
-      <c r="W19" t="n">
-        <v>320</v>
-      </c>
-      <c r="X19" t="n">
-        <v>320</v>
       </c>
       <c r="Y19" t="n">
         <v>320</v>
@@ -28937,7 +28937,7 @@
         <v>320</v>
       </c>
       <c r="C21" t="n">
-        <v>192.0084198490715</v>
+        <v>116.94923023029</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -28979,7 +28979,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>75.05918961878146</v>
       </c>
       <c r="R21" t="n">
         <v>320</v>
@@ -29034,7 +29034,7 @@
         <v>320</v>
       </c>
       <c r="I22" t="n">
-        <v>318.8640182103438</v>
+        <v>320</v>
       </c>
       <c r="J22" t="n">
         <v>320</v>
@@ -29067,7 +29067,7 @@
         <v>320</v>
       </c>
       <c r="T22" t="n">
-        <v>320</v>
+        <v>318.8640182103437</v>
       </c>
       <c r="U22" t="n">
         <v>320</v>
@@ -29113,7 +29113,7 @@
         <v>320</v>
       </c>
       <c r="I23" t="n">
-        <v>94.63721251837561</v>
+        <v>94.75154159223234</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -29140,7 +29140,7 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>160.7262319941236</v>
+        <v>160.6119029202667</v>
       </c>
       <c r="S23" t="n">
         <v>320</v>
@@ -29174,19 +29174,19 @@
         <v>320</v>
       </c>
       <c r="C24" t="n">
-        <v>320</v>
+        <v>116.94923023029</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>320</v>
       </c>
       <c r="H24" t="n">
         <v>320</v>
@@ -29216,13 +29216,13 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>75.05918961878146</v>
       </c>
       <c r="R24" t="n">
-        <v>192.0084198490713</v>
+        <v>320</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>320</v>
       </c>
       <c r="T24" t="n">
         <v>320</v>
@@ -29274,7 +29274,7 @@
         <v>320</v>
       </c>
       <c r="J25" t="n">
-        <v>320</v>
+        <v>318.8640182103438</v>
       </c>
       <c r="K25" t="n">
         <v>320</v>
@@ -29304,7 +29304,7 @@
         <v>320</v>
       </c>
       <c r="T25" t="n">
-        <v>318.8640182103437</v>
+        <v>320</v>
       </c>
       <c r="U25" t="n">
         <v>320</v>
@@ -29347,7 +29347,7 @@
         <v>320</v>
       </c>
       <c r="H26" t="n">
-        <v>319.8856709261432</v>
+        <v>320</v>
       </c>
       <c r="I26" t="n">
         <v>94.75154159223234</v>
@@ -29377,7 +29377,7 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>160.7262319941236</v>
+        <v>160.6119029202667</v>
       </c>
       <c r="S26" t="n">
         <v>320</v>
@@ -29414,19 +29414,19 @@
         <v>320</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>320</v>
       </c>
       <c r="E27" t="n">
         <v>320</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>116.94923023029</v>
       </c>
       <c r="G27" t="n">
-        <v>116.9492302302899</v>
+        <v>320</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>320</v>
       </c>
       <c r="I27" t="n">
         <v>190.6881783441787</v>
@@ -29468,16 +29468,16 @@
         <v>320</v>
       </c>
       <c r="V27" t="n">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
         <v>320</v>
       </c>
       <c r="Y27" t="n">
-        <v>320</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -29502,7 +29502,7 @@
         <v>320</v>
       </c>
       <c r="G28" t="n">
-        <v>318.8640182103437</v>
+        <v>320</v>
       </c>
       <c r="H28" t="n">
         <v>320</v>
@@ -29511,7 +29511,7 @@
         <v>320</v>
       </c>
       <c r="J28" t="n">
-        <v>320</v>
+        <v>318.8640182103438</v>
       </c>
       <c r="K28" t="n">
         <v>320</v>
@@ -29648,16 +29648,16 @@
         <v>320</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>320</v>
       </c>
       <c r="D30" t="n">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
         <v>320</v>
@@ -29666,7 +29666,7 @@
         <v>320</v>
       </c>
       <c r="I30" t="n">
-        <v>190.6881783441787</v>
+        <v>62.69659819325013</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -29693,7 +29693,7 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>192.0084198490717</v>
+        <v>320</v>
       </c>
       <c r="S30" t="n">
         <v>320</v>
@@ -29705,10 +29705,10 @@
         <v>320</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>320</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>320</v>
       </c>
       <c r="X30" t="n">
         <v>320</v>
@@ -29736,49 +29736,49 @@
         <v>320</v>
       </c>
       <c r="F31" t="n">
+        <v>320</v>
+      </c>
+      <c r="G31" t="n">
+        <v>320</v>
+      </c>
+      <c r="H31" t="n">
+        <v>320</v>
+      </c>
+      <c r="I31" t="n">
+        <v>320</v>
+      </c>
+      <c r="J31" t="n">
+        <v>320</v>
+      </c>
+      <c r="K31" t="n">
+        <v>320</v>
+      </c>
+      <c r="L31" t="n">
+        <v>320</v>
+      </c>
+      <c r="M31" t="n">
+        <v>320</v>
+      </c>
+      <c r="N31" t="n">
+        <v>320</v>
+      </c>
+      <c r="O31" t="n">
+        <v>320</v>
+      </c>
+      <c r="P31" t="n">
+        <v>320</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>320</v>
+      </c>
+      <c r="R31" t="n">
+        <v>320</v>
+      </c>
+      <c r="S31" t="n">
+        <v>320</v>
+      </c>
+      <c r="T31" t="n">
         <v>318.8640182103437</v>
-      </c>
-      <c r="G31" t="n">
-        <v>320</v>
-      </c>
-      <c r="H31" t="n">
-        <v>320</v>
-      </c>
-      <c r="I31" t="n">
-        <v>320</v>
-      </c>
-      <c r="J31" t="n">
-        <v>320</v>
-      </c>
-      <c r="K31" t="n">
-        <v>320</v>
-      </c>
-      <c r="L31" t="n">
-        <v>320</v>
-      </c>
-      <c r="M31" t="n">
-        <v>320</v>
-      </c>
-      <c r="N31" t="n">
-        <v>320</v>
-      </c>
-      <c r="O31" t="n">
-        <v>320</v>
-      </c>
-      <c r="P31" t="n">
-        <v>320</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>320</v>
-      </c>
-      <c r="R31" t="n">
-        <v>320</v>
-      </c>
-      <c r="S31" t="n">
-        <v>320</v>
-      </c>
-      <c r="T31" t="n">
-        <v>320</v>
       </c>
       <c r="U31" t="n">
         <v>320</v>
@@ -29882,16 +29882,16 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>116.9492302302901</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>320</v>
       </c>
       <c r="E33" t="n">
-        <v>192.0084198490715</v>
+        <v>320</v>
       </c>
       <c r="F33" t="n">
         <v>320</v>
@@ -29927,7 +29927,7 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>75.05918961878146</v>
       </c>
       <c r="R33" t="n">
         <v>320</v>
@@ -29942,7 +29942,7 @@
         <v>320</v>
       </c>
       <c r="V33" t="n">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
         <v>320</v>
@@ -29970,7 +29970,7 @@
         <v>320</v>
       </c>
       <c r="E34" t="n">
-        <v>320</v>
+        <v>318.8640182103436</v>
       </c>
       <c r="F34" t="n">
         <v>320</v>
@@ -30015,7 +30015,7 @@
         <v>320</v>
       </c>
       <c r="T34" t="n">
-        <v>318.8640182103437</v>
+        <v>320</v>
       </c>
       <c r="U34" t="n">
         <v>320</v>
@@ -30040,28 +30040,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C35" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D35" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="E35" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F35" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="G35" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="H35" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="I35" t="n">
-        <v>94.75154159223234</v>
+        <v>93.87001251837566</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -30091,25 +30091,25 @@
         <v>160.7262319941236</v>
       </c>
       <c r="S35" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="T35" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="U35" t="n">
-        <v>365.7144709261434</v>
+        <v>373</v>
       </c>
       <c r="V35" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="W35" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="X35" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Y35" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="36">
@@ -30119,10 +30119,10 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D36" t="n">
         <v>347.9376868977026</v>
@@ -30131,7 +30131,7 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G36" t="n">
         <v>324.9716490825745</v>
@@ -30167,28 +30167,28 @@
         <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>168.3578240866323</v>
+        <v>226.0256693032363</v>
       </c>
       <c r="S36" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="T36" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="U36" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="V36" t="n">
-        <v>372</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>372</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>372</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>373</v>
       </c>
     </row>
     <row r="37">
@@ -30198,55 +30198,55 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C37" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D37" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="E37" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F37" t="n">
-        <v>329.2121084899231</v>
+        <v>373</v>
       </c>
       <c r="G37" t="n">
-        <v>244.4001023497268</v>
+        <v>373</v>
       </c>
       <c r="H37" t="n">
         <v>223.0474211835858</v>
       </c>
       <c r="I37" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>213.7263475716348</v>
+        <v>373</v>
       </c>
       <c r="L37" t="n">
-        <v>372</v>
+        <v>345.6736140527162</v>
       </c>
       <c r="M37" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="N37" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="O37" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="P37" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Q37" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="R37" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="S37" t="n">
         <v>351.1543157684292</v>
@@ -30258,16 +30258,16 @@
         <v>150.9232765203596</v>
       </c>
       <c r="V37" t="n">
-        <v>372</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W37" t="n">
-        <v>372</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X37" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Y37" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="38">
@@ -30277,25 +30277,25 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C38" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D38" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="E38" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F38" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="G38" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="H38" t="n">
-        <v>365.7144709261435</v>
+        <v>373</v>
       </c>
       <c r="I38" t="n">
         <v>94.75154159223234</v>
@@ -30325,28 +30325,28 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>160.7262319941236</v>
+        <v>159.8447029202671</v>
       </c>
       <c r="S38" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="T38" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="U38" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="V38" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="W38" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="X38" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Y38" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="39">
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C39" t="n">
-        <v>361.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
@@ -30371,7 +30371,7 @@
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>324.9716490825745</v>
       </c>
       <c r="H39" t="n">
         <v>324.7519173751004</v>
@@ -30401,31 +30401,31 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>75.05918961878146</v>
       </c>
       <c r="R39" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="S39" t="n">
-        <v>372</v>
+        <v>80.64032136555323</v>
       </c>
       <c r="T39" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="U39" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="V39" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="W39" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="X39" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Y39" t="n">
-        <v>108.1672476213903</v>
+        <v>373</v>
       </c>
     </row>
     <row r="40">
@@ -30438,73 +30438,73 @@
         <v>287.1138003370787</v>
       </c>
       <c r="C40" t="n">
-        <v>272.7252466480447</v>
+        <v>373</v>
       </c>
       <c r="D40" t="n">
-        <v>285.5362180555555</v>
+        <v>373</v>
       </c>
       <c r="E40" t="n">
-        <v>280.9809048369565</v>
+        <v>373</v>
       </c>
       <c r="F40" t="n">
         <v>274.3828559677419</v>
       </c>
       <c r="G40" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="H40" t="n">
-        <v>323.6230619519795</v>
+        <v>373</v>
       </c>
       <c r="I40" t="n">
-        <v>372</v>
+        <v>157.2735211938888</v>
       </c>
       <c r="J40" t="n">
-        <v>372</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>372</v>
+        <v>213.7263475716348</v>
       </c>
       <c r="L40" t="n">
-        <v>372</v>
+        <v>327.8365134036808</v>
       </c>
       <c r="M40" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="N40" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="O40" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="P40" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Q40" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="R40" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="S40" t="n">
-        <v>372</v>
+        <v>351.1543157684292</v>
       </c>
       <c r="T40" t="n">
-        <v>372</v>
+        <v>207.2739107685528</v>
       </c>
       <c r="U40" t="n">
-        <v>150.9232765203596</v>
+        <v>373</v>
       </c>
       <c r="V40" t="n">
-        <v>199.1703102162162</v>
+        <v>257.8543933375625</v>
       </c>
       <c r="W40" t="n">
-        <v>226.3728098387097</v>
+        <v>373</v>
       </c>
       <c r="X40" t="n">
-        <v>247.4436454301076</v>
+        <v>373</v>
       </c>
       <c r="Y40" t="n">
-        <v>287.4653528494624</v>
+        <v>373</v>
       </c>
     </row>
     <row r="41">
@@ -30596,22 +30596,22 @@
         <v>320</v>
       </c>
       <c r="C42" t="n">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="D42" t="n">
         <v>320</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>320</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>320</v>
       </c>
       <c r="G42" t="n">
         <v>320</v>
       </c>
       <c r="H42" t="n">
-        <v>272.691174663922</v>
+        <v>217.0359850451408</v>
       </c>
       <c r="I42" t="n">
         <v>190.6881783441787</v>
@@ -30638,7 +30638,7 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>75.05918961878146</v>
       </c>
       <c r="R42" t="n">
         <v>320</v>
@@ -30650,7 +30650,7 @@
         <v>320</v>
       </c>
       <c r="U42" t="n">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
         <v>320</v>
@@ -30726,10 +30726,10 @@
         <v>320</v>
       </c>
       <c r="T43" t="n">
-        <v>320</v>
+        <v>318.8640182103439</v>
       </c>
       <c r="U43" t="n">
-        <v>318.8640182103441</v>
+        <v>320</v>
       </c>
       <c r="V43" t="n">
         <v>320</v>
@@ -30830,7 +30830,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0</v>
+        <v>320</v>
       </c>
       <c r="C45" t="n">
         <v>320</v>
@@ -30839,19 +30839,19 @@
         <v>320</v>
       </c>
       <c r="E45" t="n">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>320</v>
       </c>
       <c r="G45" t="n">
         <v>320</v>
       </c>
       <c r="H45" t="n">
-        <v>320</v>
+        <v>178.4385273754032</v>
       </c>
       <c r="I45" t="n">
-        <v>68.32016338931932</v>
+        <v>190.6881783441787</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -30878,7 +30878,7 @@
         <v>75.05918961878146</v>
       </c>
       <c r="R45" t="n">
-        <v>320</v>
+        <v>38.59745766973777</v>
       </c>
       <c r="S45" t="n">
         <v>320</v>
@@ -30936,7 +30936,7 @@
         <v>320</v>
       </c>
       <c r="K46" t="n">
-        <v>318.8640182103434</v>
+        <v>320</v>
       </c>
       <c r="L46" t="n">
         <v>320</v>
@@ -30963,7 +30963,7 @@
         <v>320</v>
       </c>
       <c r="T46" t="n">
-        <v>320</v>
+        <v>318.8640182103435</v>
       </c>
       <c r="U46" t="n">
         <v>320</v>
@@ -31091,49 +31091,49 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4100502512562811</v>
+        <v>0.4140703517587936</v>
       </c>
       <c r="H2" t="n">
-        <v>4.199427135678389</v>
+        <v>4.240597989949746</v>
       </c>
       <c r="I2" t="n">
-        <v>15.80846231155779</v>
+        <v>15.96344723618091</v>
       </c>
       <c r="J2" t="n">
-        <v>34.80250251256282</v>
+        <v>35.14370351758794</v>
       </c>
       <c r="K2" t="n">
-        <v>52.15992964824121</v>
+        <v>52.67130150753769</v>
       </c>
       <c r="L2" t="n">
-        <v>64.70900502512563</v>
+        <v>65.34340703517589</v>
       </c>
       <c r="M2" t="n">
-        <v>72.00123618090453</v>
+        <v>72.70713065326633</v>
       </c>
       <c r="N2" t="n">
-        <v>73.16629145728643</v>
+        <v>73.88360804020101</v>
       </c>
       <c r="O2" t="n">
-        <v>69.08885427135678</v>
+        <v>69.76619597989949</v>
       </c>
       <c r="P2" t="n">
-        <v>58.96573869346734</v>
+        <v>59.54383417085427</v>
       </c>
       <c r="Q2" t="n">
-        <v>44.28081407035176</v>
+        <v>44.71493969849246</v>
       </c>
       <c r="R2" t="n">
-        <v>25.75781909547739</v>
+        <v>26.01034673366835</v>
       </c>
       <c r="S2" t="n">
-        <v>9.344020100502515</v>
+        <v>9.435628140703519</v>
       </c>
       <c r="T2" t="n">
-        <v>1.794994974874371</v>
+        <v>1.81259296482412</v>
       </c>
       <c r="U2" t="n">
-        <v>0.03280402010050248</v>
+        <v>0.03312562814070349</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -31170,49 +31170,49 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2193962264150943</v>
+        <v>0.2215471698113208</v>
       </c>
       <c r="H3" t="n">
-        <v>2.118905660377359</v>
+        <v>2.139679245283019</v>
       </c>
       <c r="I3" t="n">
-        <v>7.553773584905661</v>
+        <v>7.627830188679247</v>
       </c>
       <c r="J3" t="n">
-        <v>20.7281320754717</v>
+        <v>20.93134905660378</v>
       </c>
       <c r="K3" t="n">
-        <v>35.42767924528302</v>
+        <v>35.77500943396227</v>
       </c>
       <c r="L3" t="n">
-        <v>47.63688679245283</v>
+        <v>48.10391509433963</v>
       </c>
       <c r="M3" t="n">
-        <v>55.58999999999999</v>
+        <v>56.13499999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>57.06130188679246</v>
+        <v>57.62072641509435</v>
       </c>
       <c r="O3" t="n">
-        <v>52.19994339622642</v>
+        <v>52.71170754716981</v>
       </c>
       <c r="P3" t="n">
-        <v>41.89505660377359</v>
+        <v>42.3057924528302</v>
       </c>
       <c r="Q3" t="n">
-        <v>28.00573584905661</v>
+        <v>28.28030188679246</v>
       </c>
       <c r="R3" t="n">
-        <v>13.62181132075472</v>
+        <v>13.75535849056604</v>
       </c>
       <c r="S3" t="n">
-        <v>4.07518867924528</v>
+        <v>4.115141509433959</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8843207547169808</v>
+        <v>0.8929905660377355</v>
       </c>
       <c r="U3" t="n">
-        <v>0.01443396226415095</v>
+        <v>0.01457547169811321</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -31249,49 +31249,49 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1839344262295082</v>
+        <v>0.1857377049180328</v>
       </c>
       <c r="H4" t="n">
-        <v>1.635344262295083</v>
+        <v>1.651377049180329</v>
       </c>
       <c r="I4" t="n">
-        <v>5.531409836065575</v>
+        <v>5.585639344262296</v>
       </c>
       <c r="J4" t="n">
-        <v>13.00416393442623</v>
+        <v>13.13165573770492</v>
       </c>
       <c r="K4" t="n">
-        <v>21.36983606557376</v>
+        <v>21.57934426229507</v>
       </c>
       <c r="L4" t="n">
-        <v>27.34603278688525</v>
+        <v>27.61413114754098</v>
       </c>
       <c r="M4" t="n">
-        <v>28.83255737704917</v>
+        <v>29.11522950819672</v>
       </c>
       <c r="N4" t="n">
-        <v>28.1469836065574</v>
+        <v>28.42293442622952</v>
       </c>
       <c r="O4" t="n">
-        <v>25.99829508196722</v>
+        <v>26.25318032786886</v>
       </c>
       <c r="P4" t="n">
-        <v>22.24603278688523</v>
+        <v>22.46413114754097</v>
       </c>
       <c r="Q4" t="n">
-        <v>15.402</v>
+        <v>15.553</v>
       </c>
       <c r="R4" t="n">
-        <v>8.270360655737703</v>
+        <v>8.351442622950817</v>
       </c>
       <c r="S4" t="n">
-        <v>3.205475409836064</v>
+        <v>3.236901639344261</v>
       </c>
       <c r="T4" t="n">
-        <v>0.785901639344262</v>
+        <v>0.7936065573770489</v>
       </c>
       <c r="U4" t="n">
-        <v>0.01003278688524591</v>
+        <v>0.01013114754098362</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -31328,49 +31328,49 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4100502512562811</v>
+        <v>0.4140703517587936</v>
       </c>
       <c r="H5" t="n">
-        <v>4.199427135678389</v>
+        <v>4.240597989949746</v>
       </c>
       <c r="I5" t="n">
-        <v>15.80846231155779</v>
+        <v>15.96344723618091</v>
       </c>
       <c r="J5" t="n">
-        <v>34.80250251256282</v>
+        <v>35.14370351758794</v>
       </c>
       <c r="K5" t="n">
-        <v>52.15992964824121</v>
+        <v>52.67130150753769</v>
       </c>
       <c r="L5" t="n">
-        <v>64.70900502512563</v>
+        <v>65.34340703517589</v>
       </c>
       <c r="M5" t="n">
-        <v>72.00123618090453</v>
+        <v>72.70713065326633</v>
       </c>
       <c r="N5" t="n">
-        <v>73.16629145728643</v>
+        <v>73.88360804020101</v>
       </c>
       <c r="O5" t="n">
-        <v>69.08885427135678</v>
+        <v>69.76619597989949</v>
       </c>
       <c r="P5" t="n">
-        <v>58.96573869346734</v>
+        <v>59.54383417085427</v>
       </c>
       <c r="Q5" t="n">
-        <v>44.28081407035176</v>
+        <v>44.71493969849246</v>
       </c>
       <c r="R5" t="n">
-        <v>25.75781909547739</v>
+        <v>26.01034673366835</v>
       </c>
       <c r="S5" t="n">
-        <v>9.344020100502515</v>
+        <v>9.435628140703519</v>
       </c>
       <c r="T5" t="n">
-        <v>1.794994974874371</v>
+        <v>1.81259296482412</v>
       </c>
       <c r="U5" t="n">
-        <v>0.03280402010050248</v>
+        <v>0.03312562814070349</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -31407,49 +31407,49 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2193962264150943</v>
+        <v>0.2215471698113208</v>
       </c>
       <c r="H6" t="n">
-        <v>2.118905660377359</v>
+        <v>2.139679245283019</v>
       </c>
       <c r="I6" t="n">
-        <v>7.553773584905661</v>
+        <v>7.627830188679247</v>
       </c>
       <c r="J6" t="n">
-        <v>20.7281320754717</v>
+        <v>20.93134905660378</v>
       </c>
       <c r="K6" t="n">
-        <v>35.42767924528302</v>
+        <v>35.77500943396227</v>
       </c>
       <c r="L6" t="n">
-        <v>47.63688679245283</v>
+        <v>48.10391509433963</v>
       </c>
       <c r="M6" t="n">
-        <v>55.58999999999999</v>
+        <v>56.13499999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>57.06130188679246</v>
+        <v>57.62072641509435</v>
       </c>
       <c r="O6" t="n">
-        <v>52.19994339622642</v>
+        <v>52.71170754716981</v>
       </c>
       <c r="P6" t="n">
-        <v>41.89505660377359</v>
+        <v>42.3057924528302</v>
       </c>
       <c r="Q6" t="n">
-        <v>28.00573584905661</v>
+        <v>28.28030188679246</v>
       </c>
       <c r="R6" t="n">
-        <v>13.62181132075472</v>
+        <v>13.75535849056604</v>
       </c>
       <c r="S6" t="n">
-        <v>4.07518867924528</v>
+        <v>4.115141509433959</v>
       </c>
       <c r="T6" t="n">
-        <v>0.8843207547169808</v>
+        <v>0.8929905660377355</v>
       </c>
       <c r="U6" t="n">
-        <v>0.01443396226415095</v>
+        <v>0.01457547169811321</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -31486,49 +31486,49 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1839344262295082</v>
+        <v>0.1857377049180328</v>
       </c>
       <c r="H7" t="n">
-        <v>1.635344262295083</v>
+        <v>1.651377049180329</v>
       </c>
       <c r="I7" t="n">
-        <v>5.531409836065575</v>
+        <v>5.585639344262296</v>
       </c>
       <c r="J7" t="n">
-        <v>13.00416393442623</v>
+        <v>13.13165573770492</v>
       </c>
       <c r="K7" t="n">
-        <v>21.36983606557376</v>
+        <v>21.57934426229507</v>
       </c>
       <c r="L7" t="n">
-        <v>27.34603278688525</v>
+        <v>27.61413114754098</v>
       </c>
       <c r="M7" t="n">
-        <v>28.83255737704917</v>
+        <v>29.11522950819672</v>
       </c>
       <c r="N7" t="n">
-        <v>28.1469836065574</v>
+        <v>28.42293442622952</v>
       </c>
       <c r="O7" t="n">
-        <v>25.99829508196722</v>
+        <v>26.25318032786886</v>
       </c>
       <c r="P7" t="n">
-        <v>22.24603278688523</v>
+        <v>22.46413114754097</v>
       </c>
       <c r="Q7" t="n">
-        <v>15.402</v>
+        <v>15.553</v>
       </c>
       <c r="R7" t="n">
-        <v>8.270360655737703</v>
+        <v>8.351442622950817</v>
       </c>
       <c r="S7" t="n">
-        <v>3.205475409836064</v>
+        <v>3.236901639344261</v>
       </c>
       <c r="T7" t="n">
-        <v>0.785901639344262</v>
+        <v>0.7936065573770489</v>
       </c>
       <c r="U7" t="n">
-        <v>0.01003278688524591</v>
+        <v>0.01013114754098362</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -31565,49 +31565,49 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4100502512562811</v>
+        <v>0.4140703517587936</v>
       </c>
       <c r="H8" t="n">
-        <v>4.199427135678389</v>
+        <v>4.240597989949746</v>
       </c>
       <c r="I8" t="n">
-        <v>15.80846231155779</v>
+        <v>15.96344723618091</v>
       </c>
       <c r="J8" t="n">
-        <v>34.80250251256282</v>
+        <v>35.14370351758794</v>
       </c>
       <c r="K8" t="n">
-        <v>52.15992964824121</v>
+        <v>52.67130150753769</v>
       </c>
       <c r="L8" t="n">
-        <v>64.70900502512563</v>
+        <v>65.34340703517589</v>
       </c>
       <c r="M8" t="n">
-        <v>72.00123618090453</v>
+        <v>72.70713065326633</v>
       </c>
       <c r="N8" t="n">
-        <v>73.16629145728643</v>
+        <v>73.88360804020101</v>
       </c>
       <c r="O8" t="n">
-        <v>69.08885427135678</v>
+        <v>69.76619597989949</v>
       </c>
       <c r="P8" t="n">
-        <v>58.96573869346734</v>
+        <v>59.54383417085427</v>
       </c>
       <c r="Q8" t="n">
-        <v>44.28081407035176</v>
+        <v>44.71493969849246</v>
       </c>
       <c r="R8" t="n">
-        <v>25.75781909547739</v>
+        <v>26.01034673366835</v>
       </c>
       <c r="S8" t="n">
-        <v>9.344020100502515</v>
+        <v>9.435628140703519</v>
       </c>
       <c r="T8" t="n">
-        <v>1.794994974874371</v>
+        <v>1.81259296482412</v>
       </c>
       <c r="U8" t="n">
-        <v>0.03280402010050248</v>
+        <v>0.03312562814070349</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -31644,49 +31644,49 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2193962264150943</v>
+        <v>0.2215471698113208</v>
       </c>
       <c r="H9" t="n">
-        <v>2.118905660377359</v>
+        <v>2.139679245283019</v>
       </c>
       <c r="I9" t="n">
-        <v>7.553773584905661</v>
+        <v>7.627830188679247</v>
       </c>
       <c r="J9" t="n">
-        <v>20.7281320754717</v>
+        <v>20.93134905660378</v>
       </c>
       <c r="K9" t="n">
-        <v>35.42767924528302</v>
+        <v>35.77500943396227</v>
       </c>
       <c r="L9" t="n">
-        <v>47.63688679245283</v>
+        <v>48.10391509433963</v>
       </c>
       <c r="M9" t="n">
-        <v>55.58999999999999</v>
+        <v>56.13499999999999</v>
       </c>
       <c r="N9" t="n">
-        <v>57.06130188679246</v>
+        <v>57.62072641509435</v>
       </c>
       <c r="O9" t="n">
-        <v>52.19994339622642</v>
+        <v>52.71170754716981</v>
       </c>
       <c r="P9" t="n">
-        <v>41.89505660377359</v>
+        <v>42.3057924528302</v>
       </c>
       <c r="Q9" t="n">
-        <v>28.00573584905661</v>
+        <v>28.28030188679246</v>
       </c>
       <c r="R9" t="n">
-        <v>13.62181132075472</v>
+        <v>13.75535849056604</v>
       </c>
       <c r="S9" t="n">
-        <v>4.07518867924528</v>
+        <v>4.115141509433959</v>
       </c>
       <c r="T9" t="n">
-        <v>0.8843207547169808</v>
+        <v>0.8929905660377355</v>
       </c>
       <c r="U9" t="n">
-        <v>0.01443396226415095</v>
+        <v>0.01457547169811321</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -31723,49 +31723,49 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1839344262295082</v>
+        <v>0.1857377049180328</v>
       </c>
       <c r="H10" t="n">
-        <v>1.635344262295083</v>
+        <v>1.651377049180329</v>
       </c>
       <c r="I10" t="n">
-        <v>5.531409836065575</v>
+        <v>5.585639344262296</v>
       </c>
       <c r="J10" t="n">
-        <v>13.00416393442623</v>
+        <v>13.13165573770492</v>
       </c>
       <c r="K10" t="n">
-        <v>21.36983606557376</v>
+        <v>21.57934426229507</v>
       </c>
       <c r="L10" t="n">
-        <v>27.34603278688525</v>
+        <v>27.61413114754098</v>
       </c>
       <c r="M10" t="n">
-        <v>28.83255737704917</v>
+        <v>29.11522950819672</v>
       </c>
       <c r="N10" t="n">
-        <v>28.1469836065574</v>
+        <v>28.42293442622952</v>
       </c>
       <c r="O10" t="n">
-        <v>25.99829508196722</v>
+        <v>26.25318032786886</v>
       </c>
       <c r="P10" t="n">
-        <v>22.24603278688523</v>
+        <v>22.46413114754097</v>
       </c>
       <c r="Q10" t="n">
-        <v>15.402</v>
+        <v>15.553</v>
       </c>
       <c r="R10" t="n">
-        <v>8.270360655737703</v>
+        <v>8.351442622950817</v>
       </c>
       <c r="S10" t="n">
-        <v>3.205475409836064</v>
+        <v>3.236901639344261</v>
       </c>
       <c r="T10" t="n">
-        <v>0.785901639344262</v>
+        <v>0.7936065573770489</v>
       </c>
       <c r="U10" t="n">
-        <v>0.01003278688524591</v>
+        <v>0.01013114754098362</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -34743,28 +34743,28 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>373</v>
       </c>
       <c r="K2" t="n">
-        <v>52.1599296482412</v>
+        <v>52.67130150753769</v>
       </c>
       <c r="L2" t="n">
-        <v>374</v>
+        <v>65.34340703517586</v>
       </c>
       <c r="M2" t="n">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="N2" t="n">
-        <v>374</v>
+        <v>180.6578102564064</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>58.67867865278593</v>
+        <v>59.25677413017286</v>
       </c>
       <c r="Q2" t="n">
-        <v>248.0502805878619</v>
+        <v>373</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -34822,25 +34822,25 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>145.9367383131474</v>
+        <v>146.1399552942795</v>
       </c>
       <c r="K3" t="n">
-        <v>226.5315338860743</v>
+        <v>226.8788640747536</v>
       </c>
       <c r="L3" t="n">
-        <v>321.7282621411399</v>
+        <v>318.4376284546069</v>
       </c>
       <c r="M3" t="n">
-        <v>142.5400421645043</v>
+        <v>143.0850421645043</v>
       </c>
       <c r="N3" t="n">
-        <v>191.6878519954473</v>
+        <v>192.2472765237492</v>
       </c>
       <c r="O3" t="n">
-        <v>293.6569652989728</v>
+        <v>294.1687294499162</v>
       </c>
       <c r="P3" t="n">
-        <v>155.5610611184268</v>
+        <v>155.9717969674834</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -34877,13 +34877,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>112.8861996629213</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>127.2747533519553</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>114.4637819444445</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
         <v>119.0190951630435</v>
@@ -34892,22 +34892,22 @@
         <v>125.6171440322581</v>
       </c>
       <c r="G4" t="n">
-        <v>155.1400615846995</v>
+        <v>155.141864863388</v>
       </c>
       <c r="H4" t="n">
-        <v>172.8642181606765</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>228.952183724144</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>99.85873282189253</v>
       </c>
       <c r="K4" t="n">
-        <v>132.8490622644307</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>3.798404629106074</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -34931,22 +34931,22 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>190.7690400511193</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>249.0517398730831</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>200.8296897837838</v>
       </c>
       <c r="W4" t="n">
-        <v>41.52511431909203</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>152.5563545698924</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>112.5346471505376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -34980,28 +34980,28 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>0.1006972724976123</v>
       </c>
       <c r="K5" t="n">
-        <v>374</v>
+        <v>233.2284144914465</v>
       </c>
       <c r="L5" t="n">
-        <v>64.70900502512563</v>
+        <v>65.34340703517591</v>
       </c>
       <c r="M5" t="n">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="N5" t="n">
-        <v>235.5012052109774</v>
+        <v>373</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>58.67867865278593</v>
+        <v>59.25677413017286</v>
       </c>
       <c r="Q5" t="n">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -35059,25 +35059,25 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>145.9367383131474</v>
+        <v>146.1399552942795</v>
       </c>
       <c r="K6" t="n">
-        <v>226.5315338860743</v>
+        <v>226.8788640747536</v>
       </c>
       <c r="L6" t="n">
-        <v>321.7282621411399</v>
+        <v>318.4376284546069</v>
       </c>
       <c r="M6" t="n">
-        <v>142.5400421645043</v>
+        <v>143.0850421645043</v>
       </c>
       <c r="N6" t="n">
-        <v>191.6878519954473</v>
+        <v>192.2472765237492</v>
       </c>
       <c r="O6" t="n">
-        <v>293.6569652989728</v>
+        <v>294.1687294499162</v>
       </c>
       <c r="P6" t="n">
-        <v>155.5610611184268</v>
+        <v>155.9717969674834</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -35120,22 +35120,22 @@
         <v>127.2747533519553</v>
       </c>
       <c r="D7" t="n">
-        <v>51.00702550716271</v>
+        <v>114.4637819444445</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>119.0190951630435</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>125.6171440322581</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>172.8802509475617</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>228.952183724144</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -35168,16 +35168,16 @@
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>190.7613351330866</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>249.0516415124273</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>200.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>173.6271901612903</v>
+        <v>103.055079765954</v>
       </c>
       <c r="X7" t="n">
         <v>152.5563545698924</v>
@@ -35217,31 +35217,31 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>235.5012052109774</v>
+        <v>0.1006972724976123</v>
       </c>
       <c r="K8" t="n">
-        <v>374</v>
+        <v>52.67130150753769</v>
       </c>
       <c r="L8" t="n">
-        <v>64.70900502512563</v>
+        <v>373</v>
       </c>
       <c r="M8" t="n">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="N8" t="n">
-        <v>374</v>
+        <v>245.9005200190848</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>58.67867865278593</v>
+        <v>59.25677413017286</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>373</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>6.660440997832051e-12</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -35296,25 +35296,25 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>145.9367383131474</v>
+        <v>146.1399552942795</v>
       </c>
       <c r="K9" t="n">
-        <v>226.5315338860743</v>
+        <v>226.8788640747536</v>
       </c>
       <c r="L9" t="n">
-        <v>321.7282621411399</v>
+        <v>322.1952904430266</v>
       </c>
       <c r="M9" t="n">
-        <v>142.5400421645043</v>
+        <v>143.0850421645043</v>
       </c>
       <c r="N9" t="n">
-        <v>191.6878519954473</v>
+        <v>188.4896145353295</v>
       </c>
       <c r="O9" t="n">
-        <v>293.6569652989728</v>
+        <v>294.1687294499162</v>
       </c>
       <c r="P9" t="n">
-        <v>155.5610611184268</v>
+        <v>155.9717969674834</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -35357,7 +35357,7 @@
         <v>127.2747533519553</v>
       </c>
       <c r="D10" t="n">
-        <v>114.4637819444445</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -35366,22 +35366,22 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>49.7098757081293</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>228.8979542159473</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>132.8490622644307</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>3.798404629106074</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -35402,13 +35402,13 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>40.83199570698063</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>82.51345054230484</v>
+        <v>190.7690400511193</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>249.0517398730831</v>
       </c>
       <c r="V10" t="n">
         <v>200.8296897837838</v>
@@ -35420,7 +35420,7 @@
         <v>152.5563545698924</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>112.5346471505376</v>
       </c>
     </row>
     <row r="11">
@@ -35463,10 +35463,10 @@
         <v>226.4815175879396</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>156.4484131714791</v>
       </c>
       <c r="N11" t="n">
-        <v>210.4361749831598</v>
+        <v>652</v>
       </c>
       <c r="O11" t="n">
         <v>171.5631203756563</v>
@@ -35475,7 +35475,7 @@
         <v>206.0930253864543</v>
       </c>
       <c r="Q11" t="n">
-        <v>598.0122381883194</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -35600,13 +35600,13 @@
         <v>39.01909516304346</v>
       </c>
       <c r="F13" t="n">
-        <v>44.48116224260178</v>
+        <v>45.61714403225807</v>
       </c>
       <c r="G13" t="n">
-        <v>75.59989765027325</v>
+        <v>74.46391586061698</v>
       </c>
       <c r="H13" t="n">
-        <v>96.95257881641417</v>
+        <v>96.95257881641416</v>
       </c>
       <c r="I13" t="n">
         <v>162.7264788061112</v>
@@ -35615,7 +35615,7 @@
         <v>330.245624934584</v>
       </c>
       <c r="K13" t="n">
-        <v>106.2736524283651</v>
+        <v>106.2736524283652</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -35691,7 +35691,7 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>86.76575254887953</v>
+        <v>517.0704891350363</v>
       </c>
       <c r="K14" t="n">
         <v>182.5597537688442</v>
@@ -35700,7 +35700,7 @@
         <v>226.4815175879397</v>
       </c>
       <c r="M14" t="n">
-        <v>12.27418318692654</v>
+        <v>625.8886594026346</v>
       </c>
       <c r="N14" t="n">
         <v>652</v>
@@ -35709,10 +35709,10 @@
         <v>171.5631203756563</v>
       </c>
       <c r="P14" t="n">
-        <v>652</v>
+        <v>206.0930253864543</v>
       </c>
       <c r="Q14" t="n">
-        <v>598.0122381883194</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -35834,7 +35834,7 @@
         <v>34.46378194444452</v>
       </c>
       <c r="E16" t="n">
-        <v>37.88311337338708</v>
+        <v>39.01909516304346</v>
       </c>
       <c r="F16" t="n">
         <v>45.61714403225807</v>
@@ -35843,7 +35843,7 @@
         <v>75.59989765027325</v>
       </c>
       <c r="H16" t="n">
-        <v>96.95257881641416</v>
+        <v>96.95257881641417</v>
       </c>
       <c r="I16" t="n">
         <v>162.7264788061112</v>
@@ -35852,7 +35852,7 @@
         <v>330.245624934584</v>
       </c>
       <c r="K16" t="n">
-        <v>106.2736524283652</v>
+        <v>106.2736524283651</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -35894,7 +35894,7 @@
         <v>72.55635456989245</v>
       </c>
       <c r="Y16" t="n">
-        <v>32.53464715053764</v>
+        <v>31.39866536088129</v>
       </c>
     </row>
     <row r="17">
@@ -35931,13 +35931,13 @@
         <v>86.76575254887953</v>
       </c>
       <c r="K17" t="n">
-        <v>652</v>
+        <v>182.5597537688442</v>
       </c>
       <c r="L17" t="n">
         <v>226.4815175879397</v>
       </c>
       <c r="M17" t="n">
-        <v>140.8461751440902</v>
+        <v>652</v>
       </c>
       <c r="N17" t="n">
         <v>652</v>
@@ -35946,10 +35946,10 @@
         <v>171.5631203756563</v>
       </c>
       <c r="P17" t="n">
-        <v>652</v>
+        <v>206.0930253864543</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>404.1933959887915</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -36080,7 +36080,7 @@
         <v>75.59989765027325</v>
       </c>
       <c r="H19" t="n">
-        <v>96.95257881641417</v>
+        <v>96.95257881641416</v>
       </c>
       <c r="I19" t="n">
         <v>162.7264788061112</v>
@@ -36089,7 +36089,7 @@
         <v>330.245624934584</v>
       </c>
       <c r="K19" t="n">
-        <v>106.2736524283651</v>
+        <v>106.2736524283652</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -36116,7 +36116,7 @@
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>111.5901074417909</v>
+        <v>112.7260892314472</v>
       </c>
       <c r="U19" t="n">
         <v>169.0767234796404</v>
@@ -36128,7 +36128,7 @@
         <v>93.62719016129032</v>
       </c>
       <c r="X19" t="n">
-        <v>72.55635456989245</v>
+        <v>71.42037278023614</v>
       </c>
       <c r="Y19" t="n">
         <v>32.53464715053764</v>
@@ -36165,28 +36165,28 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>517.0704891350363</v>
+        <v>86.76575254887953</v>
       </c>
       <c r="K20" t="n">
+        <v>182.5597537688442</v>
+      </c>
+      <c r="L20" t="n">
         <v>652</v>
       </c>
-      <c r="L20" t="n">
-        <v>226.4815175879396</v>
-      </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>652</v>
       </c>
       <c r="N20" t="n">
-        <v>328.0115335471354</v>
+        <v>32.66267538841186</v>
       </c>
       <c r="O20" t="n">
-        <v>652</v>
+        <v>171.5631203756563</v>
       </c>
       <c r="P20" t="n">
         <v>206.0930253864543</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>598.0122381883194</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -36320,7 +36320,7 @@
         <v>96.95257881641416</v>
       </c>
       <c r="I22" t="n">
-        <v>161.590497016455</v>
+        <v>162.7264788061112</v>
       </c>
       <c r="J22" t="n">
         <v>330.245624934584</v>
@@ -36353,7 +36353,7 @@
         <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>112.7260892314472</v>
+        <v>111.5901074417909</v>
       </c>
       <c r="U22" t="n">
         <v>169.0767234796404</v>
@@ -36402,19 +36402,19 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>86.76575254887953</v>
+        <v>517.0704891350363</v>
       </c>
       <c r="K23" t="n">
+        <v>182.5597537688442</v>
+      </c>
+      <c r="L23" t="n">
+        <v>652.0000000000001</v>
+      </c>
+      <c r="M23" t="n">
         <v>652</v>
       </c>
-      <c r="L23" t="n">
-        <v>652</v>
-      </c>
-      <c r="M23" t="n">
-        <v>161.2346673455755</v>
-      </c>
       <c r="N23" t="n">
-        <v>652</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>171.5631203756563</v>
@@ -36423,7 +36423,7 @@
         <v>206.0930253864543</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>200.370176990574</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -36560,7 +36560,7 @@
         <v>162.7264788061112</v>
       </c>
       <c r="J25" t="n">
-        <v>330.245624934584</v>
+        <v>329.1096431449278</v>
       </c>
       <c r="K25" t="n">
         <v>106.2736524283652</v>
@@ -36590,7 +36590,7 @@
         <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>111.5901074417909</v>
+        <v>112.7260892314472</v>
       </c>
       <c r="U25" t="n">
         <v>169.0767234796404</v>
@@ -36639,16 +36639,16 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>86.76575254887953</v>
+        <v>517.0704891350363</v>
       </c>
       <c r="K26" t="n">
-        <v>182.5597537688442</v>
+        <v>652</v>
       </c>
       <c r="L26" t="n">
+        <v>382.9299307594188</v>
+      </c>
+      <c r="M26" t="n">
         <v>652</v>
-      </c>
-      <c r="M26" t="n">
-        <v>238.7557007748661</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
@@ -36657,10 +36657,10 @@
         <v>171.5631203756563</v>
       </c>
       <c r="P26" t="n">
-        <v>652</v>
+        <v>206.0930253864543</v>
       </c>
       <c r="Q26" t="n">
-        <v>598.0122381883194</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -36788,19 +36788,19 @@
         <v>45.61714403225807</v>
       </c>
       <c r="G28" t="n">
-        <v>74.46391586061698</v>
+        <v>75.59989765027325</v>
       </c>
       <c r="H28" t="n">
-        <v>96.95257881641417</v>
+        <v>96.95257881641416</v>
       </c>
       <c r="I28" t="n">
         <v>162.7264788061112</v>
       </c>
       <c r="J28" t="n">
-        <v>330.245624934584</v>
+        <v>329.1096431449278</v>
       </c>
       <c r="K28" t="n">
-        <v>106.2736524283651</v>
+        <v>106.2736524283652</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -36879,25 +36879,25 @@
         <v>86.76575254887953</v>
       </c>
       <c r="K29" t="n">
-        <v>652</v>
+        <v>182.5597537688442</v>
       </c>
       <c r="L29" t="n">
-        <v>652</v>
+        <v>226.4815175879397</v>
       </c>
       <c r="M29" t="n">
         <v>652</v>
       </c>
       <c r="N29" t="n">
-        <v>161.2346673455755</v>
+        <v>12.27418318692642</v>
       </c>
       <c r="O29" t="n">
         <v>171.5631203756563</v>
       </c>
       <c r="P29" t="n">
-        <v>206.0930253864543</v>
+        <v>652</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>598.0122381883194</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -37022,13 +37022,13 @@
         <v>39.01909516304346</v>
       </c>
       <c r="F31" t="n">
-        <v>44.48116224260178</v>
+        <v>45.61714403225807</v>
       </c>
       <c r="G31" t="n">
         <v>75.59989765027325</v>
       </c>
       <c r="H31" t="n">
-        <v>96.95257881641417</v>
+        <v>96.95257881641416</v>
       </c>
       <c r="I31" t="n">
         <v>162.7264788061112</v>
@@ -37037,7 +37037,7 @@
         <v>330.245624934584</v>
       </c>
       <c r="K31" t="n">
-        <v>106.2736524283651</v>
+        <v>106.2736524283652</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -37064,7 +37064,7 @@
         <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>112.7260892314472</v>
+        <v>111.5901074417909</v>
       </c>
       <c r="U31" t="n">
         <v>169.0767234796404</v>
@@ -37122,10 +37122,10 @@
         <v>652</v>
       </c>
       <c r="M32" t="n">
-        <v>32.66267538841175</v>
+        <v>652</v>
       </c>
       <c r="N32" t="n">
-        <v>652</v>
+        <v>630.6749135767312</v>
       </c>
       <c r="O32" t="n">
         <v>171.5631203756563</v>
@@ -37134,7 +37134,7 @@
         <v>206.0930253864543</v>
       </c>
       <c r="Q32" t="n">
-        <v>598.0122381883194</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -37256,7 +37256,7 @@
         <v>34.46378194444452</v>
       </c>
       <c r="E34" t="n">
-        <v>39.01909516304346</v>
+        <v>37.88311337338708</v>
       </c>
       <c r="F34" t="n">
         <v>45.61714403225807</v>
@@ -37301,7 +37301,7 @@
         <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>111.5901074417909</v>
+        <v>112.7260892314472</v>
       </c>
       <c r="U34" t="n">
         <v>169.0767234796404</v>
@@ -37350,7 +37350,7 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>86.76575254887953</v>
+        <v>461</v>
       </c>
       <c r="K35" t="n">
         <v>182.5597537688442</v>
@@ -37359,10 +37359,10 @@
         <v>226.4815175879397</v>
       </c>
       <c r="M35" t="n">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="N35" t="n">
-        <v>466</v>
+        <v>116.6763202548429</v>
       </c>
       <c r="O35" t="n">
         <v>171.5631203756563</v>
@@ -37371,7 +37371,7 @@
         <v>206.0930253864543</v>
       </c>
       <c r="Q35" t="n">
-        <v>39.70854750394329</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -37435,13 +37435,13 @@
         <v>315.1007319992819</v>
       </c>
       <c r="L36" t="n">
-        <v>440.8204791222719</v>
+        <v>394.8860603792003</v>
       </c>
       <c r="M36" t="n">
         <v>281.5150421645043</v>
       </c>
       <c r="N36" t="n">
-        <v>308.2046677673366</v>
+        <v>334.3411067124284</v>
       </c>
       <c r="O36" t="n">
         <v>41.47502498863511</v>
@@ -37484,37 +37484,37 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>84.88619966292134</v>
+        <v>85.88619966292134</v>
       </c>
       <c r="C37" t="n">
-        <v>99.27475335195533</v>
+        <v>100.2747533519553</v>
       </c>
       <c r="D37" t="n">
-        <v>86.46378194444452</v>
+        <v>87.46378194444452</v>
       </c>
       <c r="E37" t="n">
-        <v>91.01909516304346</v>
+        <v>92.01909516304346</v>
       </c>
       <c r="F37" t="n">
-        <v>54.82925252218119</v>
+        <v>98.61714403225807</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>128.5998976502732</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>214.7264788061112</v>
+        <v>215.7264788061112</v>
       </c>
       <c r="J37" t="n">
         <v>10.24562493458403</v>
       </c>
       <c r="K37" t="n">
-        <v>0</v>
+        <v>159.2736524283652</v>
       </c>
       <c r="L37" t="n">
-        <v>44.16348659631919</v>
+        <v>17.8371006490354</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
@@ -37544,16 +37544,16 @@
         <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>172.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>145.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>124.5563545698924</v>
+        <v>125.5563545698924</v>
       </c>
       <c r="Y37" t="n">
-        <v>84.53464715053764</v>
+        <v>85.53464715053764</v>
       </c>
     </row>
     <row r="38">
@@ -37590,16 +37590,16 @@
         <v>86.76575254887953</v>
       </c>
       <c r="K38" t="n">
-        <v>466</v>
+        <v>182.5597537688442</v>
       </c>
       <c r="L38" t="n">
         <v>226.4815175879397</v>
       </c>
       <c r="M38" t="n">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="N38" t="n">
-        <v>222.2683012727873</v>
+        <v>461</v>
       </c>
       <c r="O38" t="n">
         <v>171.5631203756563</v>
@@ -37608,7 +37608,7 @@
         <v>206.0930253864543</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>29.91056770596322</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -37672,7 +37672,7 @@
         <v>315.1007319992819</v>
       </c>
       <c r="L39" t="n">
-        <v>440.8204791222719</v>
+        <v>52.73114266247383</v>
       </c>
       <c r="M39" t="n">
         <v>281.5150421645043</v>
@@ -37681,10 +37681,10 @@
         <v>334.3411067124284</v>
       </c>
       <c r="O39" t="n">
-        <v>234.4892978840927</v>
+        <v>383.6299427053615</v>
       </c>
       <c r="P39" t="n">
-        <v>41.14799078731131</v>
+        <v>260.2987026278608</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -37724,34 +37724,34 @@
         <v>0</v>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>100.2747533519553</v>
       </c>
       <c r="D40" t="n">
-        <v>0</v>
+        <v>87.46378194444452</v>
       </c>
       <c r="E40" t="n">
-        <v>0</v>
+        <v>92.01909516304346</v>
       </c>
       <c r="F40" t="n">
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>127.5998976502732</v>
+        <v>128.5998976502732</v>
       </c>
       <c r="H40" t="n">
-        <v>100.5756407683937</v>
+        <v>149.9525788164142</v>
       </c>
       <c r="I40" t="n">
-        <v>214.7264788061112</v>
+        <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>382.245624934584</v>
+        <v>10.24562493458403</v>
       </c>
       <c r="K40" t="n">
-        <v>158.2736524283652</v>
+        <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>44.16348659631919</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
         <v>0</v>
@@ -37772,25 +37772,25 @@
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>20.84568423157079</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>164.7260892314472</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>222.0767234796404</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>58.6840831213463</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>146.6271901612903</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>125.5563545698924</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>85.53464715053764</v>
       </c>
     </row>
     <row r="41">
@@ -37833,10 +37833,10 @@
         <v>226.4815175879397</v>
       </c>
       <c r="M41" t="n">
-        <v>466</v>
+        <v>29.91056770596345</v>
       </c>
       <c r="N41" t="n">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="O41" t="n">
         <v>171.5631203756563</v>
@@ -37845,7 +37845,7 @@
         <v>206.0930253864543</v>
       </c>
       <c r="Q41" t="n">
-        <v>39.70854750394329</v>
+        <v>461</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -37903,7 +37903,7 @@
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>197.7570685018267</v>
+        <v>157.2301874176494</v>
       </c>
       <c r="K42" t="n">
         <v>315.1007319992819</v>
@@ -37912,7 +37912,7 @@
         <v>52.73114266247383</v>
       </c>
       <c r="M42" t="n">
-        <v>260.7861408783069</v>
+        <v>281.5150421645043</v>
       </c>
       <c r="N42" t="n">
         <v>334.3411067124284</v>
@@ -38012,10 +38012,10 @@
         <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>112.7260892314472</v>
+        <v>111.5901074417911</v>
       </c>
       <c r="U43" t="n">
-        <v>167.9407416899845</v>
+        <v>169.0767234796404</v>
       </c>
       <c r="V43" t="n">
         <v>120.8296897837838</v>
@@ -38064,16 +38064,16 @@
         <v>86.76575254887953</v>
       </c>
       <c r="K44" t="n">
-        <v>466</v>
+        <v>182.5597537688442</v>
       </c>
       <c r="L44" t="n">
         <v>226.4815175879397</v>
       </c>
       <c r="M44" t="n">
-        <v>222.2683012727873</v>
+        <v>461</v>
       </c>
       <c r="N44" t="n">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="O44" t="n">
         <v>171.5631203756563</v>
@@ -38082,7 +38082,7 @@
         <v>206.0930253864543</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>29.91056770596322</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
@@ -38146,16 +38146,16 @@
         <v>315.1007319992819</v>
       </c>
       <c r="L45" t="n">
-        <v>440.8204791222719</v>
+        <v>52.73114266247383</v>
       </c>
       <c r="M45" t="n">
-        <v>281.5150421645043</v>
+        <v>240.988161080327</v>
       </c>
       <c r="N45" t="n">
-        <v>308.2046677673366</v>
+        <v>334.3411067124284</v>
       </c>
       <c r="O45" t="n">
-        <v>41.47502498863511</v>
+        <v>424.1568237895389</v>
       </c>
       <c r="P45" t="n">
         <v>260.2987026278608</v>
@@ -38222,7 +38222,7 @@
         <v>330.245624934584</v>
       </c>
       <c r="K46" t="n">
-        <v>105.1376706387086</v>
+        <v>106.2736524283652</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
@@ -38249,7 +38249,7 @@
         <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>112.7260892314472</v>
+        <v>111.5901074417907</v>
       </c>
       <c r="U46" t="n">
         <v>169.0767234796404</v>
